--- a/backend/templates/UC-18gsm-290NP-ABQR.xlsx
+++ b/backend/templates/UC-18gsm-290NP-ABQR.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6088979-FD2B-4E4D-B715-F668CB1598A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866E2096-4EC3-4B14-AC66-203BD360FFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Page1" sheetId="6" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1855,6 +1858,54 @@
     <xf numFmtId="2" fontId="1" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1864,9 +1915,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1921,9 +1969,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1936,155 +1981,92 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2098,97 +2080,307 @@
     <xf numFmtId="1" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -2208,197 +2400,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3045,35 +3048,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="157" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="157" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="142"/>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="142"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3094,12 +3097,12 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="143" t="s">
+      <c r="A4" s="158" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="144"/>
-      <c r="C4" s="145"/>
-      <c r="D4" s="146"/>
+      <c r="B4" s="159"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="161"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -3111,19 +3114,19 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="138"/>
-      <c r="K4" s="139"/>
+      <c r="J4" s="153"/>
+      <c r="K4" s="154"/>
       <c r="M4" s="45" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="147" t="s">
+      <c r="A5" s="162" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="148"/>
-      <c r="C5" s="149"/>
-      <c r="D5" s="150"/>
+      <c r="B5" s="163"/>
+      <c r="C5" s="164"/>
+      <c r="D5" s="165"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -3135,64 +3138,64 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="140"/>
-      <c r="K5" s="141"/>
+      <c r="J5" s="155"/>
+      <c r="K5" s="156"/>
     </row>
     <row r="6" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="155" t="s">
+      <c r="A6" s="169" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="156"/>
-      <c r="C6" s="157"/>
+      <c r="B6" s="170"/>
+      <c r="C6" s="171"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="G6" s="133"/>
-      <c r="H6" s="154"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="134"/>
-      <c r="K6" s="135"/>
+      <c r="G6" s="149"/>
+      <c r="H6" s="168"/>
+      <c r="I6" s="149"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="151"/>
     </row>
     <row r="7" spans="1:13" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="158" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="136"/>
-      <c r="C7" s="136"/>
-      <c r="D7" s="136" t="s">
+      <c r="A7" s="136" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="137"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="136" t="s">
+      <c r="E7" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="136" t="s">
+      <c r="F7" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="151" t="s">
+      <c r="G7" s="166" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="151" t="s">
+      <c r="H7" s="166" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="136" t="s">
+      <c r="I7" s="137" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="136"/>
-      <c r="K7" s="137"/>
+      <c r="J7" s="137"/>
+      <c r="K7" s="152"/>
     </row>
     <row r="8" spans="1:13" s="5" customFormat="1" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="159"/>
-      <c r="B8" s="153"/>
-      <c r="C8" s="153"/>
-      <c r="D8" s="153"/>
-      <c r="E8" s="153" t="s">
+      <c r="A8" s="138"/>
+      <c r="B8" s="139"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="139"/>
+      <c r="E8" s="139" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="153"/>
-      <c r="G8" s="152"/>
-      <c r="H8" s="152"/>
+      <c r="F8" s="139"/>
+      <c r="G8" s="167"/>
+      <c r="H8" s="167"/>
       <c r="I8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3594,11 +3597,11 @@
       <c r="K38" s="28"/>
     </row>
     <row r="39" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="166" t="s">
+      <c r="A39" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="167"/>
-      <c r="C39" s="168"/>
+      <c r="B39" s="147"/>
+      <c r="C39" s="148"/>
       <c r="D39" s="35" t="e">
         <f>AVERAGE(D9:D38)</f>
         <v>#DIV/0!</v>
@@ -3633,11 +3636,11 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="163" t="s">
+      <c r="A40" s="143" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="164"/>
-      <c r="C40" s="165"/>
+      <c r="B40" s="144"/>
+      <c r="C40" s="145"/>
       <c r="D40" s="38">
         <f>MIN(D9:D38)</f>
         <v>0</v>
@@ -3672,11 +3675,11 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="160" t="s">
+      <c r="A41" s="140" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="161"/>
-      <c r="C41" s="162"/>
+      <c r="B41" s="141"/>
+      <c r="C41" s="142"/>
       <c r="D41" s="41">
         <f>MAX(D9:D38)</f>
         <v>0</v>
@@ -3717,8 +3720,8 @@
       <c r="A42" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="170"/>
-      <c r="C42" s="170"/>
+      <c r="B42" s="134"/>
+      <c r="C42" s="134"/>
       <c r="D42" s="44" t="s">
         <v>22</v>
       </c>
@@ -3735,8 +3738,8 @@
     </row>
     <row r="43" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="50"/>
-      <c r="B43" s="171"/>
-      <c r="C43" s="171"/>
+      <c r="B43" s="135"/>
+      <c r="C43" s="135"/>
       <c r="D43" s="44"/>
       <c r="F43" s="46"/>
       <c r="G43" s="47"/>
@@ -3745,11 +3748,11 @@
       <c r="J43" s="51"/>
     </row>
     <row r="44" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="169" t="s">
+      <c r="A44" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="169"/>
-      <c r="C44" s="169"/>
+      <c r="B44" s="133"/>
+      <c r="C44" s="133"/>
       <c r="D44" s="44"/>
       <c r="E44" s="44"/>
       <c r="F44" s="47" t="s">
@@ -3761,11 +3764,11 @@
       <c r="H44" s="44"/>
     </row>
     <row r="45" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="169" t="s">
+      <c r="A45" s="133" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="169"/>
-      <c r="C45" s="169"/>
+      <c r="B45" s="133"/>
+      <c r="C45" s="133"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="44"/>
@@ -3776,9 +3779,9 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="169"/>
-      <c r="B46" s="169"/>
-      <c r="C46" s="169"/>
+      <c r="A46" s="133"/>
+      <c r="B46" s="133"/>
+      <c r="C46" s="133"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="44"/>
@@ -3807,16 +3810,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="26">
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A39:C39"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="J4:K4"/>
@@ -3833,6 +3826,16 @@
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A45:C45"/>
   </mergeCells>
   <conditionalFormatting sqref="D9:D41">
     <cfRule type="cellIs" dxfId="24" priority="13" operator="greaterThan">
@@ -3915,35 +3918,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="157" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="157" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="142"/>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="142"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3964,18 +3967,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="143" t="s">
+      <c r="A4" s="158" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="144">
+      <c r="B4" s="159">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="219">
+      <c r="C4" s="184">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="181"/>
+      <c r="D4" s="185"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -3993,25 +3996,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="220">
+      <c r="J4" s="172">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="221"/>
+      <c r="K4" s="173"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="147" t="s">
+      <c r="A5" s="162" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="148">
+      <c r="B5" s="163">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="149">
+      <c r="C5" s="164">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="150"/>
+      <c r="D5" s="165"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -4029,104 +4032,104 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="222">
+      <c r="J5" s="174">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="223"/>
+      <c r="K5" s="175"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="172" t="s">
+      <c r="A6" s="211" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="173"/>
-      <c r="C6" s="174"/>
-      <c r="D6" s="175"/>
-      <c r="E6" s="176"/>
-      <c r="F6" s="177"/>
-      <c r="G6" s="192"/>
-      <c r="H6" s="177"/>
-      <c r="I6" s="206"/>
-      <c r="J6" s="207"/>
+      <c r="B6" s="212"/>
+      <c r="C6" s="213"/>
+      <c r="D6" s="214"/>
+      <c r="E6" s="203"/>
+      <c r="F6" s="198"/>
+      <c r="G6" s="197"/>
+      <c r="H6" s="198"/>
+      <c r="I6" s="199"/>
+      <c r="J6" s="200"/>
       <c r="K6" s="56"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="175" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="176"/>
-      <c r="C7" s="176"/>
-      <c r="D7" s="180" t="s">
+      <c r="A7" s="214" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="203"/>
+      <c r="C7" s="203"/>
+      <c r="D7" s="217" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="176"/>
-      <c r="F7" s="181"/>
-      <c r="G7" s="192" t="s">
+      <c r="E7" s="203"/>
+      <c r="F7" s="185"/>
+      <c r="G7" s="197" t="s">
         <v>126</v>
       </c>
-      <c r="H7" s="176"/>
-      <c r="I7" s="192" t="s">
+      <c r="H7" s="203"/>
+      <c r="I7" s="197" t="s">
         <v>135</v>
       </c>
-      <c r="J7" s="177"/>
-      <c r="K7" s="210" t="s">
+      <c r="J7" s="198"/>
+      <c r="K7" s="192" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="186"/>
-      <c r="B8" s="187"/>
-      <c r="C8" s="187"/>
-      <c r="D8" s="186" t="s">
+      <c r="A8" s="222"/>
+      <c r="B8" s="204"/>
+      <c r="C8" s="204"/>
+      <c r="D8" s="222" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="189" t="s">
+      <c r="E8" s="224" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="190" t="s">
+      <c r="F8" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="193"/>
-      <c r="H8" s="187"/>
-      <c r="I8" s="193" t="s">
+      <c r="G8" s="180"/>
+      <c r="H8" s="204"/>
+      <c r="I8" s="180" t="s">
         <v>136</v>
       </c>
-      <c r="J8" s="190"/>
-      <c r="K8" s="211"/>
+      <c r="J8" s="181"/>
+      <c r="K8" s="193"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="186"/>
-      <c r="B9" s="187"/>
-      <c r="C9" s="187"/>
-      <c r="D9" s="186"/>
-      <c r="E9" s="151"/>
-      <c r="F9" s="190"/>
-      <c r="G9" s="193"/>
-      <c r="H9" s="187"/>
+      <c r="A9" s="222"/>
+      <c r="B9" s="204"/>
+      <c r="C9" s="204"/>
+      <c r="D9" s="222"/>
+      <c r="E9" s="166"/>
+      <c r="F9" s="181"/>
+      <c r="G9" s="180"/>
+      <c r="H9" s="204"/>
       <c r="I9" s="58" t="s">
         <v>42</v>
       </c>
       <c r="J9" s="59">
         <v>290</v>
       </c>
-      <c r="K9" s="211"/>
+      <c r="K9" s="193"/>
     </row>
     <row r="10" spans="1:11" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="186"/>
-      <c r="B10" s="187"/>
-      <c r="C10" s="187"/>
-      <c r="D10" s="188"/>
-      <c r="E10" s="152"/>
-      <c r="F10" s="191"/>
-      <c r="G10" s="194"/>
-      <c r="H10" s="195"/>
+      <c r="A10" s="222"/>
+      <c r="B10" s="204"/>
+      <c r="C10" s="204"/>
+      <c r="D10" s="223"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="225"/>
+      <c r="G10" s="205"/>
+      <c r="H10" s="206"/>
       <c r="I10" s="60" t="s">
         <v>43</v>
       </c>
       <c r="J10" s="61">
         <v>293</v>
       </c>
-      <c r="K10" s="212"/>
+      <c r="K10" s="194"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="62">
@@ -4144,10 +4147,10 @@
       <c r="D11" s="65"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
-      <c r="G11" s="198"/>
-      <c r="H11" s="198"/>
-      <c r="I11" s="224"/>
-      <c r="J11" s="225"/>
+      <c r="G11" s="209"/>
+      <c r="H11" s="209"/>
+      <c r="I11" s="178"/>
+      <c r="J11" s="179"/>
       <c r="K11" s="66"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4166,10 +4169,10 @@
       <c r="D12" s="70"/>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
-      <c r="G12" s="199"/>
-      <c r="H12" s="199"/>
-      <c r="I12" s="204"/>
-      <c r="J12" s="205"/>
+      <c r="G12" s="210"/>
+      <c r="H12" s="210"/>
+      <c r="I12" s="176"/>
+      <c r="J12" s="177"/>
       <c r="K12" s="71"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4188,10 +4191,10 @@
       <c r="D13" s="70"/>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
-      <c r="G13" s="199"/>
-      <c r="H13" s="199"/>
-      <c r="I13" s="204"/>
-      <c r="J13" s="205"/>
+      <c r="G13" s="210"/>
+      <c r="H13" s="210"/>
+      <c r="I13" s="176"/>
+      <c r="J13" s="177"/>
       <c r="K13" s="71"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4210,10 +4213,10 @@
       <c r="D14" s="70"/>
       <c r="E14" s="25"/>
       <c r="F14" s="25"/>
-      <c r="G14" s="199"/>
-      <c r="H14" s="199"/>
-      <c r="I14" s="204"/>
-      <c r="J14" s="205"/>
+      <c r="G14" s="210"/>
+      <c r="H14" s="210"/>
+      <c r="I14" s="176"/>
+      <c r="J14" s="177"/>
       <c r="K14" s="71"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4232,10 +4235,10 @@
       <c r="D15" s="70"/>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
-      <c r="G15" s="199"/>
-      <c r="H15" s="199"/>
-      <c r="I15" s="204"/>
-      <c r="J15" s="205"/>
+      <c r="G15" s="210"/>
+      <c r="H15" s="210"/>
+      <c r="I15" s="176"/>
+      <c r="J15" s="177"/>
       <c r="K15" s="71"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4254,10 +4257,10 @@
       <c r="D16" s="65"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
-      <c r="G16" s="198"/>
-      <c r="H16" s="198"/>
-      <c r="I16" s="204"/>
-      <c r="J16" s="205"/>
+      <c r="G16" s="209"/>
+      <c r="H16" s="209"/>
+      <c r="I16" s="176"/>
+      <c r="J16" s="177"/>
       <c r="K16" s="66"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4276,10 +4279,10 @@
       <c r="D17" s="70"/>
       <c r="E17" s="25"/>
       <c r="F17" s="25"/>
-      <c r="G17" s="199"/>
-      <c r="H17" s="199"/>
-      <c r="I17" s="204"/>
-      <c r="J17" s="205"/>
+      <c r="G17" s="210"/>
+      <c r="H17" s="210"/>
+      <c r="I17" s="176"/>
+      <c r="J17" s="177"/>
       <c r="K17" s="71"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4298,10 +4301,10 @@
       <c r="D18" s="70"/>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
-      <c r="G18" s="199"/>
-      <c r="H18" s="199"/>
-      <c r="I18" s="204"/>
-      <c r="J18" s="205"/>
+      <c r="G18" s="210"/>
+      <c r="H18" s="210"/>
+      <c r="I18" s="176"/>
+      <c r="J18" s="177"/>
       <c r="K18" s="71"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4320,10 +4323,10 @@
       <c r="D19" s="70"/>
       <c r="E19" s="25"/>
       <c r="F19" s="25"/>
-      <c r="G19" s="199"/>
-      <c r="H19" s="199"/>
-      <c r="I19" s="204"/>
-      <c r="J19" s="205"/>
+      <c r="G19" s="210"/>
+      <c r="H19" s="210"/>
+      <c r="I19" s="176"/>
+      <c r="J19" s="177"/>
       <c r="K19" s="71"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4342,10 +4345,10 @@
       <c r="D20" s="70"/>
       <c r="E20" s="25"/>
       <c r="F20" s="25"/>
-      <c r="G20" s="200"/>
-      <c r="H20" s="201"/>
-      <c r="I20" s="204"/>
-      <c r="J20" s="205"/>
+      <c r="G20" s="182"/>
+      <c r="H20" s="183"/>
+      <c r="I20" s="176"/>
+      <c r="J20" s="177"/>
       <c r="K20" s="71"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4364,10 +4367,10 @@
       <c r="D21" s="70"/>
       <c r="E21" s="25"/>
       <c r="F21" s="25"/>
-      <c r="G21" s="200"/>
-      <c r="H21" s="201"/>
-      <c r="I21" s="204"/>
-      <c r="J21" s="205"/>
+      <c r="G21" s="182"/>
+      <c r="H21" s="183"/>
+      <c r="I21" s="176"/>
+      <c r="J21" s="177"/>
       <c r="K21" s="71"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4386,10 +4389,10 @@
       <c r="D22" s="70"/>
       <c r="E22" s="25"/>
       <c r="F22" s="25"/>
-      <c r="G22" s="200"/>
-      <c r="H22" s="201"/>
-      <c r="I22" s="204"/>
-      <c r="J22" s="205"/>
+      <c r="G22" s="182"/>
+      <c r="H22" s="183"/>
+      <c r="I22" s="176"/>
+      <c r="J22" s="177"/>
       <c r="K22" s="71"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4408,10 +4411,10 @@
       <c r="D23" s="70"/>
       <c r="E23" s="25"/>
       <c r="F23" s="25"/>
-      <c r="G23" s="200"/>
-      <c r="H23" s="201"/>
-      <c r="I23" s="204"/>
-      <c r="J23" s="205"/>
+      <c r="G23" s="182"/>
+      <c r="H23" s="183"/>
+      <c r="I23" s="176"/>
+      <c r="J23" s="177"/>
       <c r="K23" s="71"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4430,10 +4433,10 @@
       <c r="D24" s="70"/>
       <c r="E24" s="25"/>
       <c r="F24" s="25"/>
-      <c r="G24" s="200"/>
-      <c r="H24" s="201"/>
-      <c r="I24" s="204"/>
-      <c r="J24" s="205"/>
+      <c r="G24" s="182"/>
+      <c r="H24" s="183"/>
+      <c r="I24" s="176"/>
+      <c r="J24" s="177"/>
       <c r="K24" s="71"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4452,10 +4455,10 @@
       <c r="D25" s="70"/>
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
-      <c r="G25" s="200"/>
-      <c r="H25" s="201"/>
-      <c r="I25" s="204"/>
-      <c r="J25" s="205"/>
+      <c r="G25" s="182"/>
+      <c r="H25" s="183"/>
+      <c r="I25" s="176"/>
+      <c r="J25" s="177"/>
       <c r="K25" s="71"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4474,10 +4477,10 @@
       <c r="D26" s="70"/>
       <c r="E26" s="25"/>
       <c r="F26" s="25"/>
-      <c r="G26" s="200"/>
-      <c r="H26" s="201"/>
-      <c r="I26" s="204"/>
-      <c r="J26" s="205"/>
+      <c r="G26" s="182"/>
+      <c r="H26" s="183"/>
+      <c r="I26" s="176"/>
+      <c r="J26" s="177"/>
       <c r="K26" s="71"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4496,10 +4499,10 @@
       <c r="D27" s="70"/>
       <c r="E27" s="25"/>
       <c r="F27" s="25"/>
-      <c r="G27" s="200"/>
-      <c r="H27" s="201"/>
-      <c r="I27" s="204"/>
-      <c r="J27" s="205"/>
+      <c r="G27" s="182"/>
+      <c r="H27" s="183"/>
+      <c r="I27" s="176"/>
+      <c r="J27" s="177"/>
       <c r="K27" s="71"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4518,10 +4521,10 @@
       <c r="D28" s="70"/>
       <c r="E28" s="25"/>
       <c r="F28" s="25"/>
-      <c r="G28" s="200"/>
-      <c r="H28" s="201"/>
-      <c r="I28" s="204"/>
-      <c r="J28" s="205"/>
+      <c r="G28" s="182"/>
+      <c r="H28" s="183"/>
+      <c r="I28" s="176"/>
+      <c r="J28" s="177"/>
       <c r="K28" s="71"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4540,10 +4543,10 @@
       <c r="D29" s="70"/>
       <c r="E29" s="25"/>
       <c r="F29" s="25"/>
-      <c r="G29" s="200"/>
-      <c r="H29" s="201"/>
-      <c r="I29" s="204"/>
-      <c r="J29" s="205"/>
+      <c r="G29" s="182"/>
+      <c r="H29" s="183"/>
+      <c r="I29" s="176"/>
+      <c r="J29" s="177"/>
       <c r="K29" s="71"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4562,10 +4565,10 @@
       <c r="D30" s="70"/>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
-      <c r="G30" s="200"/>
-      <c r="H30" s="201"/>
-      <c r="I30" s="204"/>
-      <c r="J30" s="205"/>
+      <c r="G30" s="182"/>
+      <c r="H30" s="183"/>
+      <c r="I30" s="176"/>
+      <c r="J30" s="177"/>
       <c r="K30" s="71"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4584,10 +4587,10 @@
       <c r="D31" s="70"/>
       <c r="E31" s="25"/>
       <c r="F31" s="25"/>
-      <c r="G31" s="200"/>
-      <c r="H31" s="201"/>
-      <c r="I31" s="204"/>
-      <c r="J31" s="205"/>
+      <c r="G31" s="182"/>
+      <c r="H31" s="183"/>
+      <c r="I31" s="176"/>
+      <c r="J31" s="177"/>
       <c r="K31" s="71"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4606,10 +4609,10 @@
       <c r="D32" s="70"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
-      <c r="G32" s="200"/>
-      <c r="H32" s="201"/>
-      <c r="I32" s="204"/>
-      <c r="J32" s="205"/>
+      <c r="G32" s="182"/>
+      <c r="H32" s="183"/>
+      <c r="I32" s="176"/>
+      <c r="J32" s="177"/>
       <c r="K32" s="71"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4628,10 +4631,10 @@
       <c r="D33" s="70"/>
       <c r="E33" s="25"/>
       <c r="F33" s="25"/>
-      <c r="G33" s="200"/>
-      <c r="H33" s="201"/>
-      <c r="I33" s="204"/>
-      <c r="J33" s="205"/>
+      <c r="G33" s="182"/>
+      <c r="H33" s="183"/>
+      <c r="I33" s="176"/>
+      <c r="J33" s="177"/>
       <c r="K33" s="71"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4650,10 +4653,10 @@
       <c r="D34" s="70"/>
       <c r="E34" s="25"/>
       <c r="F34" s="25"/>
-      <c r="G34" s="200"/>
-      <c r="H34" s="201"/>
-      <c r="I34" s="204"/>
-      <c r="J34" s="205"/>
+      <c r="G34" s="182"/>
+      <c r="H34" s="183"/>
+      <c r="I34" s="176"/>
+      <c r="J34" s="177"/>
       <c r="K34" s="71"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4672,10 +4675,10 @@
       <c r="D35" s="70"/>
       <c r="E35" s="25"/>
       <c r="F35" s="25"/>
-      <c r="G35" s="200"/>
-      <c r="H35" s="201"/>
-      <c r="I35" s="204"/>
-      <c r="J35" s="205"/>
+      <c r="G35" s="182"/>
+      <c r="H35" s="183"/>
+      <c r="I35" s="176"/>
+      <c r="J35" s="177"/>
       <c r="K35" s="71"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4694,10 +4697,10 @@
       <c r="D36" s="70"/>
       <c r="E36" s="25"/>
       <c r="F36" s="25"/>
-      <c r="G36" s="200"/>
-      <c r="H36" s="201"/>
-      <c r="I36" s="204"/>
-      <c r="J36" s="205"/>
+      <c r="G36" s="182"/>
+      <c r="H36" s="183"/>
+      <c r="I36" s="176"/>
+      <c r="J36" s="177"/>
       <c r="K36" s="71"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4716,10 +4719,10 @@
       <c r="D37" s="70"/>
       <c r="E37" s="25"/>
       <c r="F37" s="25"/>
-      <c r="G37" s="200"/>
-      <c r="H37" s="201"/>
-      <c r="I37" s="204"/>
-      <c r="J37" s="205"/>
+      <c r="G37" s="182"/>
+      <c r="H37" s="183"/>
+      <c r="I37" s="176"/>
+      <c r="J37" s="177"/>
       <c r="K37" s="71"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4738,10 +4741,10 @@
       <c r="D38" s="70"/>
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
-      <c r="G38" s="200"/>
-      <c r="H38" s="201"/>
-      <c r="I38" s="204"/>
-      <c r="J38" s="205"/>
+      <c r="G38" s="182"/>
+      <c r="H38" s="183"/>
+      <c r="I38" s="176"/>
+      <c r="J38" s="177"/>
       <c r="K38" s="71"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4760,10 +4763,10 @@
       <c r="D39" s="70"/>
       <c r="E39" s="25"/>
       <c r="F39" s="25"/>
-      <c r="G39" s="200"/>
-      <c r="H39" s="201"/>
-      <c r="I39" s="204"/>
-      <c r="J39" s="205"/>
+      <c r="G39" s="182"/>
+      <c r="H39" s="183"/>
+      <c r="I39" s="176"/>
+      <c r="J39" s="177"/>
       <c r="K39" s="71"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4782,18 +4785,18 @@
       <c r="D40" s="70"/>
       <c r="E40" s="25"/>
       <c r="F40" s="25"/>
-      <c r="G40" s="199"/>
-      <c r="H40" s="199"/>
-      <c r="I40" s="204"/>
-      <c r="J40" s="205"/>
+      <c r="G40" s="210"/>
+      <c r="H40" s="210"/>
+      <c r="I40" s="176"/>
+      <c r="J40" s="177"/>
       <c r="K40" s="71"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="182" t="s">
+      <c r="A41" s="218" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="183"/>
-      <c r="C41" s="183"/>
+      <c r="B41" s="219"/>
+      <c r="C41" s="219"/>
       <c r="D41" s="79" t="e">
         <f>AVERAGE(D11:D40)</f>
         <v>#DIV/0!</v>
@@ -4806,27 +4809,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G41" s="196" t="e">
+      <c r="G41" s="207" t="e">
         <f>AVERAGE(G11:H40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="197"/>
-      <c r="I41" s="208" t="e">
+      <c r="H41" s="208"/>
+      <c r="I41" s="201" t="e">
         <f>AVERAGE(I11:J40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="209"/>
+      <c r="J41" s="202"/>
       <c r="K41" s="37" t="e">
         <f>AVERAGE(K11:K40)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="184" t="s">
+      <c r="A42" s="220" t="s">
         <v>31</v>
       </c>
-      <c r="B42" s="185"/>
-      <c r="C42" s="185"/>
+      <c r="B42" s="221"/>
+      <c r="C42" s="221"/>
       <c r="D42" s="80">
         <f>MIN(D11:D40)</f>
         <v>0</v>
@@ -4839,27 +4842,27 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G42" s="217">
+      <c r="G42" s="190">
         <f>MIN(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="218"/>
-      <c r="I42" s="202">
+      <c r="H42" s="191"/>
+      <c r="I42" s="195">
         <f>MIN(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="203"/>
+      <c r="J42" s="196"/>
       <c r="K42" s="40">
         <f>MIN(K11:K40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="178" t="s">
+      <c r="A43" s="215" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="179"/>
-      <c r="C43" s="179"/>
+      <c r="B43" s="216"/>
+      <c r="C43" s="216"/>
       <c r="D43" s="81">
         <f>MAX(D11:D40)</f>
         <v>0</v>
@@ -4872,16 +4875,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G43" s="215">
+      <c r="G43" s="188">
         <f>MAX(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="216"/>
-      <c r="I43" s="213">
+      <c r="H43" s="189"/>
+      <c r="I43" s="186">
         <f>MAX(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="214"/>
+      <c r="J43" s="187"/>
       <c r="K43" s="83">
         <f>MAX(K11:K40)</f>
         <v>0</v>
@@ -4891,8 +4894,8 @@
       <c r="A44" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="170"/>
-      <c r="C44" s="170"/>
+      <c r="B44" s="134"/>
+      <c r="C44" s="134"/>
       <c r="D44" s="44" t="s">
         <v>22</v>
       </c>
@@ -4909,8 +4912,8 @@
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="50"/>
-      <c r="B45" s="171"/>
-      <c r="C45" s="171"/>
+      <c r="B45" s="135"/>
+      <c r="C45" s="135"/>
       <c r="D45" s="44"/>
       <c r="F45" s="46"/>
       <c r="G45" s="47"/>
@@ -4919,11 +4922,11 @@
       <c r="J45" s="51"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="169" t="s">
+      <c r="A46" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="169"/>
-      <c r="C46" s="169"/>
+      <c r="B46" s="133"/>
+      <c r="C46" s="133"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="47" t="s">
@@ -4936,11 +4939,11 @@
       <c r="H46" s="44"/>
     </row>
     <row r="47" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="169" t="s">
+      <c r="A47" s="133" t="s">
         <v>134</v>
       </c>
-      <c r="B47" s="169"/>
-      <c r="C47" s="169"/>
+      <c r="B47" s="133"/>
+      <c r="C47" s="133"/>
       <c r="D47" s="44"/>
       <c r="E47" s="44"/>
       <c r="F47" s="44"/>
@@ -4995,6 +4998,84 @@
     </row>
   </sheetData>
   <mergeCells count="94">
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A7:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H10"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K7:K10"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="J5:K5"/>
@@ -5011,84 +5092,6 @@
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="G39:H39"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K7:K10"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H10"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A7:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="D11:D43">
@@ -5144,35 +5147,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="157" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="157" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="142"/>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="142"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -5193,18 +5196,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="143" t="s">
+      <c r="A4" s="158" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="144">
+      <c r="B4" s="159">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="219">
+      <c r="C4" s="184">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="181"/>
+      <c r="D4" s="185"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -5222,25 +5225,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="220">
+      <c r="J4" s="172">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="221"/>
+      <c r="K4" s="173"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="147" t="s">
+      <c r="A5" s="162" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="148">
+      <c r="B5" s="163">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="149">
+      <c r="C5" s="164">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="150"/>
+      <c r="D5" s="165"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -5258,81 +5261,81 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="222">
+      <c r="J5" s="174">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="223"/>
+      <c r="K5" s="175"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="155" t="s">
+      <c r="A6" s="169" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="156"/>
-      <c r="C6" s="234"/>
-      <c r="D6" s="235"/>
-      <c r="E6" s="134"/>
-      <c r="F6" s="134"/>
-      <c r="G6" s="154"/>
+      <c r="B6" s="170"/>
+      <c r="C6" s="226"/>
+      <c r="D6" s="227"/>
+      <c r="E6" s="150"/>
+      <c r="F6" s="150"/>
+      <c r="G6" s="168"/>
       <c r="H6" s="119"/>
-      <c r="I6" s="175"/>
-      <c r="J6" s="176"/>
-      <c r="K6" s="210"/>
+      <c r="I6" s="214"/>
+      <c r="J6" s="203"/>
+      <c r="K6" s="192"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="175" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="176"/>
-      <c r="C7" s="210"/>
-      <c r="D7" s="180" t="s">
+      <c r="A7" s="214" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="203"/>
+      <c r="C7" s="192"/>
+      <c r="D7" s="217" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="236"/>
-      <c r="F7" s="236"/>
-      <c r="G7" s="181"/>
-      <c r="H7" s="226" t="s">
+      <c r="E7" s="228"/>
+      <c r="F7" s="228"/>
+      <c r="G7" s="185"/>
+      <c r="H7" s="232" t="s">
         <v>130</v>
       </c>
-      <c r="I7" s="186"/>
-      <c r="J7" s="187"/>
-      <c r="K7" s="211"/>
+      <c r="I7" s="222"/>
+      <c r="J7" s="204"/>
+      <c r="K7" s="193"/>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="186"/>
-      <c r="B8" s="187"/>
-      <c r="C8" s="211"/>
-      <c r="D8" s="232" t="s">
+      <c r="A8" s="222"/>
+      <c r="B8" s="204"/>
+      <c r="C8" s="193"/>
+      <c r="D8" s="238" t="s">
         <v>127</v>
       </c>
-      <c r="E8" s="189" t="s">
+      <c r="E8" s="224" t="s">
         <v>128</v>
       </c>
-      <c r="F8" s="189" t="s">
+      <c r="F8" s="224" t="s">
         <v>131</v>
       </c>
-      <c r="G8" s="189" t="s">
+      <c r="G8" s="224" t="s">
         <v>129</v>
       </c>
-      <c r="H8" s="227" t="s">
+      <c r="H8" s="233" t="s">
         <v>130</v>
       </c>
-      <c r="I8" s="186"/>
-      <c r="J8" s="187"/>
-      <c r="K8" s="211"/>
+      <c r="I8" s="222"/>
+      <c r="J8" s="204"/>
+      <c r="K8" s="193"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="188"/>
-      <c r="B9" s="195"/>
-      <c r="C9" s="212"/>
-      <c r="D9" s="233"/>
-      <c r="E9" s="152"/>
-      <c r="F9" s="152"/>
-      <c r="G9" s="152"/>
-      <c r="H9" s="228"/>
-      <c r="I9" s="186"/>
-      <c r="J9" s="187"/>
-      <c r="K9" s="211"/>
+      <c r="A9" s="223"/>
+      <c r="B9" s="206"/>
+      <c r="C9" s="194"/>
+      <c r="D9" s="239"/>
+      <c r="E9" s="167"/>
+      <c r="F9" s="167"/>
+      <c r="G9" s="167"/>
+      <c r="H9" s="234"/>
+      <c r="I9" s="222"/>
+      <c r="J9" s="204"/>
+      <c r="K9" s="193"/>
     </row>
     <row r="10" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="62">
@@ -5352,9 +5355,9 @@
       <c r="F10" s="23"/>
       <c r="G10" s="121"/>
       <c r="H10" s="122"/>
-      <c r="I10" s="186"/>
-      <c r="J10" s="187"/>
-      <c r="K10" s="211"/>
+      <c r="I10" s="222"/>
+      <c r="J10" s="204"/>
+      <c r="K10" s="193"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="67">
@@ -5374,9 +5377,9 @@
       <c r="F11" s="26"/>
       <c r="G11" s="124"/>
       <c r="H11" s="125"/>
-      <c r="I11" s="186"/>
-      <c r="J11" s="187"/>
-      <c r="K11" s="211"/>
+      <c r="I11" s="222"/>
+      <c r="J11" s="204"/>
+      <c r="K11" s="193"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="67">
@@ -5396,9 +5399,9 @@
       <c r="F12" s="26"/>
       <c r="G12" s="124"/>
       <c r="H12" s="125"/>
-      <c r="I12" s="186"/>
-      <c r="J12" s="187"/>
-      <c r="K12" s="211"/>
+      <c r="I12" s="222"/>
+      <c r="J12" s="204"/>
+      <c r="K12" s="193"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="67">
@@ -5418,9 +5421,9 @@
       <c r="F13" s="23"/>
       <c r="G13" s="121"/>
       <c r="H13" s="125"/>
-      <c r="I13" s="186"/>
-      <c r="J13" s="187"/>
-      <c r="K13" s="211"/>
+      <c r="I13" s="222"/>
+      <c r="J13" s="204"/>
+      <c r="K13" s="193"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="67">
@@ -5440,9 +5443,9 @@
       <c r="F14" s="26"/>
       <c r="G14" s="124"/>
       <c r="H14" s="125"/>
-      <c r="I14" s="186"/>
-      <c r="J14" s="187"/>
-      <c r="K14" s="211"/>
+      <c r="I14" s="222"/>
+      <c r="J14" s="204"/>
+      <c r="K14" s="193"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="67">
@@ -5462,9 +5465,9 @@
       <c r="F15" s="26"/>
       <c r="G15" s="124"/>
       <c r="H15" s="125"/>
-      <c r="I15" s="186"/>
-      <c r="J15" s="187"/>
-      <c r="K15" s="211"/>
+      <c r="I15" s="222"/>
+      <c r="J15" s="204"/>
+      <c r="K15" s="193"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="67">
@@ -5484,9 +5487,9 @@
       <c r="F16" s="26"/>
       <c r="G16" s="124"/>
       <c r="H16" s="125"/>
-      <c r="I16" s="186"/>
-      <c r="J16" s="187"/>
-      <c r="K16" s="211"/>
+      <c r="I16" s="222"/>
+      <c r="J16" s="204"/>
+      <c r="K16" s="193"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="67">
@@ -5506,9 +5509,9 @@
       <c r="F17" s="26"/>
       <c r="G17" s="124"/>
       <c r="H17" s="125"/>
-      <c r="I17" s="186"/>
-      <c r="J17" s="187"/>
-      <c r="K17" s="211"/>
+      <c r="I17" s="222"/>
+      <c r="J17" s="204"/>
+      <c r="K17" s="193"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="67">
@@ -5528,9 +5531,9 @@
       <c r="F18" s="26"/>
       <c r="G18" s="124"/>
       <c r="H18" s="125"/>
-      <c r="I18" s="186"/>
-      <c r="J18" s="187"/>
-      <c r="K18" s="211"/>
+      <c r="I18" s="222"/>
+      <c r="J18" s="204"/>
+      <c r="K18" s="193"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="67">
@@ -5550,9 +5553,9 @@
       <c r="F19" s="26"/>
       <c r="G19" s="124"/>
       <c r="H19" s="125"/>
-      <c r="I19" s="186"/>
-      <c r="J19" s="187"/>
-      <c r="K19" s="211"/>
+      <c r="I19" s="222"/>
+      <c r="J19" s="204"/>
+      <c r="K19" s="193"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="75">
@@ -5572,9 +5575,9 @@
       <c r="F20" s="26"/>
       <c r="G20" s="124"/>
       <c r="H20" s="125"/>
-      <c r="I20" s="186"/>
-      <c r="J20" s="187"/>
-      <c r="K20" s="211"/>
+      <c r="I20" s="222"/>
+      <c r="J20" s="204"/>
+      <c r="K20" s="193"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="67">
@@ -5594,9 +5597,9 @@
       <c r="F21" s="26"/>
       <c r="G21" s="124"/>
       <c r="H21" s="125"/>
-      <c r="I21" s="186"/>
-      <c r="J21" s="187"/>
-      <c r="K21" s="211"/>
+      <c r="I21" s="222"/>
+      <c r="J21" s="204"/>
+      <c r="K21" s="193"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="67">
@@ -5616,9 +5619,9 @@
       <c r="F22" s="26"/>
       <c r="G22" s="124"/>
       <c r="H22" s="125"/>
-      <c r="I22" s="186"/>
-      <c r="J22" s="187"/>
-      <c r="K22" s="211"/>
+      <c r="I22" s="222"/>
+      <c r="J22" s="204"/>
+      <c r="K22" s="193"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="67">
@@ -5638,9 +5641,9 @@
       <c r="F23" s="26"/>
       <c r="G23" s="124"/>
       <c r="H23" s="125"/>
-      <c r="I23" s="186"/>
-      <c r="J23" s="187"/>
-      <c r="K23" s="211"/>
+      <c r="I23" s="222"/>
+      <c r="J23" s="204"/>
+      <c r="K23" s="193"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="67">
@@ -5660,9 +5663,9 @@
       <c r="F24" s="26"/>
       <c r="G24" s="124"/>
       <c r="H24" s="125"/>
-      <c r="I24" s="186"/>
-      <c r="J24" s="187"/>
-      <c r="K24" s="211"/>
+      <c r="I24" s="222"/>
+      <c r="J24" s="204"/>
+      <c r="K24" s="193"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="67">
@@ -5682,9 +5685,9 @@
       <c r="F25" s="26"/>
       <c r="G25" s="124"/>
       <c r="H25" s="125"/>
-      <c r="I25" s="186"/>
-      <c r="J25" s="187"/>
-      <c r="K25" s="211"/>
+      <c r="I25" s="222"/>
+      <c r="J25" s="204"/>
+      <c r="K25" s="193"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="67">
@@ -5704,9 +5707,9 @@
       <c r="F26" s="26"/>
       <c r="G26" s="124"/>
       <c r="H26" s="125"/>
-      <c r="I26" s="186"/>
-      <c r="J26" s="187"/>
-      <c r="K26" s="211"/>
+      <c r="I26" s="222"/>
+      <c r="J26" s="204"/>
+      <c r="K26" s="193"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="67">
@@ -5726,9 +5729,9 @@
       <c r="F27" s="26"/>
       <c r="G27" s="124"/>
       <c r="H27" s="125"/>
-      <c r="I27" s="186"/>
-      <c r="J27" s="187"/>
-      <c r="K27" s="211"/>
+      <c r="I27" s="222"/>
+      <c r="J27" s="204"/>
+      <c r="K27" s="193"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="67">
@@ -5748,9 +5751,9 @@
       <c r="F28" s="26"/>
       <c r="G28" s="124"/>
       <c r="H28" s="125"/>
-      <c r="I28" s="186"/>
-      <c r="J28" s="187"/>
-      <c r="K28" s="211"/>
+      <c r="I28" s="222"/>
+      <c r="J28" s="204"/>
+      <c r="K28" s="193"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="67">
@@ -5770,9 +5773,9 @@
       <c r="F29" s="26"/>
       <c r="G29" s="124"/>
       <c r="H29" s="125"/>
-      <c r="I29" s="186"/>
-      <c r="J29" s="187"/>
-      <c r="K29" s="211"/>
+      <c r="I29" s="222"/>
+      <c r="J29" s="204"/>
+      <c r="K29" s="193"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="75">
@@ -5792,9 +5795,9 @@
       <c r="F30" s="26"/>
       <c r="G30" s="124"/>
       <c r="H30" s="125"/>
-      <c r="I30" s="186"/>
-      <c r="J30" s="187"/>
-      <c r="K30" s="211"/>
+      <c r="I30" s="222"/>
+      <c r="J30" s="204"/>
+      <c r="K30" s="193"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="67">
@@ -5814,9 +5817,9 @@
       <c r="F31" s="26"/>
       <c r="G31" s="124"/>
       <c r="H31" s="125"/>
-      <c r="I31" s="186"/>
-      <c r="J31" s="187"/>
-      <c r="K31" s="211"/>
+      <c r="I31" s="222"/>
+      <c r="J31" s="204"/>
+      <c r="K31" s="193"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="67">
@@ -5836,9 +5839,9 @@
       <c r="F32" s="26"/>
       <c r="G32" s="124"/>
       <c r="H32" s="125"/>
-      <c r="I32" s="186"/>
-      <c r="J32" s="187"/>
-      <c r="K32" s="211"/>
+      <c r="I32" s="222"/>
+      <c r="J32" s="204"/>
+      <c r="K32" s="193"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="67">
@@ -5858,9 +5861,9 @@
       <c r="F33" s="26"/>
       <c r="G33" s="124"/>
       <c r="H33" s="125"/>
-      <c r="I33" s="186"/>
-      <c r="J33" s="187"/>
-      <c r="K33" s="211"/>
+      <c r="I33" s="222"/>
+      <c r="J33" s="204"/>
+      <c r="K33" s="193"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="67">
@@ -5880,9 +5883,9 @@
       <c r="F34" s="26"/>
       <c r="G34" s="124"/>
       <c r="H34" s="125"/>
-      <c r="I34" s="186"/>
-      <c r="J34" s="187"/>
-      <c r="K34" s="211"/>
+      <c r="I34" s="222"/>
+      <c r="J34" s="204"/>
+      <c r="K34" s="193"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="67">
@@ -5902,9 +5905,9 @@
       <c r="F35" s="26"/>
       <c r="G35" s="124"/>
       <c r="H35" s="125"/>
-      <c r="I35" s="186"/>
-      <c r="J35" s="187"/>
-      <c r="K35" s="211"/>
+      <c r="I35" s="222"/>
+      <c r="J35" s="204"/>
+      <c r="K35" s="193"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="67">
@@ -5924,9 +5927,9 @@
       <c r="F36" s="26"/>
       <c r="G36" s="124"/>
       <c r="H36" s="125"/>
-      <c r="I36" s="186"/>
-      <c r="J36" s="187"/>
-      <c r="K36" s="211"/>
+      <c r="I36" s="222"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="193"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="67">
@@ -5946,9 +5949,9 @@
       <c r="F37" s="26"/>
       <c r="G37" s="124"/>
       <c r="H37" s="125"/>
-      <c r="I37" s="186"/>
-      <c r="J37" s="187"/>
-      <c r="K37" s="211"/>
+      <c r="I37" s="222"/>
+      <c r="J37" s="204"/>
+      <c r="K37" s="193"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="67">
@@ -5968,9 +5971,9 @@
       <c r="F38" s="26"/>
       <c r="G38" s="124"/>
       <c r="H38" s="125"/>
-      <c r="I38" s="186"/>
-      <c r="J38" s="187"/>
-      <c r="K38" s="211"/>
+      <c r="I38" s="222"/>
+      <c r="J38" s="204"/>
+      <c r="K38" s="193"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="76">
@@ -5990,16 +5993,16 @@
       <c r="F39" s="26"/>
       <c r="G39" s="124"/>
       <c r="H39" s="125"/>
-      <c r="I39" s="186"/>
-      <c r="J39" s="187"/>
-      <c r="K39" s="211"/>
+      <c r="I39" s="222"/>
+      <c r="J39" s="204"/>
+      <c r="K39" s="193"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="237" t="s">
+      <c r="A40" s="229" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="238"/>
-      <c r="C40" s="239"/>
+      <c r="B40" s="230"/>
+      <c r="C40" s="231"/>
       <c r="D40" s="126" t="e">
         <f>AVERAGE(D10:D39)</f>
         <v>#DIV/0!</v>
@@ -6020,16 +6023,16 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I40" s="186"/>
-      <c r="J40" s="187"/>
-      <c r="K40" s="211"/>
+      <c r="I40" s="222"/>
+      <c r="J40" s="204"/>
+      <c r="K40" s="193"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="163" t="s">
+      <c r="A41" s="143" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="164"/>
-      <c r="C41" s="165"/>
+      <c r="B41" s="144"/>
+      <c r="C41" s="145"/>
       <c r="D41" s="128">
         <f>MIN(D10:D39)</f>
         <v>0</v>
@@ -6050,16 +6053,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I41" s="186"/>
-      <c r="J41" s="187"/>
-      <c r="K41" s="211"/>
+      <c r="I41" s="222"/>
+      <c r="J41" s="204"/>
+      <c r="K41" s="193"/>
     </row>
     <row r="42" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="229" t="s">
+      <c r="A42" s="235" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="230"/>
-      <c r="C42" s="231"/>
+      <c r="B42" s="236"/>
+      <c r="C42" s="237"/>
       <c r="D42" s="130">
         <f>MAX(D10:D39)</f>
         <v>0</v>
@@ -6080,16 +6083,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I42" s="188"/>
-      <c r="J42" s="195"/>
-      <c r="K42" s="212"/>
+      <c r="I42" s="223"/>
+      <c r="J42" s="206"/>
+      <c r="K42" s="194"/>
     </row>
     <row r="43" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="170"/>
-      <c r="C43" s="170"/>
+      <c r="B43" s="134"/>
+      <c r="C43" s="134"/>
       <c r="D43" s="44" t="s">
         <v>22</v>
       </c>
@@ -6106,8 +6109,8 @@
     </row>
     <row r="44" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="50"/>
-      <c r="B44" s="171"/>
-      <c r="C44" s="171"/>
+      <c r="B44" s="135"/>
+      <c r="C44" s="135"/>
       <c r="D44" s="44"/>
       <c r="F44" s="46"/>
       <c r="G44" s="47"/>
@@ -6116,11 +6119,11 @@
       <c r="J44" s="51"/>
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="169" t="s">
+      <c r="A45" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="169"/>
-      <c r="C45" s="169"/>
+      <c r="B45" s="133"/>
+      <c r="C45" s="133"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="47" t="s">
@@ -6133,11 +6136,11 @@
       <c r="H45" s="44"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="169" t="s">
+      <c r="A46" s="133" t="s">
         <v>134</v>
       </c>
-      <c r="B46" s="169"/>
-      <c r="C46" s="169"/>
+      <c r="B46" s="133"/>
+      <c r="C46" s="133"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="44"/>
@@ -6162,6 +6165,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A7:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="J4:K4"/>
@@ -6178,15 +6190,6 @@
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="A40:C40"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A7:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
   </mergeCells>
   <conditionalFormatting sqref="D10:D42">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="notBetween">
@@ -6233,15 +6236,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="240" t="s">
+      <c r="A1" s="303" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="241"/>
-      <c r="E1" s="241"/>
-      <c r="F1" s="241"/>
-      <c r="G1" s="242"/>
+      <c r="B1" s="304"/>
+      <c r="C1" s="304"/>
+      <c r="D1" s="304"/>
+      <c r="E1" s="304"/>
+      <c r="F1" s="304"/>
+      <c r="G1" s="305"/>
     </row>
     <row r="2" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="87"/>
@@ -6255,37 +6258,37 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="291" t="s">
+      <c r="A3" s="241" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="292"/>
-      <c r="C3" s="292"/>
-      <c r="D3" s="292"/>
-      <c r="E3" s="292"/>
-      <c r="F3" s="292"/>
-      <c r="G3" s="293"/>
+      <c r="B3" s="242"/>
+      <c r="C3" s="242"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="243"/>
     </row>
     <row r="4" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="222" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="187"/>
-      <c r="C4" s="187"/>
-      <c r="D4" s="187"/>
-      <c r="E4" s="187"/>
-      <c r="F4" s="187"/>
-      <c r="G4" s="211"/>
+      <c r="B4" s="204"/>
+      <c r="C4" s="204"/>
+      <c r="D4" s="204"/>
+      <c r="E4" s="204"/>
+      <c r="F4" s="204"/>
+      <c r="G4" s="193"/>
     </row>
     <row r="5" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="243" t="s">
+      <c r="A5" s="306" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="244"/>
-      <c r="C5" s="244"/>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="245"/>
+      <c r="B5" s="307"/>
+      <c r="C5" s="307"/>
+      <c r="D5" s="307"/>
+      <c r="E5" s="307"/>
+      <c r="F5" s="307"/>
+      <c r="G5" s="308"/>
     </row>
     <row r="6" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="90" t="s">
@@ -6297,14 +6300,14 @@
       <c r="C6" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="246" t="s">
+      <c r="D6" s="262" t="s">
         <v>143</v>
       </c>
-      <c r="E6" s="247"/>
-      <c r="F6" s="248" t="s">
+      <c r="E6" s="264"/>
+      <c r="F6" s="283" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="249">
+      <c r="G6" s="287">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
@@ -6317,13 +6320,13 @@
       <c r="C7" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="246">
+      <c r="D7" s="262">
         <f>Page1!F5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="247"/>
-      <c r="F7" s="248"/>
-      <c r="G7" s="250"/>
+      <c r="E7" s="264"/>
+      <c r="F7" s="283"/>
+      <c r="G7" s="309"/>
     </row>
     <row r="8" spans="1:7" s="86" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="90" t="s">
@@ -6336,15 +6339,15 @@
       <c r="C8" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="248">
+      <c r="D8" s="283">
         <f>Page1!H5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="248"/>
-      <c r="F8" s="260" t="s">
+      <c r="E8" s="283"/>
+      <c r="F8" s="284" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="249">
+      <c r="G8" s="287">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
@@ -6357,15 +6360,15 @@
         <f>Page1!G44</f>
         <v>461347000</v>
       </c>
-      <c r="C9" s="260" t="s">
+      <c r="C9" s="284" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="265" t="s">
+      <c r="D9" s="290" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="266"/>
-      <c r="F9" s="261"/>
-      <c r="G9" s="263"/>
+      <c r="E9" s="291"/>
+      <c r="F9" s="285"/>
+      <c r="G9" s="288"/>
     </row>
     <row r="10" spans="1:7" s="86" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="97" t="s">
@@ -6375,34 +6378,34 @@
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="C10" s="262"/>
-      <c r="D10" s="267"/>
-      <c r="E10" s="268"/>
-      <c r="F10" s="262"/>
-      <c r="G10" s="264"/>
+      <c r="C10" s="286"/>
+      <c r="D10" s="292"/>
+      <c r="E10" s="293"/>
+      <c r="F10" s="286"/>
+      <c r="G10" s="289"/>
     </row>
     <row r="11" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="251" t="s">
+      <c r="A11" s="294" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="253" t="s">
+      <c r="B11" s="296" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="255" t="s">
+      <c r="C11" s="298" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="256"/>
-      <c r="E11" s="257"/>
-      <c r="F11" s="253" t="s">
+      <c r="D11" s="299"/>
+      <c r="E11" s="300"/>
+      <c r="F11" s="296" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="258" t="s">
+      <c r="G11" s="301" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="252"/>
-      <c r="B12" s="254"/>
+      <c r="A12" s="295"/>
+      <c r="B12" s="297"/>
       <c r="C12" s="99" t="s">
         <v>63</v>
       </c>
@@ -6412,8 +6415,8 @@
       <c r="E12" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="254"/>
-      <c r="G12" s="259"/>
+      <c r="F12" s="297"/>
+      <c r="G12" s="302"/>
     </row>
     <row r="13" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="100" t="s">
@@ -6483,7 +6486,7 @@
         <f>Page1!K39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="269" t="s">
+      <c r="G15" s="279" t="s">
         <v>74</v>
       </c>
     </row>
@@ -6507,7 +6510,7 @@
         <f>Page2!F41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="227"/>
+      <c r="G16" s="233"/>
     </row>
     <row r="17" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="104" t="s">
@@ -6529,7 +6532,7 @@
         <f>Page1!I39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="227"/>
+      <c r="G17" s="233"/>
     </row>
     <row r="18" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="104" t="s">
@@ -6551,7 +6554,7 @@
         <f>Page2!D41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="227"/>
+      <c r="G18" s="233"/>
     </row>
     <row r="19" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="104" t="s">
@@ -6573,7 +6576,7 @@
         <f>Page1!J39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="227"/>
+      <c r="G19" s="233"/>
     </row>
     <row r="20" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="104" t="s">
@@ -6595,7 +6598,7 @@
         <f>Page2!E41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="227"/>
+      <c r="G20" s="233"/>
     </row>
     <row r="21" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="104" t="s">
@@ -6617,7 +6620,7 @@
         <f>Page1!G39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="227"/>
+      <c r="G21" s="233"/>
     </row>
     <row r="22" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="104" t="s">
@@ -6639,7 +6642,7 @@
         <f>Page1!H39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="137"/>
+      <c r="G22" s="152"/>
     </row>
     <row r="23" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="104" t="s">
@@ -6737,26 +6740,26 @@
       </c>
     </row>
     <row r="27" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="270" t="s">
+      <c r="A27" s="276" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="271"/>
-      <c r="C27" s="271"/>
-      <c r="D27" s="271"/>
-      <c r="E27" s="271"/>
-      <c r="F27" s="271"/>
-      <c r="G27" s="272"/>
+      <c r="B27" s="277"/>
+      <c r="C27" s="277"/>
+      <c r="D27" s="277"/>
+      <c r="E27" s="277"/>
+      <c r="F27" s="277"/>
+      <c r="G27" s="278"/>
     </row>
     <row r="28" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="273" t="s">
+      <c r="A28" s="260" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="274"/>
-      <c r="C28" s="275" t="s">
+      <c r="B28" s="261"/>
+      <c r="C28" s="280" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="276"/>
-      <c r="E28" s="277"/>
+      <c r="D28" s="281"/>
+      <c r="E28" s="282"/>
       <c r="F28" s="113" t="s">
         <v>95</v>
       </c>
@@ -6765,15 +6768,15 @@
       </c>
     </row>
     <row r="29" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="278" t="s">
+      <c r="A29" s="265" t="s">
         <v>97</v>
       </c>
-      <c r="B29" s="247"/>
-      <c r="C29" s="279" t="s">
+      <c r="B29" s="264"/>
+      <c r="C29" s="270" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="280"/>
-      <c r="E29" s="281"/>
+      <c r="D29" s="271"/>
+      <c r="E29" s="272"/>
       <c r="F29" s="80" t="s">
         <v>95</v>
       </c>
@@ -6782,15 +6785,15 @@
       </c>
     </row>
     <row r="30" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="278" t="s">
+      <c r="A30" s="265" t="s">
         <v>100</v>
       </c>
-      <c r="B30" s="247"/>
-      <c r="C30" s="279" t="s">
+      <c r="B30" s="264"/>
+      <c r="C30" s="270" t="s">
         <v>101</v>
       </c>
-      <c r="D30" s="280"/>
-      <c r="E30" s="281"/>
+      <c r="D30" s="271"/>
+      <c r="E30" s="272"/>
       <c r="F30" s="80" t="s">
         <v>95</v>
       </c>
@@ -6799,15 +6802,15 @@
       </c>
     </row>
     <row r="31" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="278" t="s">
+      <c r="A31" s="265" t="s">
         <v>102</v>
       </c>
-      <c r="B31" s="247"/>
-      <c r="C31" s="279" t="s">
+      <c r="B31" s="264"/>
+      <c r="C31" s="270" t="s">
         <v>103</v>
       </c>
-      <c r="D31" s="280"/>
-      <c r="E31" s="281"/>
+      <c r="D31" s="271"/>
+      <c r="E31" s="272"/>
       <c r="F31" s="80" t="s">
         <v>95</v>
       </c>
@@ -6816,15 +6819,15 @@
       </c>
     </row>
     <row r="32" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="278" t="s">
+      <c r="A32" s="265" t="s">
         <v>105</v>
       </c>
-      <c r="B32" s="247"/>
-      <c r="C32" s="279" t="s">
+      <c r="B32" s="264"/>
+      <c r="C32" s="270" t="s">
         <v>106</v>
       </c>
-      <c r="D32" s="280"/>
-      <c r="E32" s="281"/>
+      <c r="D32" s="271"/>
+      <c r="E32" s="272"/>
       <c r="F32" s="80" t="s">
         <v>95</v>
       </c>
@@ -6833,15 +6836,15 @@
       </c>
     </row>
     <row r="33" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="278" t="s">
+      <c r="A33" s="265" t="s">
         <v>107</v>
       </c>
-      <c r="B33" s="247"/>
-      <c r="C33" s="279" t="s">
+      <c r="B33" s="264"/>
+      <c r="C33" s="270" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="280"/>
-      <c r="E33" s="281"/>
+      <c r="D33" s="271"/>
+      <c r="E33" s="272"/>
       <c r="F33" s="80" t="s">
         <v>95</v>
       </c>
@@ -6850,15 +6853,15 @@
       </c>
     </row>
     <row r="34" spans="1:7" s="86" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="147" t="s">
+      <c r="A34" s="162" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="148"/>
-      <c r="C34" s="282" t="s">
+      <c r="B34" s="163"/>
+      <c r="C34" s="273" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="283"/>
-      <c r="E34" s="284"/>
+      <c r="D34" s="274"/>
+      <c r="E34" s="275"/>
       <c r="F34" s="114" t="s">
         <v>95</v>
       </c>
@@ -6867,26 +6870,26 @@
       </c>
     </row>
     <row r="35" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="270" t="s">
+      <c r="A35" s="276" t="s">
         <v>112</v>
       </c>
-      <c r="B35" s="271"/>
-      <c r="C35" s="271"/>
-      <c r="D35" s="271"/>
-      <c r="E35" s="271"/>
-      <c r="F35" s="271"/>
-      <c r="G35" s="272"/>
+      <c r="B35" s="277"/>
+      <c r="C35" s="277"/>
+      <c r="D35" s="277"/>
+      <c r="E35" s="277"/>
+      <c r="F35" s="277"/>
+      <c r="G35" s="278"/>
     </row>
     <row r="36" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="143" t="s">
+      <c r="A36" s="158" t="s">
         <v>113</v>
       </c>
-      <c r="B36" s="144"/>
-      <c r="C36" s="288" t="s">
+      <c r="B36" s="159"/>
+      <c r="C36" s="268" t="s">
         <v>101</v>
       </c>
-      <c r="D36" s="289"/>
-      <c r="E36" s="144"/>
+      <c r="D36" s="269"/>
+      <c r="E36" s="159"/>
       <c r="F36" s="10" t="s">
         <v>95</v>
       </c>
@@ -6895,15 +6898,15 @@
       </c>
     </row>
     <row r="37" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="273" t="s">
+      <c r="A37" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="B37" s="274"/>
-      <c r="C37" s="246" t="s">
+      <c r="B37" s="261"/>
+      <c r="C37" s="262" t="s">
         <v>115</v>
       </c>
-      <c r="D37" s="285"/>
-      <c r="E37" s="247"/>
+      <c r="D37" s="263"/>
+      <c r="E37" s="264"/>
       <c r="F37" s="106" t="s">
         <v>95</v>
       </c>
@@ -6912,15 +6915,15 @@
       </c>
     </row>
     <row r="38" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="278" t="s">
+      <c r="A38" s="265" t="s">
         <v>116</v>
       </c>
-      <c r="B38" s="247"/>
-      <c r="C38" s="246" t="s">
+      <c r="B38" s="264"/>
+      <c r="C38" s="262" t="s">
         <v>117</v>
       </c>
-      <c r="D38" s="285"/>
-      <c r="E38" s="247"/>
+      <c r="D38" s="263"/>
+      <c r="E38" s="264"/>
       <c r="F38" s="106" t="s">
         <v>95</v>
       </c>
@@ -6929,15 +6932,15 @@
       </c>
     </row>
     <row r="39" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="147" t="s">
+      <c r="A39" s="162" t="s">
         <v>118</v>
       </c>
-      <c r="B39" s="148"/>
-      <c r="C39" s="286" t="s">
+      <c r="B39" s="163"/>
+      <c r="C39" s="266" t="s">
         <v>119</v>
       </c>
-      <c r="D39" s="287"/>
-      <c r="E39" s="148"/>
+      <c r="D39" s="267"/>
+      <c r="E39" s="163"/>
       <c r="F39" s="1" t="s">
         <v>95</v>
       </c>
@@ -6946,50 +6949,50 @@
       </c>
     </row>
     <row r="40" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="294" t="s">
+      <c r="A40" s="244" t="s">
         <v>120</v>
       </c>
-      <c r="B40" s="295"/>
-      <c r="C40" s="296" t="s">
+      <c r="B40" s="245"/>
+      <c r="C40" s="246" t="s">
         <v>137</v>
       </c>
-      <c r="D40" s="297"/>
-      <c r="E40" s="298"/>
-      <c r="F40" s="296" t="s">
+      <c r="D40" s="247"/>
+      <c r="E40" s="248"/>
+      <c r="F40" s="246" t="s">
         <v>138</v>
       </c>
-      <c r="G40" s="298"/>
+      <c r="G40" s="248"/>
     </row>
     <row r="41" spans="1:7" s="86" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="299"/>
-      <c r="B41" s="300"/>
-      <c r="C41" s="186"/>
-      <c r="D41" s="187"/>
-      <c r="E41" s="211"/>
-      <c r="F41" s="303"/>
-      <c r="G41" s="304"/>
+      <c r="A41" s="249"/>
+      <c r="B41" s="250"/>
+      <c r="C41" s="222"/>
+      <c r="D41" s="204"/>
+      <c r="E41" s="193"/>
+      <c r="F41" s="253"/>
+      <c r="G41" s="254"/>
     </row>
     <row r="42" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="301"/>
-      <c r="B42" s="302"/>
-      <c r="C42" s="305" t="s">
+      <c r="A42" s="251"/>
+      <c r="B42" s="252"/>
+      <c r="C42" s="255" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="306"/>
-      <c r="E42" s="307"/>
-      <c r="F42" s="305" t="s">
+      <c r="D42" s="256"/>
+      <c r="E42" s="257"/>
+      <c r="F42" s="255" t="s">
         <v>139</v>
       </c>
-      <c r="G42" s="307"/>
+      <c r="G42" s="257"/>
     </row>
     <row r="43" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="115"/>
       <c r="B43" s="115"/>
       <c r="C43" s="115"/>
       <c r="D43" s="115"/>
-      <c r="E43" s="308"/>
-      <c r="F43" s="308"/>
-      <c r="G43" s="308"/>
+      <c r="E43" s="258"/>
+      <c r="F43" s="258"/>
+      <c r="G43" s="258"/>
     </row>
     <row r="44" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="46" t="s">
@@ -6998,25 +7001,64 @@
       <c r="B44" s="116"/>
       <c r="C44" s="117"/>
       <c r="D44" s="115"/>
-      <c r="E44" s="309"/>
-      <c r="F44" s="309"/>
-      <c r="G44" s="309"/>
+      <c r="E44" s="259"/>
+      <c r="F44" s="259"/>
+      <c r="G44" s="259"/>
     </row>
     <row r="45" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="290" t="s">
+      <c r="A46" s="240" t="s">
         <v>122</v>
       </c>
-      <c r="B46" s="290"/>
+      <c r="B46" s="240"/>
     </row>
     <row r="47" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="290" t="s">
+      <c r="A47" s="240" t="s">
         <v>123</v>
       </c>
-      <c r="B47" s="290"/>
+      <c r="B47" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="G15:G22"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:E36"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A3:G3"/>
@@ -7033,45 +7075,6 @@
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="G15:G22"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="D7:E7"/>
   </mergeCells>
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.78740157480314965" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="84" orientation="portrait" r:id="rId1"/>

--- a/backend/templates/UC-18gsm-290NP-ABQR.xlsx
+++ b/backend/templates/UC-18gsm-290NP-ABQR.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866E2096-4EC3-4B14-AC66-203BD360FFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6D00F0-BB63-4202-B7D4-3A4170F5A11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="142">
   <si>
     <t>Sample No.</t>
   </si>
@@ -512,12 +512,6 @@
   </si>
   <si>
     <t>Swanson Plastics(India) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>290</t>
-  </si>
-  <si>
-    <t>293</t>
   </si>
   <si>
     <t>#02</t>
@@ -1435,7 +1429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="310">
+  <cellXfs count="311">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1858,6 +1852,123 @@
     <xf numFmtId="2" fontId="1" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1867,166 +1978,133 @@
     <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2047,108 +2125,51 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2169,29 +2190,155 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2252,273 +2399,1450 @@
     </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+  <dxfs count="160">
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -3048,35 +4372,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="157" t="s">
+      <c r="A2" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3097,12 +4421,12 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="158" t="s">
+      <c r="A4" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="159"/>
-      <c r="C4" s="160"/>
-      <c r="D4" s="161"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="147"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -3114,19 +4438,19 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="153"/>
-      <c r="K4" s="154"/>
+      <c r="J4" s="139"/>
+      <c r="K4" s="140"/>
       <c r="M4" s="45" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="163"/>
-      <c r="C5" s="164"/>
-      <c r="D5" s="165"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="150"/>
+      <c r="D5" s="151"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -3138,28 +4462,28 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="155"/>
-      <c r="K5" s="156"/>
+      <c r="J5" s="141"/>
+      <c r="K5" s="142"/>
     </row>
     <row r="6" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="169" t="s">
+      <c r="A6" s="156" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="170"/>
-      <c r="C6" s="171"/>
+      <c r="B6" s="157"/>
+      <c r="C6" s="158"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="G6" s="149"/>
-      <c r="H6" s="168"/>
-      <c r="I6" s="149"/>
-      <c r="J6" s="150"/>
-      <c r="K6" s="151"/>
+      <c r="G6" s="134"/>
+      <c r="H6" s="155"/>
+      <c r="I6" s="134"/>
+      <c r="J6" s="135"/>
+      <c r="K6" s="136"/>
     </row>
     <row r="7" spans="1:13" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="136" t="s">
+      <c r="A7" s="159" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="137"/>
@@ -3173,29 +4497,29 @@
       <c r="F7" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="166" t="s">
+      <c r="G7" s="152" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="166" t="s">
+      <c r="H7" s="152" t="s">
         <v>41</v>
       </c>
       <c r="I7" s="137" t="s">
         <v>1</v>
       </c>
       <c r="J7" s="137"/>
-      <c r="K7" s="152"/>
+      <c r="K7" s="138"/>
     </row>
     <row r="8" spans="1:13" s="5" customFormat="1" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="138"/>
-      <c r="B8" s="139"/>
-      <c r="C8" s="139"/>
-      <c r="D8" s="139"/>
-      <c r="E8" s="139" t="s">
+      <c r="A8" s="160"/>
+      <c r="B8" s="154"/>
+      <c r="C8" s="154"/>
+      <c r="D8" s="154"/>
+      <c r="E8" s="154" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="139"/>
-      <c r="G8" s="167"/>
-      <c r="H8" s="167"/>
+      <c r="F8" s="154"/>
+      <c r="G8" s="153"/>
+      <c r="H8" s="153"/>
       <c r="I8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3597,11 +4921,11 @@
       <c r="K38" s="28"/>
     </row>
     <row r="39" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="146" t="s">
+      <c r="A39" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="147"/>
-      <c r="C39" s="148"/>
+      <c r="B39" s="168"/>
+      <c r="C39" s="169"/>
       <c r="D39" s="35" t="e">
         <f>AVERAGE(D9:D38)</f>
         <v>#DIV/0!</v>
@@ -3636,11 +4960,11 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="143" t="s">
+      <c r="A40" s="164" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="144"/>
-      <c r="C40" s="145"/>
+      <c r="B40" s="165"/>
+      <c r="C40" s="166"/>
       <c r="D40" s="38">
         <f>MIN(D9:D38)</f>
         <v>0</v>
@@ -3675,11 +4999,11 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="140" t="s">
+      <c r="A41" s="161" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="141"/>
-      <c r="C41" s="142"/>
+      <c r="B41" s="162"/>
+      <c r="C41" s="163"/>
       <c r="D41" s="41">
         <f>MAX(D9:D38)</f>
         <v>0</v>
@@ -3720,8 +5044,8 @@
       <c r="A42" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="134"/>
-      <c r="C42" s="134"/>
+      <c r="B42" s="171"/>
+      <c r="C42" s="171"/>
       <c r="D42" s="44" t="s">
         <v>22</v>
       </c>
@@ -3738,8 +5062,8 @@
     </row>
     <row r="43" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="50"/>
-      <c r="B43" s="135"/>
-      <c r="C43" s="135"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="44"/>
       <c r="F43" s="46"/>
       <c r="G43" s="47"/>
@@ -3748,11 +5072,11 @@
       <c r="J43" s="51"/>
     </row>
     <row r="44" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="133" t="s">
+      <c r="A44" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="133"/>
-      <c r="C44" s="133"/>
+      <c r="B44" s="170"/>
+      <c r="C44" s="170"/>
       <c r="D44" s="44"/>
       <c r="E44" s="44"/>
       <c r="F44" s="47" t="s">
@@ -3764,11 +5088,11 @@
       <c r="H44" s="44"/>
     </row>
     <row r="45" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="133" t="s">
+      <c r="A45" s="170" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="133"/>
-      <c r="C45" s="133"/>
+      <c r="B45" s="170"/>
+      <c r="C45" s="170"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="44"/>
@@ -3779,9 +5103,9 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="133"/>
-      <c r="B46" s="133"/>
-      <c r="C46" s="133"/>
+      <c r="A46" s="170"/>
+      <c r="B46" s="170"/>
+      <c r="C46" s="170"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="44"/>
@@ -3810,6 +5134,16 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="26">
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A39:C39"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="J4:K4"/>
@@ -3826,76 +5160,50 @@
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A45:C45"/>
   </mergeCells>
   <conditionalFormatting sqref="D9:D41">
-    <cfRule type="cellIs" dxfId="24" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="87" priority="13" operator="notBetween">
+      <formula>17</formula>
       <formula>20</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="14" operator="lessThan">
-      <formula>17</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E41">
-    <cfRule type="cellIs" dxfId="22" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="86" priority="11" operator="notBetween">
+      <formula>18</formula>
       <formula>28</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="12" operator="lessThan">
-      <formula>18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F41">
-    <cfRule type="cellIs" dxfId="20" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="85" priority="9" operator="notBetween">
+      <formula>360</formula>
       <formula>400</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="10" operator="lessThan">
-      <formula>360</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:G41">
-    <cfRule type="cellIs" dxfId="18" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="84" priority="7" operator="notBetween">
+      <formula>0.3</formula>
       <formula>0.6</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="8" operator="lessThan">
-      <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H38">
-    <cfRule type="cellIs" dxfId="16" priority="1" stopIfTrue="1" operator="notBetween">
-      <formula>0.6</formula>
-      <formula>1.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
-    <cfRule type="cellIs" priority="2" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="83" priority="1" stopIfTrue="1" operator="notBetween">
       <formula>0.6</formula>
       <formula>1.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I41">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="82" priority="5" operator="notBetween">
+      <formula>900</formula>
       <formula>1200</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="lessThan">
-      <formula>900</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J41">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="81" priority="4" operator="lessThan">
       <formula>350</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K41">
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="3" operator="lessThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3918,35 +5226,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="157" t="s">
+      <c r="A2" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3967,18 +5275,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="158" t="s">
+      <c r="A4" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="159">
+      <c r="B4" s="145">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="184">
+      <c r="C4" s="220">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="185"/>
+      <c r="D4" s="182"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -3996,25 +5304,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="172">
+      <c r="J4" s="221">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="173"/>
+      <c r="K4" s="222"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="163">
+      <c r="B5" s="149">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="164">
+      <c r="C5" s="150">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="165"/>
+      <c r="D5" s="151"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -4032,104 +5340,104 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="174">
+      <c r="J5" s="223">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="175"/>
+      <c r="K5" s="224"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="211" t="s">
+      <c r="A6" s="173" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="212"/>
-      <c r="C6" s="213"/>
-      <c r="D6" s="214"/>
-      <c r="E6" s="203"/>
-      <c r="F6" s="198"/>
-      <c r="G6" s="197"/>
-      <c r="H6" s="198"/>
-      <c r="I6" s="199"/>
-      <c r="J6" s="200"/>
+      <c r="B6" s="174"/>
+      <c r="C6" s="175"/>
+      <c r="D6" s="176"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="178"/>
+      <c r="G6" s="193"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="207"/>
+      <c r="J6" s="208"/>
       <c r="K6" s="56"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="214" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="203"/>
-      <c r="C7" s="203"/>
-      <c r="D7" s="217" t="s">
+      <c r="A7" s="176" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="177"/>
+      <c r="C7" s="177"/>
+      <c r="D7" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="203"/>
-      <c r="F7" s="185"/>
-      <c r="G7" s="197" t="s">
+      <c r="E7" s="177"/>
+      <c r="F7" s="182"/>
+      <c r="G7" s="193" t="s">
         <v>126</v>
       </c>
-      <c r="H7" s="203"/>
-      <c r="I7" s="197" t="s">
+      <c r="H7" s="177"/>
+      <c r="I7" s="193" t="s">
         <v>135</v>
       </c>
-      <c r="J7" s="198"/>
-      <c r="K7" s="192" t="s">
+      <c r="J7" s="178"/>
+      <c r="K7" s="211" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="222"/>
-      <c r="B8" s="204"/>
-      <c r="C8" s="204"/>
-      <c r="D8" s="222" t="s">
+      <c r="A8" s="187"/>
+      <c r="B8" s="188"/>
+      <c r="C8" s="188"/>
+      <c r="D8" s="187" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="224" t="s">
+      <c r="E8" s="190" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="181" t="s">
+      <c r="F8" s="191" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="180"/>
-      <c r="H8" s="204"/>
-      <c r="I8" s="180" t="s">
+      <c r="G8" s="194"/>
+      <c r="H8" s="188"/>
+      <c r="I8" s="194" t="s">
         <v>136</v>
       </c>
-      <c r="J8" s="181"/>
-      <c r="K8" s="193"/>
+      <c r="J8" s="191"/>
+      <c r="K8" s="212"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="222"/>
-      <c r="B9" s="204"/>
-      <c r="C9" s="204"/>
-      <c r="D9" s="222"/>
-      <c r="E9" s="166"/>
-      <c r="F9" s="181"/>
-      <c r="G9" s="180"/>
-      <c r="H9" s="204"/>
+      <c r="A9" s="187"/>
+      <c r="B9" s="188"/>
+      <c r="C9" s="188"/>
+      <c r="D9" s="187"/>
+      <c r="E9" s="152"/>
+      <c r="F9" s="191"/>
+      <c r="G9" s="194"/>
+      <c r="H9" s="188"/>
       <c r="I9" s="58" t="s">
         <v>42</v>
       </c>
       <c r="J9" s="59">
         <v>290</v>
       </c>
-      <c r="K9" s="193"/>
+      <c r="K9" s="212"/>
     </row>
     <row r="10" spans="1:11" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="222"/>
-      <c r="B10" s="204"/>
-      <c r="C10" s="204"/>
-      <c r="D10" s="223"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="225"/>
-      <c r="G10" s="205"/>
-      <c r="H10" s="206"/>
+      <c r="A10" s="187"/>
+      <c r="B10" s="188"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="189"/>
+      <c r="E10" s="153"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="195"/>
+      <c r="H10" s="196"/>
       <c r="I10" s="60" t="s">
         <v>43</v>
       </c>
       <c r="J10" s="61">
         <v>293</v>
       </c>
-      <c r="K10" s="194"/>
+      <c r="K10" s="213"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="62">
@@ -4147,10 +5455,10 @@
       <c r="D11" s="65"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
-      <c r="G11" s="209"/>
-      <c r="H11" s="209"/>
-      <c r="I11" s="178"/>
-      <c r="J11" s="179"/>
+      <c r="G11" s="199"/>
+      <c r="H11" s="199"/>
+      <c r="I11" s="225"/>
+      <c r="J11" s="226"/>
       <c r="K11" s="66"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4169,10 +5477,10 @@
       <c r="D12" s="70"/>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
-      <c r="G12" s="210"/>
-      <c r="H12" s="210"/>
-      <c r="I12" s="176"/>
-      <c r="J12" s="177"/>
+      <c r="G12" s="200"/>
+      <c r="H12" s="200"/>
+      <c r="I12" s="205"/>
+      <c r="J12" s="206"/>
       <c r="K12" s="71"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4191,10 +5499,10 @@
       <c r="D13" s="70"/>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
-      <c r="G13" s="210"/>
-      <c r="H13" s="210"/>
-      <c r="I13" s="176"/>
-      <c r="J13" s="177"/>
+      <c r="G13" s="200"/>
+      <c r="H13" s="200"/>
+      <c r="I13" s="205"/>
+      <c r="J13" s="206"/>
       <c r="K13" s="71"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4213,10 +5521,10 @@
       <c r="D14" s="70"/>
       <c r="E14" s="25"/>
       <c r="F14" s="25"/>
-      <c r="G14" s="210"/>
-      <c r="H14" s="210"/>
-      <c r="I14" s="176"/>
-      <c r="J14" s="177"/>
+      <c r="G14" s="200"/>
+      <c r="H14" s="200"/>
+      <c r="I14" s="205"/>
+      <c r="J14" s="206"/>
       <c r="K14" s="71"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4235,10 +5543,10 @@
       <c r="D15" s="70"/>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
-      <c r="G15" s="210"/>
-      <c r="H15" s="210"/>
-      <c r="I15" s="176"/>
-      <c r="J15" s="177"/>
+      <c r="G15" s="200"/>
+      <c r="H15" s="200"/>
+      <c r="I15" s="205"/>
+      <c r="J15" s="206"/>
       <c r="K15" s="71"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4257,10 +5565,10 @@
       <c r="D16" s="65"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
-      <c r="G16" s="209"/>
-      <c r="H16" s="209"/>
-      <c r="I16" s="176"/>
-      <c r="J16" s="177"/>
+      <c r="G16" s="199"/>
+      <c r="H16" s="199"/>
+      <c r="I16" s="205"/>
+      <c r="J16" s="206"/>
       <c r="K16" s="66"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4279,10 +5587,10 @@
       <c r="D17" s="70"/>
       <c r="E17" s="25"/>
       <c r="F17" s="25"/>
-      <c r="G17" s="210"/>
-      <c r="H17" s="210"/>
-      <c r="I17" s="176"/>
-      <c r="J17" s="177"/>
+      <c r="G17" s="200"/>
+      <c r="H17" s="200"/>
+      <c r="I17" s="205"/>
+      <c r="J17" s="206"/>
       <c r="K17" s="71"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4301,10 +5609,10 @@
       <c r="D18" s="70"/>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
-      <c r="G18" s="210"/>
-      <c r="H18" s="210"/>
-      <c r="I18" s="176"/>
-      <c r="J18" s="177"/>
+      <c r="G18" s="200"/>
+      <c r="H18" s="200"/>
+      <c r="I18" s="205"/>
+      <c r="J18" s="206"/>
       <c r="K18" s="71"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4323,10 +5631,10 @@
       <c r="D19" s="70"/>
       <c r="E19" s="25"/>
       <c r="F19" s="25"/>
-      <c r="G19" s="210"/>
-      <c r="H19" s="210"/>
-      <c r="I19" s="176"/>
-      <c r="J19" s="177"/>
+      <c r="G19" s="200"/>
+      <c r="H19" s="200"/>
+      <c r="I19" s="205"/>
+      <c r="J19" s="206"/>
       <c r="K19" s="71"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4345,10 +5653,10 @@
       <c r="D20" s="70"/>
       <c r="E20" s="25"/>
       <c r="F20" s="25"/>
-      <c r="G20" s="182"/>
-      <c r="H20" s="183"/>
-      <c r="I20" s="176"/>
-      <c r="J20" s="177"/>
+      <c r="G20" s="201"/>
+      <c r="H20" s="202"/>
+      <c r="I20" s="205"/>
+      <c r="J20" s="206"/>
       <c r="K20" s="71"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4367,10 +5675,10 @@
       <c r="D21" s="70"/>
       <c r="E21" s="25"/>
       <c r="F21" s="25"/>
-      <c r="G21" s="182"/>
-      <c r="H21" s="183"/>
-      <c r="I21" s="176"/>
-      <c r="J21" s="177"/>
+      <c r="G21" s="201"/>
+      <c r="H21" s="202"/>
+      <c r="I21" s="205"/>
+      <c r="J21" s="206"/>
       <c r="K21" s="71"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4389,10 +5697,10 @@
       <c r="D22" s="70"/>
       <c r="E22" s="25"/>
       <c r="F22" s="25"/>
-      <c r="G22" s="182"/>
-      <c r="H22" s="183"/>
-      <c r="I22" s="176"/>
-      <c r="J22" s="177"/>
+      <c r="G22" s="201"/>
+      <c r="H22" s="202"/>
+      <c r="I22" s="205"/>
+      <c r="J22" s="206"/>
       <c r="K22" s="71"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4411,10 +5719,10 @@
       <c r="D23" s="70"/>
       <c r="E23" s="25"/>
       <c r="F23" s="25"/>
-      <c r="G23" s="182"/>
-      <c r="H23" s="183"/>
-      <c r="I23" s="176"/>
-      <c r="J23" s="177"/>
+      <c r="G23" s="201"/>
+      <c r="H23" s="202"/>
+      <c r="I23" s="205"/>
+      <c r="J23" s="206"/>
       <c r="K23" s="71"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4433,10 +5741,10 @@
       <c r="D24" s="70"/>
       <c r="E24" s="25"/>
       <c r="F24" s="25"/>
-      <c r="G24" s="182"/>
-      <c r="H24" s="183"/>
-      <c r="I24" s="176"/>
-      <c r="J24" s="177"/>
+      <c r="G24" s="201"/>
+      <c r="H24" s="202"/>
+      <c r="I24" s="205"/>
+      <c r="J24" s="206"/>
       <c r="K24" s="71"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4455,10 +5763,10 @@
       <c r="D25" s="70"/>
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
-      <c r="G25" s="182"/>
-      <c r="H25" s="183"/>
-      <c r="I25" s="176"/>
-      <c r="J25" s="177"/>
+      <c r="G25" s="201"/>
+      <c r="H25" s="202"/>
+      <c r="I25" s="205"/>
+      <c r="J25" s="206"/>
       <c r="K25" s="71"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4477,10 +5785,10 @@
       <c r="D26" s="70"/>
       <c r="E26" s="25"/>
       <c r="F26" s="25"/>
-      <c r="G26" s="182"/>
-      <c r="H26" s="183"/>
-      <c r="I26" s="176"/>
-      <c r="J26" s="177"/>
+      <c r="G26" s="201"/>
+      <c r="H26" s="202"/>
+      <c r="I26" s="205"/>
+      <c r="J26" s="206"/>
       <c r="K26" s="71"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4499,10 +5807,10 @@
       <c r="D27" s="70"/>
       <c r="E27" s="25"/>
       <c r="F27" s="25"/>
-      <c r="G27" s="182"/>
-      <c r="H27" s="183"/>
-      <c r="I27" s="176"/>
-      <c r="J27" s="177"/>
+      <c r="G27" s="201"/>
+      <c r="H27" s="202"/>
+      <c r="I27" s="205"/>
+      <c r="J27" s="206"/>
       <c r="K27" s="71"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4521,10 +5829,10 @@
       <c r="D28" s="70"/>
       <c r="E28" s="25"/>
       <c r="F28" s="25"/>
-      <c r="G28" s="182"/>
-      <c r="H28" s="183"/>
-      <c r="I28" s="176"/>
-      <c r="J28" s="177"/>
+      <c r="G28" s="201"/>
+      <c r="H28" s="202"/>
+      <c r="I28" s="205"/>
+      <c r="J28" s="206"/>
       <c r="K28" s="71"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4543,10 +5851,10 @@
       <c r="D29" s="70"/>
       <c r="E29" s="25"/>
       <c r="F29" s="25"/>
-      <c r="G29" s="182"/>
-      <c r="H29" s="183"/>
-      <c r="I29" s="176"/>
-      <c r="J29" s="177"/>
+      <c r="G29" s="201"/>
+      <c r="H29" s="202"/>
+      <c r="I29" s="205"/>
+      <c r="J29" s="206"/>
       <c r="K29" s="71"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4565,10 +5873,10 @@
       <c r="D30" s="70"/>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
-      <c r="G30" s="182"/>
-      <c r="H30" s="183"/>
-      <c r="I30" s="176"/>
-      <c r="J30" s="177"/>
+      <c r="G30" s="201"/>
+      <c r="H30" s="202"/>
+      <c r="I30" s="205"/>
+      <c r="J30" s="206"/>
       <c r="K30" s="71"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4587,10 +5895,10 @@
       <c r="D31" s="70"/>
       <c r="E31" s="25"/>
       <c r="F31" s="25"/>
-      <c r="G31" s="182"/>
-      <c r="H31" s="183"/>
-      <c r="I31" s="176"/>
-      <c r="J31" s="177"/>
+      <c r="G31" s="201"/>
+      <c r="H31" s="202"/>
+      <c r="I31" s="205"/>
+      <c r="J31" s="206"/>
       <c r="K31" s="71"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4609,10 +5917,10 @@
       <c r="D32" s="70"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
-      <c r="G32" s="182"/>
-      <c r="H32" s="183"/>
-      <c r="I32" s="176"/>
-      <c r="J32" s="177"/>
+      <c r="G32" s="201"/>
+      <c r="H32" s="202"/>
+      <c r="I32" s="205"/>
+      <c r="J32" s="206"/>
       <c r="K32" s="71"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4631,10 +5939,10 @@
       <c r="D33" s="70"/>
       <c r="E33" s="25"/>
       <c r="F33" s="25"/>
-      <c r="G33" s="182"/>
-      <c r="H33" s="183"/>
-      <c r="I33" s="176"/>
-      <c r="J33" s="177"/>
+      <c r="G33" s="201"/>
+      <c r="H33" s="202"/>
+      <c r="I33" s="205"/>
+      <c r="J33" s="206"/>
       <c r="K33" s="71"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4653,10 +5961,10 @@
       <c r="D34" s="70"/>
       <c r="E34" s="25"/>
       <c r="F34" s="25"/>
-      <c r="G34" s="182"/>
-      <c r="H34" s="183"/>
-      <c r="I34" s="176"/>
-      <c r="J34" s="177"/>
+      <c r="G34" s="201"/>
+      <c r="H34" s="202"/>
+      <c r="I34" s="205"/>
+      <c r="J34" s="206"/>
       <c r="K34" s="71"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4675,10 +5983,10 @@
       <c r="D35" s="70"/>
       <c r="E35" s="25"/>
       <c r="F35" s="25"/>
-      <c r="G35" s="182"/>
-      <c r="H35" s="183"/>
-      <c r="I35" s="176"/>
-      <c r="J35" s="177"/>
+      <c r="G35" s="201"/>
+      <c r="H35" s="202"/>
+      <c r="I35" s="205"/>
+      <c r="J35" s="206"/>
       <c r="K35" s="71"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4697,10 +6005,10 @@
       <c r="D36" s="70"/>
       <c r="E36" s="25"/>
       <c r="F36" s="25"/>
-      <c r="G36" s="182"/>
-      <c r="H36" s="183"/>
-      <c r="I36" s="176"/>
-      <c r="J36" s="177"/>
+      <c r="G36" s="201"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="205"/>
+      <c r="J36" s="206"/>
       <c r="K36" s="71"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4719,10 +6027,10 @@
       <c r="D37" s="70"/>
       <c r="E37" s="25"/>
       <c r="F37" s="25"/>
-      <c r="G37" s="182"/>
-      <c r="H37" s="183"/>
-      <c r="I37" s="176"/>
-      <c r="J37" s="177"/>
+      <c r="G37" s="201"/>
+      <c r="H37" s="202"/>
+      <c r="I37" s="205"/>
+      <c r="J37" s="206"/>
       <c r="K37" s="71"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4741,10 +6049,10 @@
       <c r="D38" s="70"/>
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
-      <c r="G38" s="182"/>
-      <c r="H38" s="183"/>
-      <c r="I38" s="176"/>
-      <c r="J38" s="177"/>
+      <c r="G38" s="201"/>
+      <c r="H38" s="202"/>
+      <c r="I38" s="205"/>
+      <c r="J38" s="206"/>
       <c r="K38" s="71"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4763,10 +6071,10 @@
       <c r="D39" s="70"/>
       <c r="E39" s="25"/>
       <c r="F39" s="25"/>
-      <c r="G39" s="182"/>
-      <c r="H39" s="183"/>
-      <c r="I39" s="176"/>
-      <c r="J39" s="177"/>
+      <c r="G39" s="201"/>
+      <c r="H39" s="202"/>
+      <c r="I39" s="205"/>
+      <c r="J39" s="206"/>
       <c r="K39" s="71"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4785,18 +6093,18 @@
       <c r="D40" s="70"/>
       <c r="E40" s="25"/>
       <c r="F40" s="25"/>
-      <c r="G40" s="210"/>
-      <c r="H40" s="210"/>
-      <c r="I40" s="176"/>
-      <c r="J40" s="177"/>
+      <c r="G40" s="200"/>
+      <c r="H40" s="200"/>
+      <c r="I40" s="205"/>
+      <c r="J40" s="206"/>
       <c r="K40" s="71"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="218" t="s">
+      <c r="A41" s="183" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="219"/>
-      <c r="C41" s="219"/>
+      <c r="B41" s="184"/>
+      <c r="C41" s="184"/>
       <c r="D41" s="79" t="e">
         <f>AVERAGE(D11:D40)</f>
         <v>#DIV/0!</v>
@@ -4809,27 +6117,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G41" s="207" t="e">
+      <c r="G41" s="197" t="e">
         <f>AVERAGE(G11:H40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="208"/>
-      <c r="I41" s="201" t="e">
+      <c r="H41" s="198"/>
+      <c r="I41" s="209" t="e">
         <f>AVERAGE(I11:J40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="202"/>
+      <c r="J41" s="210"/>
       <c r="K41" s="37" t="e">
         <f>AVERAGE(K11:K40)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="220" t="s">
+      <c r="A42" s="185" t="s">
         <v>31</v>
       </c>
-      <c r="B42" s="221"/>
-      <c r="C42" s="221"/>
+      <c r="B42" s="186"/>
+      <c r="C42" s="186"/>
       <c r="D42" s="80">
         <f>MIN(D11:D40)</f>
         <v>0</v>
@@ -4842,27 +6150,27 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G42" s="190">
+      <c r="G42" s="218">
         <f>MIN(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="191"/>
-      <c r="I42" s="195">
+      <c r="H42" s="219"/>
+      <c r="I42" s="203">
         <f>MIN(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="196"/>
+      <c r="J42" s="204"/>
       <c r="K42" s="40">
         <f>MIN(K11:K40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="215" t="s">
+      <c r="A43" s="179" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="216"/>
-      <c r="C43" s="216"/>
+      <c r="B43" s="180"/>
+      <c r="C43" s="180"/>
       <c r="D43" s="81">
         <f>MAX(D11:D40)</f>
         <v>0</v>
@@ -4875,16 +6183,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G43" s="188">
+      <c r="G43" s="216">
         <f>MAX(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="189"/>
-      <c r="I43" s="186">
+      <c r="H43" s="217"/>
+      <c r="I43" s="214">
         <f>MAX(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="187"/>
+      <c r="J43" s="215"/>
       <c r="K43" s="83">
         <f>MAX(K11:K40)</f>
         <v>0</v>
@@ -4894,8 +6202,8 @@
       <c r="A44" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="134"/>
-      <c r="C44" s="134"/>
+      <c r="B44" s="171"/>
+      <c r="C44" s="171"/>
       <c r="D44" s="44" t="s">
         <v>22</v>
       </c>
@@ -4912,8 +6220,8 @@
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="50"/>
-      <c r="B45" s="135"/>
-      <c r="C45" s="135"/>
+      <c r="B45" s="172"/>
+      <c r="C45" s="172"/>
       <c r="D45" s="44"/>
       <c r="F45" s="46"/>
       <c r="G45" s="47"/>
@@ -4922,11 +6230,11 @@
       <c r="J45" s="51"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="133" t="s">
+      <c r="A46" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="133"/>
-      <c r="C46" s="133"/>
+      <c r="B46" s="170"/>
+      <c r="C46" s="170"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="47" t="s">
@@ -4939,11 +6247,11 @@
       <c r="H46" s="44"/>
     </row>
     <row r="47" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="133" t="s">
+      <c r="A47" s="170" t="s">
         <v>134</v>
       </c>
-      <c r="B47" s="133"/>
-      <c r="C47" s="133"/>
+      <c r="B47" s="170"/>
+      <c r="C47" s="170"/>
       <c r="D47" s="44"/>
       <c r="E47" s="44"/>
       <c r="F47" s="44"/>
@@ -4998,19 +6306,71 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A7:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K7:K10"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I33:J33"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="G7:H10"/>
     <mergeCell ref="G41:H41"/>
@@ -5027,105 +6387,53 @@
     <mergeCell ref="G40:H40"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K7:K10"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A7:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="D11:D43">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="8" operator="notBetween">
+      <formula>700</formula>
       <formula>1000</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="lessThan">
-      <formula>700</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11:E43">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="7" operator="lessThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:F43">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="6" operator="lessThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:H19 G20:G39 G40:H43">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="lessThan">
-      <formula>50</formula>
+    <cfRule type="cellIs" dxfId="33" priority="4" operator="notBetween">
+      <formula>45</formula>
+      <formula>55</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:K43">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="notBetween">
+      <formula>410</formula>
       <formula>450</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="lessThan">
-      <formula>410</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:J43">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="notBetween">
+      <formula>290</formula>
+      <formula>293</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.11811023622047245" bottom="0.11811023622047245" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5147,35 +6455,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="157" t="s">
+      <c r="A2" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -5196,18 +6504,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="158" t="s">
+      <c r="A4" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="159">
+      <c r="B4" s="145">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="184">
+      <c r="C4" s="220">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="185"/>
+      <c r="D4" s="182"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -5225,25 +6533,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="172">
+      <c r="J4" s="221">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="173"/>
+      <c r="K4" s="222"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="162" t="s">
+      <c r="A5" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="163">
+      <c r="B5" s="149">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="164">
+      <c r="C5" s="150">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="165"/>
+      <c r="D5" s="151"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -5261,81 +6569,81 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="174">
+      <c r="J5" s="223">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="175"/>
+      <c r="K5" s="224"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="169" t="s">
+      <c r="A6" s="156" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="170"/>
-      <c r="C6" s="226"/>
-      <c r="D6" s="227"/>
-      <c r="E6" s="150"/>
-      <c r="F6" s="150"/>
-      <c r="G6" s="168"/>
+      <c r="B6" s="157"/>
+      <c r="C6" s="235"/>
+      <c r="D6" s="236"/>
+      <c r="E6" s="135"/>
+      <c r="F6" s="135"/>
+      <c r="G6" s="155"/>
       <c r="H6" s="119"/>
-      <c r="I6" s="214"/>
-      <c r="J6" s="203"/>
-      <c r="K6" s="192"/>
+      <c r="I6" s="176"/>
+      <c r="J6" s="177"/>
+      <c r="K6" s="211"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="214" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="203"/>
-      <c r="C7" s="192"/>
-      <c r="D7" s="217" t="s">
+      <c r="A7" s="176" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="177"/>
+      <c r="C7" s="211"/>
+      <c r="D7" s="181" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="228"/>
-      <c r="F7" s="228"/>
-      <c r="G7" s="185"/>
-      <c r="H7" s="232" t="s">
+      <c r="E7" s="237"/>
+      <c r="F7" s="237"/>
+      <c r="G7" s="182"/>
+      <c r="H7" s="227" t="s">
         <v>130</v>
       </c>
-      <c r="I7" s="222"/>
-      <c r="J7" s="204"/>
-      <c r="K7" s="193"/>
+      <c r="I7" s="187"/>
+      <c r="J7" s="188"/>
+      <c r="K7" s="212"/>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="222"/>
-      <c r="B8" s="204"/>
-      <c r="C8" s="193"/>
-      <c r="D8" s="238" t="s">
+      <c r="A8" s="187"/>
+      <c r="B8" s="188"/>
+      <c r="C8" s="212"/>
+      <c r="D8" s="233" t="s">
         <v>127</v>
       </c>
-      <c r="E8" s="224" t="s">
+      <c r="E8" s="190" t="s">
         <v>128</v>
       </c>
-      <c r="F8" s="224" t="s">
+      <c r="F8" s="190" t="s">
         <v>131</v>
       </c>
-      <c r="G8" s="224" t="s">
+      <c r="G8" s="190" t="s">
         <v>129</v>
       </c>
-      <c r="H8" s="233" t="s">
+      <c r="H8" s="228" t="s">
         <v>130</v>
       </c>
-      <c r="I8" s="222"/>
-      <c r="J8" s="204"/>
-      <c r="K8" s="193"/>
+      <c r="I8" s="187"/>
+      <c r="J8" s="188"/>
+      <c r="K8" s="212"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="223"/>
-      <c r="B9" s="206"/>
-      <c r="C9" s="194"/>
-      <c r="D9" s="239"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="167"/>
-      <c r="G9" s="167"/>
-      <c r="H9" s="234"/>
-      <c r="I9" s="222"/>
-      <c r="J9" s="204"/>
-      <c r="K9" s="193"/>
+      <c r="A9" s="189"/>
+      <c r="B9" s="196"/>
+      <c r="C9" s="213"/>
+      <c r="D9" s="234"/>
+      <c r="E9" s="153"/>
+      <c r="F9" s="153"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="229"/>
+      <c r="I9" s="187"/>
+      <c r="J9" s="188"/>
+      <c r="K9" s="212"/>
     </row>
     <row r="10" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="62">
@@ -5355,9 +6663,9 @@
       <c r="F10" s="23"/>
       <c r="G10" s="121"/>
       <c r="H10" s="122"/>
-      <c r="I10" s="222"/>
-      <c r="J10" s="204"/>
-      <c r="K10" s="193"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="188"/>
+      <c r="K10" s="212"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="67">
@@ -5377,9 +6685,9 @@
       <c r="F11" s="26"/>
       <c r="G11" s="124"/>
       <c r="H11" s="125"/>
-      <c r="I11" s="222"/>
-      <c r="J11" s="204"/>
-      <c r="K11" s="193"/>
+      <c r="I11" s="187"/>
+      <c r="J11" s="188"/>
+      <c r="K11" s="212"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="67">
@@ -5399,9 +6707,9 @@
       <c r="F12" s="26"/>
       <c r="G12" s="124"/>
       <c r="H12" s="125"/>
-      <c r="I12" s="222"/>
-      <c r="J12" s="204"/>
-      <c r="K12" s="193"/>
+      <c r="I12" s="187"/>
+      <c r="J12" s="188"/>
+      <c r="K12" s="212"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="67">
@@ -5421,9 +6729,9 @@
       <c r="F13" s="23"/>
       <c r="G13" s="121"/>
       <c r="H13" s="125"/>
-      <c r="I13" s="222"/>
-      <c r="J13" s="204"/>
-      <c r="K13" s="193"/>
+      <c r="I13" s="187"/>
+      <c r="J13" s="188"/>
+      <c r="K13" s="212"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="67">
@@ -5443,9 +6751,9 @@
       <c r="F14" s="26"/>
       <c r="G14" s="124"/>
       <c r="H14" s="125"/>
-      <c r="I14" s="222"/>
-      <c r="J14" s="204"/>
-      <c r="K14" s="193"/>
+      <c r="I14" s="187"/>
+      <c r="J14" s="188"/>
+      <c r="K14" s="212"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="67">
@@ -5465,9 +6773,9 @@
       <c r="F15" s="26"/>
       <c r="G15" s="124"/>
       <c r="H15" s="125"/>
-      <c r="I15" s="222"/>
-      <c r="J15" s="204"/>
-      <c r="K15" s="193"/>
+      <c r="I15" s="187"/>
+      <c r="J15" s="188"/>
+      <c r="K15" s="212"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="67">
@@ -5487,9 +6795,9 @@
       <c r="F16" s="26"/>
       <c r="G16" s="124"/>
       <c r="H16" s="125"/>
-      <c r="I16" s="222"/>
-      <c r="J16" s="204"/>
-      <c r="K16" s="193"/>
+      <c r="I16" s="187"/>
+      <c r="J16" s="188"/>
+      <c r="K16" s="212"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="67">
@@ -5509,9 +6817,9 @@
       <c r="F17" s="26"/>
       <c r="G17" s="124"/>
       <c r="H17" s="125"/>
-      <c r="I17" s="222"/>
-      <c r="J17" s="204"/>
-      <c r="K17" s="193"/>
+      <c r="I17" s="187"/>
+      <c r="J17" s="188"/>
+      <c r="K17" s="212"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="67">
@@ -5531,9 +6839,9 @@
       <c r="F18" s="26"/>
       <c r="G18" s="124"/>
       <c r="H18" s="125"/>
-      <c r="I18" s="222"/>
-      <c r="J18" s="204"/>
-      <c r="K18" s="193"/>
+      <c r="I18" s="187"/>
+      <c r="J18" s="188"/>
+      <c r="K18" s="212"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="67">
@@ -5553,9 +6861,9 @@
       <c r="F19" s="26"/>
       <c r="G19" s="124"/>
       <c r="H19" s="125"/>
-      <c r="I19" s="222"/>
-      <c r="J19" s="204"/>
-      <c r="K19" s="193"/>
+      <c r="I19" s="187"/>
+      <c r="J19" s="188"/>
+      <c r="K19" s="212"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="75">
@@ -5575,9 +6883,9 @@
       <c r="F20" s="26"/>
       <c r="G20" s="124"/>
       <c r="H20" s="125"/>
-      <c r="I20" s="222"/>
-      <c r="J20" s="204"/>
-      <c r="K20" s="193"/>
+      <c r="I20" s="187"/>
+      <c r="J20" s="188"/>
+      <c r="K20" s="212"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="67">
@@ -5597,9 +6905,9 @@
       <c r="F21" s="26"/>
       <c r="G21" s="124"/>
       <c r="H21" s="125"/>
-      <c r="I21" s="222"/>
-      <c r="J21" s="204"/>
-      <c r="K21" s="193"/>
+      <c r="I21" s="187"/>
+      <c r="J21" s="188"/>
+      <c r="K21" s="212"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="67">
@@ -5619,9 +6927,9 @@
       <c r="F22" s="26"/>
       <c r="G22" s="124"/>
       <c r="H22" s="125"/>
-      <c r="I22" s="222"/>
-      <c r="J22" s="204"/>
-      <c r="K22" s="193"/>
+      <c r="I22" s="187"/>
+      <c r="J22" s="188"/>
+      <c r="K22" s="212"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="67">
@@ -5641,9 +6949,9 @@
       <c r="F23" s="26"/>
       <c r="G23" s="124"/>
       <c r="H23" s="125"/>
-      <c r="I23" s="222"/>
-      <c r="J23" s="204"/>
-      <c r="K23" s="193"/>
+      <c r="I23" s="187"/>
+      <c r="J23" s="188"/>
+      <c r="K23" s="212"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="67">
@@ -5663,9 +6971,9 @@
       <c r="F24" s="26"/>
       <c r="G24" s="124"/>
       <c r="H24" s="125"/>
-      <c r="I24" s="222"/>
-      <c r="J24" s="204"/>
-      <c r="K24" s="193"/>
+      <c r="I24" s="187"/>
+      <c r="J24" s="188"/>
+      <c r="K24" s="212"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="67">
@@ -5685,9 +6993,9 @@
       <c r="F25" s="26"/>
       <c r="G25" s="124"/>
       <c r="H25" s="125"/>
-      <c r="I25" s="222"/>
-      <c r="J25" s="204"/>
-      <c r="K25" s="193"/>
+      <c r="I25" s="187"/>
+      <c r="J25" s="188"/>
+      <c r="K25" s="212"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="67">
@@ -5707,9 +7015,9 @@
       <c r="F26" s="26"/>
       <c r="G26" s="124"/>
       <c r="H26" s="125"/>
-      <c r="I26" s="222"/>
-      <c r="J26" s="204"/>
-      <c r="K26" s="193"/>
+      <c r="I26" s="187"/>
+      <c r="J26" s="188"/>
+      <c r="K26" s="212"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="67">
@@ -5729,9 +7037,9 @@
       <c r="F27" s="26"/>
       <c r="G27" s="124"/>
       <c r="H27" s="125"/>
-      <c r="I27" s="222"/>
-      <c r="J27" s="204"/>
-      <c r="K27" s="193"/>
+      <c r="I27" s="187"/>
+      <c r="J27" s="188"/>
+      <c r="K27" s="212"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="67">
@@ -5751,9 +7059,9 @@
       <c r="F28" s="26"/>
       <c r="G28" s="124"/>
       <c r="H28" s="125"/>
-      <c r="I28" s="222"/>
-      <c r="J28" s="204"/>
-      <c r="K28" s="193"/>
+      <c r="I28" s="187"/>
+      <c r="J28" s="188"/>
+      <c r="K28" s="212"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="67">
@@ -5773,9 +7081,9 @@
       <c r="F29" s="26"/>
       <c r="G29" s="124"/>
       <c r="H29" s="125"/>
-      <c r="I29" s="222"/>
-      <c r="J29" s="204"/>
-      <c r="K29" s="193"/>
+      <c r="I29" s="187"/>
+      <c r="J29" s="188"/>
+      <c r="K29" s="212"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="75">
@@ -5795,9 +7103,9 @@
       <c r="F30" s="26"/>
       <c r="G30" s="124"/>
       <c r="H30" s="125"/>
-      <c r="I30" s="222"/>
-      <c r="J30" s="204"/>
-      <c r="K30" s="193"/>
+      <c r="I30" s="187"/>
+      <c r="J30" s="188"/>
+      <c r="K30" s="212"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="67">
@@ -5817,9 +7125,9 @@
       <c r="F31" s="26"/>
       <c r="G31" s="124"/>
       <c r="H31" s="125"/>
-      <c r="I31" s="222"/>
-      <c r="J31" s="204"/>
-      <c r="K31" s="193"/>
+      <c r="I31" s="187"/>
+      <c r="J31" s="188"/>
+      <c r="K31" s="212"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="67">
@@ -5839,9 +7147,9 @@
       <c r="F32" s="26"/>
       <c r="G32" s="124"/>
       <c r="H32" s="125"/>
-      <c r="I32" s="222"/>
-      <c r="J32" s="204"/>
-      <c r="K32" s="193"/>
+      <c r="I32" s="187"/>
+      <c r="J32" s="188"/>
+      <c r="K32" s="212"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="67">
@@ -5861,9 +7169,9 @@
       <c r="F33" s="26"/>
       <c r="G33" s="124"/>
       <c r="H33" s="125"/>
-      <c r="I33" s="222"/>
-      <c r="J33" s="204"/>
-      <c r="K33" s="193"/>
+      <c r="I33" s="187"/>
+      <c r="J33" s="188"/>
+      <c r="K33" s="212"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="67">
@@ -5883,9 +7191,9 @@
       <c r="F34" s="26"/>
       <c r="G34" s="124"/>
       <c r="H34" s="125"/>
-      <c r="I34" s="222"/>
-      <c r="J34" s="204"/>
-      <c r="K34" s="193"/>
+      <c r="I34" s="187"/>
+      <c r="J34" s="188"/>
+      <c r="K34" s="212"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="67">
@@ -5905,9 +7213,9 @@
       <c r="F35" s="26"/>
       <c r="G35" s="124"/>
       <c r="H35" s="125"/>
-      <c r="I35" s="222"/>
-      <c r="J35" s="204"/>
-      <c r="K35" s="193"/>
+      <c r="I35" s="187"/>
+      <c r="J35" s="188"/>
+      <c r="K35" s="212"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="67">
@@ -5927,9 +7235,9 @@
       <c r="F36" s="26"/>
       <c r="G36" s="124"/>
       <c r="H36" s="125"/>
-      <c r="I36" s="222"/>
-      <c r="J36" s="204"/>
-      <c r="K36" s="193"/>
+      <c r="I36" s="187"/>
+      <c r="J36" s="188"/>
+      <c r="K36" s="212"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="67">
@@ -5949,9 +7257,9 @@
       <c r="F37" s="26"/>
       <c r="G37" s="124"/>
       <c r="H37" s="125"/>
-      <c r="I37" s="222"/>
-      <c r="J37" s="204"/>
-      <c r="K37" s="193"/>
+      <c r="I37" s="187"/>
+      <c r="J37" s="188"/>
+      <c r="K37" s="212"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="67">
@@ -5971,9 +7279,9 @@
       <c r="F38" s="26"/>
       <c r="G38" s="124"/>
       <c r="H38" s="125"/>
-      <c r="I38" s="222"/>
-      <c r="J38" s="204"/>
-      <c r="K38" s="193"/>
+      <c r="I38" s="187"/>
+      <c r="J38" s="188"/>
+      <c r="K38" s="212"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="76">
@@ -5993,16 +7301,16 @@
       <c r="F39" s="26"/>
       <c r="G39" s="124"/>
       <c r="H39" s="125"/>
-      <c r="I39" s="222"/>
-      <c r="J39" s="204"/>
-      <c r="K39" s="193"/>
+      <c r="I39" s="187"/>
+      <c r="J39" s="188"/>
+      <c r="K39" s="212"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="229" t="s">
+      <c r="A40" s="238" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="230"/>
-      <c r="C40" s="231"/>
+      <c r="B40" s="239"/>
+      <c r="C40" s="240"/>
       <c r="D40" s="126" t="e">
         <f>AVERAGE(D10:D39)</f>
         <v>#DIV/0!</v>
@@ -6023,16 +7331,16 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I40" s="222"/>
-      <c r="J40" s="204"/>
-      <c r="K40" s="193"/>
+      <c r="I40" s="187"/>
+      <c r="J40" s="188"/>
+      <c r="K40" s="212"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="143" t="s">
+      <c r="A41" s="164" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="144"/>
-      <c r="C41" s="145"/>
+      <c r="B41" s="165"/>
+      <c r="C41" s="166"/>
       <c r="D41" s="128">
         <f>MIN(D10:D39)</f>
         <v>0</v>
@@ -6053,16 +7361,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I41" s="222"/>
-      <c r="J41" s="204"/>
-      <c r="K41" s="193"/>
+      <c r="I41" s="187"/>
+      <c r="J41" s="188"/>
+      <c r="K41" s="212"/>
     </row>
     <row r="42" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="235" t="s">
+      <c r="A42" s="230" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="236"/>
-      <c r="C42" s="237"/>
+      <c r="B42" s="231"/>
+      <c r="C42" s="232"/>
       <c r="D42" s="130">
         <f>MAX(D10:D39)</f>
         <v>0</v>
@@ -6083,16 +7391,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I42" s="223"/>
-      <c r="J42" s="206"/>
-      <c r="K42" s="194"/>
+      <c r="I42" s="189"/>
+      <c r="J42" s="196"/>
+      <c r="K42" s="213"/>
     </row>
     <row r="43" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="134"/>
-      <c r="C43" s="134"/>
+      <c r="B43" s="171"/>
+      <c r="C43" s="171"/>
       <c r="D43" s="44" t="s">
         <v>22</v>
       </c>
@@ -6109,8 +7417,8 @@
     </row>
     <row r="44" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="50"/>
-      <c r="B44" s="135"/>
-      <c r="C44" s="135"/>
+      <c r="B44" s="172"/>
+      <c r="C44" s="172"/>
       <c r="D44" s="44"/>
       <c r="F44" s="46"/>
       <c r="G44" s="47"/>
@@ -6119,11 +7427,11 @@
       <c r="J44" s="51"/>
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="133" t="s">
+      <c r="A45" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="133"/>
-      <c r="C45" s="133"/>
+      <c r="B45" s="170"/>
+      <c r="C45" s="170"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="47" t="s">
@@ -6136,11 +7444,11 @@
       <c r="H45" s="44"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="133" t="s">
+      <c r="A46" s="170" t="s">
         <v>134</v>
       </c>
-      <c r="B46" s="133"/>
-      <c r="C46" s="133"/>
+      <c r="B46" s="170"/>
+      <c r="C46" s="170"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="44"/>
@@ -6165,15 +7473,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A7:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="J4:K4"/>
@@ -6190,27 +7489,36 @@
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="A40:C40"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A7:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
   </mergeCells>
   <conditionalFormatting sqref="D10:D42">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="notBetween">
-      <formula>52</formula>
-      <formula>64</formula>
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="notBetween">
+      <formula>53</formula>
+      <formula>65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10:E42">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="notBetween">
-      <formula>49</formula>
-      <formula>59</formula>
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="notBetween">
+      <formula>31</formula>
+      <formula>41</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F42">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="notBetween">
-      <formula>-12.5</formula>
-      <formula>-4.5</formula>
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="notBetween">
+      <formula>-28</formula>
+      <formula>-20</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:H42">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="notBetween">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="notBetween">
       <formula>0</formula>
       <formula>4</formula>
     </cfRule>
@@ -6236,15 +7544,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="303" t="s">
+      <c r="A1" s="241" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="304"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
-      <c r="F1" s="304"/>
-      <c r="G1" s="305"/>
+      <c r="B1" s="242"/>
+      <c r="C1" s="242"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="242"/>
+      <c r="F1" s="242"/>
+      <c r="G1" s="243"/>
     </row>
     <row r="2" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="87"/>
@@ -6258,37 +7566,37 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="241" t="s">
+      <c r="A3" s="292" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="242"/>
-      <c r="C3" s="242"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="243"/>
+      <c r="B3" s="293"/>
+      <c r="C3" s="293"/>
+      <c r="D3" s="293"/>
+      <c r="E3" s="293"/>
+      <c r="F3" s="293"/>
+      <c r="G3" s="294"/>
     </row>
     <row r="4" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="222" t="s">
+      <c r="A4" s="187" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="204"/>
-      <c r="C4" s="204"/>
-      <c r="D4" s="204"/>
-      <c r="E4" s="204"/>
-      <c r="F4" s="204"/>
-      <c r="G4" s="193"/>
+      <c r="B4" s="188"/>
+      <c r="C4" s="188"/>
+      <c r="D4" s="188"/>
+      <c r="E4" s="188"/>
+      <c r="F4" s="188"/>
+      <c r="G4" s="212"/>
     </row>
     <row r="5" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="306" t="s">
+      <c r="A5" s="244" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="307"/>
-      <c r="C5" s="307"/>
-      <c r="D5" s="307"/>
-      <c r="E5" s="307"/>
-      <c r="F5" s="307"/>
-      <c r="G5" s="308"/>
+      <c r="B5" s="245"/>
+      <c r="C5" s="245"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="246"/>
     </row>
     <row r="6" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="90" t="s">
@@ -6300,14 +7608,14 @@
       <c r="C6" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="262" t="s">
-        <v>143</v>
-      </c>
-      <c r="E6" s="264"/>
-      <c r="F6" s="283" t="s">
+      <c r="D6" s="247" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="248"/>
+      <c r="F6" s="249" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="287">
+      <c r="G6" s="250">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
@@ -6320,13 +7628,13 @@
       <c r="C7" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="262">
+      <c r="D7" s="247">
         <f>Page1!F5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="264"/>
-      <c r="F7" s="283"/>
-      <c r="G7" s="309"/>
+      <c r="E7" s="248"/>
+      <c r="F7" s="249"/>
+      <c r="G7" s="251"/>
     </row>
     <row r="8" spans="1:7" s="86" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="90" t="s">
@@ -6339,15 +7647,15 @@
       <c r="C8" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="283">
+      <c r="D8" s="249">
         <f>Page1!H5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="283"/>
-      <c r="F8" s="284" t="s">
+      <c r="E8" s="249"/>
+      <c r="F8" s="261" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="287">
+      <c r="G8" s="250">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
@@ -6360,15 +7668,15 @@
         <f>Page1!G44</f>
         <v>461347000</v>
       </c>
-      <c r="C9" s="284" t="s">
+      <c r="C9" s="261" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="290" t="s">
+      <c r="D9" s="266" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="291"/>
-      <c r="F9" s="285"/>
-      <c r="G9" s="288"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="262"/>
+      <c r="G9" s="264"/>
     </row>
     <row r="10" spans="1:7" s="86" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="97" t="s">
@@ -6378,34 +7686,34 @@
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="C10" s="286"/>
-      <c r="D10" s="292"/>
-      <c r="E10" s="293"/>
-      <c r="F10" s="286"/>
-      <c r="G10" s="289"/>
+      <c r="C10" s="263"/>
+      <c r="D10" s="268"/>
+      <c r="E10" s="269"/>
+      <c r="F10" s="263"/>
+      <c r="G10" s="265"/>
     </row>
     <row r="11" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="294" t="s">
+      <c r="A11" s="252" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="296" t="s">
+      <c r="B11" s="254" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="298" t="s">
+      <c r="C11" s="256" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="299"/>
-      <c r="E11" s="300"/>
-      <c r="F11" s="296" t="s">
+      <c r="D11" s="257"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="254" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="301" t="s">
+      <c r="G11" s="259" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="295"/>
-      <c r="B12" s="297"/>
+      <c r="A12" s="253"/>
+      <c r="B12" s="255"/>
       <c r="C12" s="99" t="s">
         <v>63</v>
       </c>
@@ -6415,8 +7723,8 @@
       <c r="E12" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="297"/>
-      <c r="G12" s="302"/>
+      <c r="F12" s="255"/>
+      <c r="G12" s="260"/>
     </row>
     <row r="13" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="100" t="s">
@@ -6486,7 +7794,7 @@
         <f>Page1!K39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="279" t="s">
+      <c r="G15" s="270" t="s">
         <v>74</v>
       </c>
     </row>
@@ -6510,7 +7818,7 @@
         <f>Page2!F41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="233"/>
+      <c r="G16" s="228"/>
     </row>
     <row r="17" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="104" t="s">
@@ -6532,7 +7840,7 @@
         <f>Page1!I39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="233"/>
+      <c r="G17" s="228"/>
     </row>
     <row r="18" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="104" t="s">
@@ -6554,7 +7862,7 @@
         <f>Page2!D41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="233"/>
+      <c r="G18" s="228"/>
     </row>
     <row r="19" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="104" t="s">
@@ -6576,7 +7884,7 @@
         <f>Page1!J39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="233"/>
+      <c r="G19" s="228"/>
     </row>
     <row r="20" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="104" t="s">
@@ -6598,7 +7906,7 @@
         <f>Page2!E41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="233"/>
+      <c r="G20" s="228"/>
     </row>
     <row r="21" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="104" t="s">
@@ -6620,7 +7928,7 @@
         <f>Page1!G39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="233"/>
+      <c r="G21" s="228"/>
     </row>
     <row r="22" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="104" t="s">
@@ -6642,7 +7950,7 @@
         <f>Page1!H39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="152"/>
+      <c r="G22" s="138"/>
     </row>
     <row r="23" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="104" t="s">
@@ -6678,11 +7986,13 @@
       <c r="C24" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>142</v>
+      <c r="D24" s="39">
+        <f>Page2!J9</f>
+        <v>290</v>
+      </c>
+      <c r="E24" s="39">
+        <f>Page2!J10</f>
+        <v>293</v>
       </c>
       <c r="F24" s="39" t="e">
         <f>Page2!I41</f>
@@ -6740,26 +8050,26 @@
       </c>
     </row>
     <row r="27" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="276" t="s">
+      <c r="A27" s="271" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="277"/>
-      <c r="C27" s="277"/>
-      <c r="D27" s="277"/>
-      <c r="E27" s="277"/>
-      <c r="F27" s="277"/>
-      <c r="G27" s="278"/>
+      <c r="B27" s="272"/>
+      <c r="C27" s="272"/>
+      <c r="D27" s="272"/>
+      <c r="E27" s="272"/>
+      <c r="F27" s="272"/>
+      <c r="G27" s="273"/>
     </row>
     <row r="28" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="260" t="s">
+      <c r="A28" s="274" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="261"/>
-      <c r="C28" s="280" t="s">
+      <c r="B28" s="275"/>
+      <c r="C28" s="276" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="281"/>
-      <c r="E28" s="282"/>
+      <c r="D28" s="277"/>
+      <c r="E28" s="278"/>
       <c r="F28" s="113" t="s">
         <v>95</v>
       </c>
@@ -6768,15 +8078,15 @@
       </c>
     </row>
     <row r="29" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="265" t="s">
+      <c r="A29" s="279" t="s">
         <v>97</v>
       </c>
-      <c r="B29" s="264"/>
-      <c r="C29" s="270" t="s">
+      <c r="B29" s="248"/>
+      <c r="C29" s="280" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="271"/>
-      <c r="E29" s="272"/>
+      <c r="D29" s="281"/>
+      <c r="E29" s="282"/>
       <c r="F29" s="80" t="s">
         <v>95</v>
       </c>
@@ -6785,15 +8095,15 @@
       </c>
     </row>
     <row r="30" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="265" t="s">
+      <c r="A30" s="279" t="s">
         <v>100</v>
       </c>
-      <c r="B30" s="264"/>
-      <c r="C30" s="270" t="s">
+      <c r="B30" s="248"/>
+      <c r="C30" s="280" t="s">
         <v>101</v>
       </c>
-      <c r="D30" s="271"/>
-      <c r="E30" s="272"/>
+      <c r="D30" s="281"/>
+      <c r="E30" s="282"/>
       <c r="F30" s="80" t="s">
         <v>95</v>
       </c>
@@ -6802,15 +8112,15 @@
       </c>
     </row>
     <row r="31" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="265" t="s">
+      <c r="A31" s="279" t="s">
         <v>102</v>
       </c>
-      <c r="B31" s="264"/>
-      <c r="C31" s="270" t="s">
+      <c r="B31" s="248"/>
+      <c r="C31" s="280" t="s">
         <v>103</v>
       </c>
-      <c r="D31" s="271"/>
-      <c r="E31" s="272"/>
+      <c r="D31" s="281"/>
+      <c r="E31" s="282"/>
       <c r="F31" s="80" t="s">
         <v>95</v>
       </c>
@@ -6819,15 +8129,15 @@
       </c>
     </row>
     <row r="32" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="265" t="s">
+      <c r="A32" s="279" t="s">
         <v>105</v>
       </c>
-      <c r="B32" s="264"/>
-      <c r="C32" s="270" t="s">
+      <c r="B32" s="248"/>
+      <c r="C32" s="280" t="s">
         <v>106</v>
       </c>
-      <c r="D32" s="271"/>
-      <c r="E32" s="272"/>
+      <c r="D32" s="281"/>
+      <c r="E32" s="282"/>
       <c r="F32" s="80" t="s">
         <v>95</v>
       </c>
@@ -6835,61 +8145,61 @@
         <v>99</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="265" t="s">
+    <row r="33" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="279" t="s">
         <v>107</v>
       </c>
-      <c r="B33" s="264"/>
-      <c r="C33" s="270" t="s">
+      <c r="B33" s="248"/>
+      <c r="C33" s="280" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="271"/>
-      <c r="E33" s="272"/>
+      <c r="D33" s="281"/>
+      <c r="E33" s="282"/>
       <c r="F33" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="G33" s="19" t="s">
+      <c r="G33" s="108" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="86" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="162" t="s">
+      <c r="A34" s="148" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="163"/>
-      <c r="C34" s="273" t="s">
+      <c r="B34" s="149"/>
+      <c r="C34" s="283" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="274"/>
-      <c r="E34" s="275"/>
+      <c r="D34" s="284"/>
+      <c r="E34" s="285"/>
       <c r="F34" s="114" t="s">
         <v>95</v>
       </c>
-      <c r="G34" s="19" t="s">
+      <c r="G34" s="133" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="276" t="s">
+      <c r="A35" s="271" t="s">
         <v>112</v>
       </c>
-      <c r="B35" s="277"/>
-      <c r="C35" s="277"/>
-      <c r="D35" s="277"/>
-      <c r="E35" s="277"/>
-      <c r="F35" s="277"/>
-      <c r="G35" s="278"/>
+      <c r="B35" s="272"/>
+      <c r="C35" s="272"/>
+      <c r="D35" s="272"/>
+      <c r="E35" s="272"/>
+      <c r="F35" s="272"/>
+      <c r="G35" s="273"/>
     </row>
     <row r="36" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="158" t="s">
+      <c r="A36" s="144" t="s">
         <v>113</v>
       </c>
-      <c r="B36" s="159"/>
-      <c r="C36" s="268" t="s">
+      <c r="B36" s="145"/>
+      <c r="C36" s="289" t="s">
         <v>101</v>
       </c>
-      <c r="D36" s="269"/>
-      <c r="E36" s="159"/>
+      <c r="D36" s="290"/>
+      <c r="E36" s="145"/>
       <c r="F36" s="10" t="s">
         <v>95</v>
       </c>
@@ -6898,15 +8208,15 @@
       </c>
     </row>
     <row r="37" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="260" t="s">
+      <c r="A37" s="274" t="s">
         <v>114</v>
       </c>
-      <c r="B37" s="261"/>
-      <c r="C37" s="262" t="s">
+      <c r="B37" s="275"/>
+      <c r="C37" s="247" t="s">
         <v>115</v>
       </c>
-      <c r="D37" s="263"/>
-      <c r="E37" s="264"/>
+      <c r="D37" s="286"/>
+      <c r="E37" s="248"/>
       <c r="F37" s="106" t="s">
         <v>95</v>
       </c>
@@ -6915,15 +8225,15 @@
       </c>
     </row>
     <row r="38" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="265" t="s">
+      <c r="A38" s="279" t="s">
         <v>116</v>
       </c>
-      <c r="B38" s="264"/>
-      <c r="C38" s="262" t="s">
+      <c r="B38" s="248"/>
+      <c r="C38" s="247" t="s">
         <v>117</v>
       </c>
-      <c r="D38" s="263"/>
-      <c r="E38" s="264"/>
+      <c r="D38" s="286"/>
+      <c r="E38" s="248"/>
       <c r="F38" s="106" t="s">
         <v>95</v>
       </c>
@@ -6932,15 +8242,15 @@
       </c>
     </row>
     <row r="39" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="162" t="s">
+      <c r="A39" s="148" t="s">
         <v>118</v>
       </c>
-      <c r="B39" s="163"/>
-      <c r="C39" s="266" t="s">
+      <c r="B39" s="149"/>
+      <c r="C39" s="287" t="s">
         <v>119</v>
       </c>
-      <c r="D39" s="267"/>
-      <c r="E39" s="163"/>
+      <c r="D39" s="288"/>
+      <c r="E39" s="149"/>
       <c r="F39" s="1" t="s">
         <v>95</v>
       </c>
@@ -6949,50 +8259,50 @@
       </c>
     </row>
     <row r="40" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="244" t="s">
+      <c r="A40" s="295" t="s">
         <v>120</v>
       </c>
-      <c r="B40" s="245"/>
-      <c r="C40" s="246" t="s">
+      <c r="B40" s="296"/>
+      <c r="C40" s="297" t="s">
         <v>137</v>
       </c>
-      <c r="D40" s="247"/>
-      <c r="E40" s="248"/>
-      <c r="F40" s="246" t="s">
+      <c r="D40" s="298"/>
+      <c r="E40" s="299"/>
+      <c r="F40" s="297" t="s">
         <v>138</v>
       </c>
-      <c r="G40" s="248"/>
+      <c r="G40" s="299"/>
     </row>
     <row r="41" spans="1:7" s="86" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="249"/>
-      <c r="B41" s="250"/>
-      <c r="C41" s="222"/>
-      <c r="D41" s="204"/>
-      <c r="E41" s="193"/>
-      <c r="F41" s="253"/>
-      <c r="G41" s="254"/>
+      <c r="A41" s="300"/>
+      <c r="B41" s="301"/>
+      <c r="C41" s="187"/>
+      <c r="D41" s="188"/>
+      <c r="E41" s="212"/>
+      <c r="F41" s="304"/>
+      <c r="G41" s="305"/>
     </row>
     <row r="42" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="251"/>
-      <c r="B42" s="252"/>
-      <c r="C42" s="255" t="s">
+      <c r="A42" s="302"/>
+      <c r="B42" s="303"/>
+      <c r="C42" s="306" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="256"/>
-      <c r="E42" s="257"/>
-      <c r="F42" s="255" t="s">
+      <c r="D42" s="307"/>
+      <c r="E42" s="308"/>
+      <c r="F42" s="306" t="s">
         <v>139</v>
       </c>
-      <c r="G42" s="257"/>
+      <c r="G42" s="308"/>
     </row>
     <row r="43" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="115"/>
       <c r="B43" s="115"/>
       <c r="C43" s="115"/>
       <c r="D43" s="115"/>
-      <c r="E43" s="258"/>
-      <c r="F43" s="258"/>
-      <c r="G43" s="258"/>
+      <c r="E43" s="309"/>
+      <c r="F43" s="309"/>
+      <c r="G43" s="309"/>
     </row>
     <row r="44" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="46" t="s">
@@ -7001,64 +8311,25 @@
       <c r="B44" s="116"/>
       <c r="C44" s="117"/>
       <c r="D44" s="115"/>
-      <c r="E44" s="259"/>
-      <c r="F44" s="259"/>
-      <c r="G44" s="259"/>
+      <c r="E44" s="310"/>
+      <c r="F44" s="310"/>
+      <c r="G44" s="310"/>
     </row>
     <row r="45" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="240" t="s">
+      <c r="A46" s="291" t="s">
         <v>122</v>
       </c>
-      <c r="B46" s="240"/>
+      <c r="B46" s="291"/>
     </row>
     <row r="47" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="240" t="s">
+      <c r="A47" s="291" t="s">
         <v>123</v>
       </c>
-      <c r="B47" s="240"/>
+      <c r="B47" s="291"/>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="G15:G22"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:E36"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A3:G3"/>
@@ -7075,6 +8346,45 @@
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="G15:G22"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="D7:E7"/>
   </mergeCells>
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.78740157480314965" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="84" orientation="portrait" r:id="rId1"/>

--- a/backend/templates/UC-18gsm-290NP-ABQR.xlsx
+++ b/backend/templates/UC-18gsm-290NP-ABQR.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6D00F0-BB63-4202-B7D4-3A4170F5A11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABCA98F-3912-46E8-BE56-CA0A23ACA099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="141">
   <si>
     <t>Sample No.</t>
   </si>
@@ -512,9 +512,6 @@
   </si>
   <si>
     <t>Swanson Plastics(India) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>#02</t>
   </si>
 </sst>
 </file>
@@ -1855,6 +1852,54 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1864,9 +1909,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1921,9 +1963,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1936,155 +1975,92 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2098,97 +2074,307 @@
     <xf numFmtId="1" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -2208,329 +2394,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="160">
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
         <strike/>
@@ -2571,457 +2442,6 @@
         <strike/>
         <color rgb="FFFF0000"/>
       </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3142,833 +2562,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -4372,35 +2965,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="158" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -4421,12 +3014,12 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="144" t="s">
+      <c r="A4" s="159" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="145"/>
-      <c r="C4" s="146"/>
-      <c r="D4" s="147"/>
+      <c r="B4" s="160"/>
+      <c r="C4" s="161"/>
+      <c r="D4" s="162"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -4438,19 +3031,19 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="139"/>
-      <c r="K4" s="140"/>
+      <c r="J4" s="154"/>
+      <c r="K4" s="155"/>
       <c r="M4" s="45" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="148" t="s">
+      <c r="A5" s="163" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="149"/>
-      <c r="C5" s="150"/>
-      <c r="D5" s="151"/>
+      <c r="B5" s="164"/>
+      <c r="C5" s="165"/>
+      <c r="D5" s="166"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -4462,64 +3055,64 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="141"/>
-      <c r="K5" s="142"/>
+      <c r="J5" s="156"/>
+      <c r="K5" s="157"/>
     </row>
     <row r="6" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="156" t="s">
+      <c r="A6" s="170" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="157"/>
-      <c r="C6" s="158"/>
+      <c r="B6" s="171"/>
+      <c r="C6" s="172"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="G6" s="134"/>
-      <c r="H6" s="155"/>
-      <c r="I6" s="134"/>
-      <c r="J6" s="135"/>
-      <c r="K6" s="136"/>
+      <c r="G6" s="150"/>
+      <c r="H6" s="169"/>
+      <c r="I6" s="150"/>
+      <c r="J6" s="151"/>
+      <c r="K6" s="152"/>
     </row>
     <row r="7" spans="1:13" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="159" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="137"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="137" t="s">
+      <c r="A7" s="137" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="137" t="s">
+      <c r="E7" s="138" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="137" t="s">
+      <c r="F7" s="138" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="152" t="s">
+      <c r="G7" s="167" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="152" t="s">
+      <c r="H7" s="167" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="137" t="s">
+      <c r="I7" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="137"/>
-      <c r="K7" s="138"/>
+      <c r="J7" s="138"/>
+      <c r="K7" s="153"/>
     </row>
     <row r="8" spans="1:13" s="5" customFormat="1" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="160"/>
-      <c r="B8" s="154"/>
-      <c r="C8" s="154"/>
-      <c r="D8" s="154"/>
-      <c r="E8" s="154" t="s">
+      <c r="A8" s="139"/>
+      <c r="B8" s="140"/>
+      <c r="C8" s="140"/>
+      <c r="D8" s="140"/>
+      <c r="E8" s="140" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="154"/>
-      <c r="G8" s="153"/>
-      <c r="H8" s="153"/>
+      <c r="F8" s="140"/>
+      <c r="G8" s="168"/>
+      <c r="H8" s="168"/>
       <c r="I8" s="1" t="s">
         <v>10</v>
       </c>
@@ -4921,11 +3514,11 @@
       <c r="K38" s="28"/>
     </row>
     <row r="39" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="167" t="s">
+      <c r="A39" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="168"/>
-      <c r="C39" s="169"/>
+      <c r="B39" s="148"/>
+      <c r="C39" s="149"/>
       <c r="D39" s="35" t="e">
         <f>AVERAGE(D9:D38)</f>
         <v>#DIV/0!</v>
@@ -4960,11 +3553,11 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="164" t="s">
+      <c r="A40" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="165"/>
-      <c r="C40" s="166"/>
+      <c r="B40" s="145"/>
+      <c r="C40" s="146"/>
       <c r="D40" s="38">
         <f>MIN(D9:D38)</f>
         <v>0</v>
@@ -4999,11 +3592,11 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="161" t="s">
+      <c r="A41" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="162"/>
-      <c r="C41" s="163"/>
+      <c r="B41" s="142"/>
+      <c r="C41" s="143"/>
       <c r="D41" s="41">
         <f>MAX(D9:D38)</f>
         <v>0</v>
@@ -5044,8 +3637,8 @@
       <c r="A42" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="171"/>
-      <c r="C42" s="171"/>
+      <c r="B42" s="135"/>
+      <c r="C42" s="135"/>
       <c r="D42" s="44" t="s">
         <v>22</v>
       </c>
@@ -5062,8 +3655,8 @@
     </row>
     <row r="43" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="50"/>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="B43" s="136"/>
+      <c r="C43" s="136"/>
       <c r="D43" s="44"/>
       <c r="F43" s="46"/>
       <c r="G43" s="47"/>
@@ -5072,11 +3665,11 @@
       <c r="J43" s="51"/>
     </row>
     <row r="44" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="170" t="s">
+      <c r="A44" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="170"/>
-      <c r="C44" s="170"/>
+      <c r="B44" s="134"/>
+      <c r="C44" s="134"/>
       <c r="D44" s="44"/>
       <c r="E44" s="44"/>
       <c r="F44" s="47" t="s">
@@ -5088,11 +3681,11 @@
       <c r="H44" s="44"/>
     </row>
     <row r="45" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="170" t="s">
+      <c r="A45" s="134" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="170"/>
-      <c r="C45" s="170"/>
+      <c r="B45" s="134"/>
+      <c r="C45" s="134"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="44"/>
@@ -5103,9 +3696,9 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="170"/>
-      <c r="B46" s="170"/>
-      <c r="C46" s="170"/>
+      <c r="A46" s="134"/>
+      <c r="B46" s="134"/>
+      <c r="C46" s="134"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="44"/>
@@ -5134,16 +3727,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="26">
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A39:C39"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="J4:K4"/>
@@ -5160,50 +3743,60 @@
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A45:C45"/>
   </mergeCells>
   <conditionalFormatting sqref="D9:D41">
-    <cfRule type="cellIs" dxfId="87" priority="13" operator="notBetween">
+    <cfRule type="cellIs" dxfId="17" priority="13" operator="notBetween">
       <formula>17</formula>
       <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E41">
-    <cfRule type="cellIs" dxfId="86" priority="11" operator="notBetween">
+    <cfRule type="cellIs" dxfId="16" priority="11" operator="notBetween">
       <formula>18</formula>
       <formula>28</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F41">
-    <cfRule type="cellIs" dxfId="85" priority="9" operator="notBetween">
+    <cfRule type="cellIs" dxfId="15" priority="9" operator="notBetween">
       <formula>360</formula>
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:G41">
-    <cfRule type="cellIs" dxfId="84" priority="7" operator="notBetween">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="notBetween">
       <formula>0.3</formula>
       <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H38">
-    <cfRule type="cellIs" dxfId="83" priority="1" stopIfTrue="1" operator="notBetween">
+    <cfRule type="cellIs" dxfId="13" priority="1" stopIfTrue="1" operator="notBetween">
       <formula>0.6</formula>
       <formula>1.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I41">
-    <cfRule type="cellIs" dxfId="82" priority="5" operator="notBetween">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="notBetween">
       <formula>900</formula>
       <formula>1200</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J41">
-    <cfRule type="cellIs" dxfId="81" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="lessThan">
       <formula>350</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K41">
-    <cfRule type="cellIs" dxfId="80" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="lessThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5226,35 +3819,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="158" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -5275,18 +3868,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="144" t="s">
+      <c r="A4" s="159" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="145">
+      <c r="B4" s="160">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="220">
+      <c r="C4" s="185">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="182"/>
+      <c r="D4" s="186"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -5304,25 +3897,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221">
+      <c r="J4" s="173">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="222"/>
+      <c r="K4" s="174"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="148" t="s">
+      <c r="A5" s="163" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="149">
+      <c r="B5" s="164">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="150">
+      <c r="C5" s="165">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="151"/>
+      <c r="D5" s="166"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -5340,104 +3933,104 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="223">
+      <c r="J5" s="175">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="224"/>
+      <c r="K5" s="176"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="173" t="s">
+      <c r="A6" s="212" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="174"/>
-      <c r="C6" s="175"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="177"/>
-      <c r="F6" s="178"/>
-      <c r="G6" s="193"/>
-      <c r="H6" s="178"/>
-      <c r="I6" s="207"/>
-      <c r="J6" s="208"/>
+      <c r="B6" s="213"/>
+      <c r="C6" s="214"/>
+      <c r="D6" s="215"/>
+      <c r="E6" s="204"/>
+      <c r="F6" s="199"/>
+      <c r="G6" s="198"/>
+      <c r="H6" s="199"/>
+      <c r="I6" s="200"/>
+      <c r="J6" s="201"/>
       <c r="K6" s="56"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="176" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="177"/>
-      <c r="C7" s="177"/>
-      <c r="D7" s="181" t="s">
+      <c r="A7" s="215" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="204"/>
+      <c r="C7" s="204"/>
+      <c r="D7" s="218" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="177"/>
-      <c r="F7" s="182"/>
-      <c r="G7" s="193" t="s">
+      <c r="E7" s="204"/>
+      <c r="F7" s="186"/>
+      <c r="G7" s="198" t="s">
         <v>126</v>
       </c>
-      <c r="H7" s="177"/>
-      <c r="I7" s="193" t="s">
+      <c r="H7" s="204"/>
+      <c r="I7" s="198" t="s">
         <v>135</v>
       </c>
-      <c r="J7" s="178"/>
-      <c r="K7" s="211" t="s">
+      <c r="J7" s="199"/>
+      <c r="K7" s="193" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="187"/>
-      <c r="B8" s="188"/>
-      <c r="C8" s="188"/>
-      <c r="D8" s="187" t="s">
+      <c r="A8" s="223"/>
+      <c r="B8" s="205"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="223" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="190" t="s">
+      <c r="E8" s="225" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="191" t="s">
+      <c r="F8" s="182" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="194"/>
-      <c r="H8" s="188"/>
-      <c r="I8" s="194" t="s">
+      <c r="G8" s="181"/>
+      <c r="H8" s="205"/>
+      <c r="I8" s="181" t="s">
         <v>136</v>
       </c>
-      <c r="J8" s="191"/>
-      <c r="K8" s="212"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="194"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="187"/>
-      <c r="B9" s="188"/>
-      <c r="C9" s="188"/>
-      <c r="D9" s="187"/>
-      <c r="E9" s="152"/>
-      <c r="F9" s="191"/>
-      <c r="G9" s="194"/>
-      <c r="H9" s="188"/>
+      <c r="A9" s="223"/>
+      <c r="B9" s="205"/>
+      <c r="C9" s="205"/>
+      <c r="D9" s="223"/>
+      <c r="E9" s="167"/>
+      <c r="F9" s="182"/>
+      <c r="G9" s="181"/>
+      <c r="H9" s="205"/>
       <c r="I9" s="58" t="s">
         <v>42</v>
       </c>
       <c r="J9" s="59">
         <v>290</v>
       </c>
-      <c r="K9" s="212"/>
+      <c r="K9" s="194"/>
     </row>
     <row r="10" spans="1:11" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="187"/>
-      <c r="B10" s="188"/>
-      <c r="C10" s="188"/>
-      <c r="D10" s="189"/>
-      <c r="E10" s="153"/>
-      <c r="F10" s="192"/>
-      <c r="G10" s="195"/>
-      <c r="H10" s="196"/>
+      <c r="A10" s="223"/>
+      <c r="B10" s="205"/>
+      <c r="C10" s="205"/>
+      <c r="D10" s="224"/>
+      <c r="E10" s="168"/>
+      <c r="F10" s="226"/>
+      <c r="G10" s="206"/>
+      <c r="H10" s="207"/>
       <c r="I10" s="60" t="s">
         <v>43</v>
       </c>
       <c r="J10" s="61">
         <v>293</v>
       </c>
-      <c r="K10" s="213"/>
+      <c r="K10" s="195"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="62">
@@ -5455,10 +4048,10 @@
       <c r="D11" s="65"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
-      <c r="G11" s="199"/>
-      <c r="H11" s="199"/>
-      <c r="I11" s="225"/>
-      <c r="J11" s="226"/>
+      <c r="G11" s="210"/>
+      <c r="H11" s="210"/>
+      <c r="I11" s="179"/>
+      <c r="J11" s="180"/>
       <c r="K11" s="66"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5477,10 +4070,10 @@
       <c r="D12" s="70"/>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
-      <c r="G12" s="200"/>
-      <c r="H12" s="200"/>
-      <c r="I12" s="205"/>
-      <c r="J12" s="206"/>
+      <c r="G12" s="211"/>
+      <c r="H12" s="211"/>
+      <c r="I12" s="177"/>
+      <c r="J12" s="178"/>
       <c r="K12" s="71"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5499,10 +4092,10 @@
       <c r="D13" s="70"/>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
-      <c r="G13" s="200"/>
-      <c r="H13" s="200"/>
-      <c r="I13" s="205"/>
-      <c r="J13" s="206"/>
+      <c r="G13" s="211"/>
+      <c r="H13" s="211"/>
+      <c r="I13" s="177"/>
+      <c r="J13" s="178"/>
       <c r="K13" s="71"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5521,10 +4114,10 @@
       <c r="D14" s="70"/>
       <c r="E14" s="25"/>
       <c r="F14" s="25"/>
-      <c r="G14" s="200"/>
-      <c r="H14" s="200"/>
-      <c r="I14" s="205"/>
-      <c r="J14" s="206"/>
+      <c r="G14" s="211"/>
+      <c r="H14" s="211"/>
+      <c r="I14" s="177"/>
+      <c r="J14" s="178"/>
       <c r="K14" s="71"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5543,10 +4136,10 @@
       <c r="D15" s="70"/>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
-      <c r="G15" s="200"/>
-      <c r="H15" s="200"/>
-      <c r="I15" s="205"/>
-      <c r="J15" s="206"/>
+      <c r="G15" s="211"/>
+      <c r="H15" s="211"/>
+      <c r="I15" s="177"/>
+      <c r="J15" s="178"/>
       <c r="K15" s="71"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5565,10 +4158,10 @@
       <c r="D16" s="65"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
-      <c r="G16" s="199"/>
-      <c r="H16" s="199"/>
-      <c r="I16" s="205"/>
-      <c r="J16" s="206"/>
+      <c r="G16" s="210"/>
+      <c r="H16" s="210"/>
+      <c r="I16" s="177"/>
+      <c r="J16" s="178"/>
       <c r="K16" s="66"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5587,10 +4180,10 @@
       <c r="D17" s="70"/>
       <c r="E17" s="25"/>
       <c r="F17" s="25"/>
-      <c r="G17" s="200"/>
-      <c r="H17" s="200"/>
-      <c r="I17" s="205"/>
-      <c r="J17" s="206"/>
+      <c r="G17" s="211"/>
+      <c r="H17" s="211"/>
+      <c r="I17" s="177"/>
+      <c r="J17" s="178"/>
       <c r="K17" s="71"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5609,10 +4202,10 @@
       <c r="D18" s="70"/>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
-      <c r="G18" s="200"/>
-      <c r="H18" s="200"/>
-      <c r="I18" s="205"/>
-      <c r="J18" s="206"/>
+      <c r="G18" s="211"/>
+      <c r="H18" s="211"/>
+      <c r="I18" s="177"/>
+      <c r="J18" s="178"/>
       <c r="K18" s="71"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5631,10 +4224,10 @@
       <c r="D19" s="70"/>
       <c r="E19" s="25"/>
       <c r="F19" s="25"/>
-      <c r="G19" s="200"/>
-      <c r="H19" s="200"/>
-      <c r="I19" s="205"/>
-      <c r="J19" s="206"/>
+      <c r="G19" s="211"/>
+      <c r="H19" s="211"/>
+      <c r="I19" s="177"/>
+      <c r="J19" s="178"/>
       <c r="K19" s="71"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5653,10 +4246,10 @@
       <c r="D20" s="70"/>
       <c r="E20" s="25"/>
       <c r="F20" s="25"/>
-      <c r="G20" s="201"/>
-      <c r="H20" s="202"/>
-      <c r="I20" s="205"/>
-      <c r="J20" s="206"/>
+      <c r="G20" s="183"/>
+      <c r="H20" s="184"/>
+      <c r="I20" s="177"/>
+      <c r="J20" s="178"/>
       <c r="K20" s="71"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5675,10 +4268,10 @@
       <c r="D21" s="70"/>
       <c r="E21" s="25"/>
       <c r="F21" s="25"/>
-      <c r="G21" s="201"/>
-      <c r="H21" s="202"/>
-      <c r="I21" s="205"/>
-      <c r="J21" s="206"/>
+      <c r="G21" s="183"/>
+      <c r="H21" s="184"/>
+      <c r="I21" s="177"/>
+      <c r="J21" s="178"/>
       <c r="K21" s="71"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5697,10 +4290,10 @@
       <c r="D22" s="70"/>
       <c r="E22" s="25"/>
       <c r="F22" s="25"/>
-      <c r="G22" s="201"/>
-      <c r="H22" s="202"/>
-      <c r="I22" s="205"/>
-      <c r="J22" s="206"/>
+      <c r="G22" s="183"/>
+      <c r="H22" s="184"/>
+      <c r="I22" s="177"/>
+      <c r="J22" s="178"/>
       <c r="K22" s="71"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5719,10 +4312,10 @@
       <c r="D23" s="70"/>
       <c r="E23" s="25"/>
       <c r="F23" s="25"/>
-      <c r="G23" s="201"/>
-      <c r="H23" s="202"/>
-      <c r="I23" s="205"/>
-      <c r="J23" s="206"/>
+      <c r="G23" s="183"/>
+      <c r="H23" s="184"/>
+      <c r="I23" s="177"/>
+      <c r="J23" s="178"/>
       <c r="K23" s="71"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5741,10 +4334,10 @@
       <c r="D24" s="70"/>
       <c r="E24" s="25"/>
       <c r="F24" s="25"/>
-      <c r="G24" s="201"/>
-      <c r="H24" s="202"/>
-      <c r="I24" s="205"/>
-      <c r="J24" s="206"/>
+      <c r="G24" s="183"/>
+      <c r="H24" s="184"/>
+      <c r="I24" s="177"/>
+      <c r="J24" s="178"/>
       <c r="K24" s="71"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5763,10 +4356,10 @@
       <c r="D25" s="70"/>
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
-      <c r="G25" s="201"/>
-      <c r="H25" s="202"/>
-      <c r="I25" s="205"/>
-      <c r="J25" s="206"/>
+      <c r="G25" s="183"/>
+      <c r="H25" s="184"/>
+      <c r="I25" s="177"/>
+      <c r="J25" s="178"/>
       <c r="K25" s="71"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5785,10 +4378,10 @@
       <c r="D26" s="70"/>
       <c r="E26" s="25"/>
       <c r="F26" s="25"/>
-      <c r="G26" s="201"/>
-      <c r="H26" s="202"/>
-      <c r="I26" s="205"/>
-      <c r="J26" s="206"/>
+      <c r="G26" s="183"/>
+      <c r="H26" s="184"/>
+      <c r="I26" s="177"/>
+      <c r="J26" s="178"/>
       <c r="K26" s="71"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5807,10 +4400,10 @@
       <c r="D27" s="70"/>
       <c r="E27" s="25"/>
       <c r="F27" s="25"/>
-      <c r="G27" s="201"/>
-      <c r="H27" s="202"/>
-      <c r="I27" s="205"/>
-      <c r="J27" s="206"/>
+      <c r="G27" s="183"/>
+      <c r="H27" s="184"/>
+      <c r="I27" s="177"/>
+      <c r="J27" s="178"/>
       <c r="K27" s="71"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5829,10 +4422,10 @@
       <c r="D28" s="70"/>
       <c r="E28" s="25"/>
       <c r="F28" s="25"/>
-      <c r="G28" s="201"/>
-      <c r="H28" s="202"/>
-      <c r="I28" s="205"/>
-      <c r="J28" s="206"/>
+      <c r="G28" s="183"/>
+      <c r="H28" s="184"/>
+      <c r="I28" s="177"/>
+      <c r="J28" s="178"/>
       <c r="K28" s="71"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5851,10 +4444,10 @@
       <c r="D29" s="70"/>
       <c r="E29" s="25"/>
       <c r="F29" s="25"/>
-      <c r="G29" s="201"/>
-      <c r="H29" s="202"/>
-      <c r="I29" s="205"/>
-      <c r="J29" s="206"/>
+      <c r="G29" s="183"/>
+      <c r="H29" s="184"/>
+      <c r="I29" s="177"/>
+      <c r="J29" s="178"/>
       <c r="K29" s="71"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5873,10 +4466,10 @@
       <c r="D30" s="70"/>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
-      <c r="G30" s="201"/>
-      <c r="H30" s="202"/>
-      <c r="I30" s="205"/>
-      <c r="J30" s="206"/>
+      <c r="G30" s="183"/>
+      <c r="H30" s="184"/>
+      <c r="I30" s="177"/>
+      <c r="J30" s="178"/>
       <c r="K30" s="71"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5895,10 +4488,10 @@
       <c r="D31" s="70"/>
       <c r="E31" s="25"/>
       <c r="F31" s="25"/>
-      <c r="G31" s="201"/>
-      <c r="H31" s="202"/>
-      <c r="I31" s="205"/>
-      <c r="J31" s="206"/>
+      <c r="G31" s="183"/>
+      <c r="H31" s="184"/>
+      <c r="I31" s="177"/>
+      <c r="J31" s="178"/>
       <c r="K31" s="71"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5917,10 +4510,10 @@
       <c r="D32" s="70"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
-      <c r="G32" s="201"/>
-      <c r="H32" s="202"/>
-      <c r="I32" s="205"/>
-      <c r="J32" s="206"/>
+      <c r="G32" s="183"/>
+      <c r="H32" s="184"/>
+      <c r="I32" s="177"/>
+      <c r="J32" s="178"/>
       <c r="K32" s="71"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5939,10 +4532,10 @@
       <c r="D33" s="70"/>
       <c r="E33" s="25"/>
       <c r="F33" s="25"/>
-      <c r="G33" s="201"/>
-      <c r="H33" s="202"/>
-      <c r="I33" s="205"/>
-      <c r="J33" s="206"/>
+      <c r="G33" s="183"/>
+      <c r="H33" s="184"/>
+      <c r="I33" s="177"/>
+      <c r="J33" s="178"/>
       <c r="K33" s="71"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5961,10 +4554,10 @@
       <c r="D34" s="70"/>
       <c r="E34" s="25"/>
       <c r="F34" s="25"/>
-      <c r="G34" s="201"/>
-      <c r="H34" s="202"/>
-      <c r="I34" s="205"/>
-      <c r="J34" s="206"/>
+      <c r="G34" s="183"/>
+      <c r="H34" s="184"/>
+      <c r="I34" s="177"/>
+      <c r="J34" s="178"/>
       <c r="K34" s="71"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5983,10 +4576,10 @@
       <c r="D35" s="70"/>
       <c r="E35" s="25"/>
       <c r="F35" s="25"/>
-      <c r="G35" s="201"/>
-      <c r="H35" s="202"/>
-      <c r="I35" s="205"/>
-      <c r="J35" s="206"/>
+      <c r="G35" s="183"/>
+      <c r="H35" s="184"/>
+      <c r="I35" s="177"/>
+      <c r="J35" s="178"/>
       <c r="K35" s="71"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6005,10 +4598,10 @@
       <c r="D36" s="70"/>
       <c r="E36" s="25"/>
       <c r="F36" s="25"/>
-      <c r="G36" s="201"/>
-      <c r="H36" s="202"/>
-      <c r="I36" s="205"/>
-      <c r="J36" s="206"/>
+      <c r="G36" s="183"/>
+      <c r="H36" s="184"/>
+      <c r="I36" s="177"/>
+      <c r="J36" s="178"/>
       <c r="K36" s="71"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6027,10 +4620,10 @@
       <c r="D37" s="70"/>
       <c r="E37" s="25"/>
       <c r="F37" s="25"/>
-      <c r="G37" s="201"/>
-      <c r="H37" s="202"/>
-      <c r="I37" s="205"/>
-      <c r="J37" s="206"/>
+      <c r="G37" s="183"/>
+      <c r="H37" s="184"/>
+      <c r="I37" s="177"/>
+      <c r="J37" s="178"/>
       <c r="K37" s="71"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6049,10 +4642,10 @@
       <c r="D38" s="70"/>
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
-      <c r="G38" s="201"/>
-      <c r="H38" s="202"/>
-      <c r="I38" s="205"/>
-      <c r="J38" s="206"/>
+      <c r="G38" s="183"/>
+      <c r="H38" s="184"/>
+      <c r="I38" s="177"/>
+      <c r="J38" s="178"/>
       <c r="K38" s="71"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6071,10 +4664,10 @@
       <c r="D39" s="70"/>
       <c r="E39" s="25"/>
       <c r="F39" s="25"/>
-      <c r="G39" s="201"/>
-      <c r="H39" s="202"/>
-      <c r="I39" s="205"/>
-      <c r="J39" s="206"/>
+      <c r="G39" s="183"/>
+      <c r="H39" s="184"/>
+      <c r="I39" s="177"/>
+      <c r="J39" s="178"/>
       <c r="K39" s="71"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6093,18 +4686,18 @@
       <c r="D40" s="70"/>
       <c r="E40" s="25"/>
       <c r="F40" s="25"/>
-      <c r="G40" s="200"/>
-      <c r="H40" s="200"/>
-      <c r="I40" s="205"/>
-      <c r="J40" s="206"/>
+      <c r="G40" s="211"/>
+      <c r="H40" s="211"/>
+      <c r="I40" s="177"/>
+      <c r="J40" s="178"/>
       <c r="K40" s="71"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="183" t="s">
+      <c r="A41" s="219" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="184"/>
-      <c r="C41" s="184"/>
+      <c r="B41" s="220"/>
+      <c r="C41" s="220"/>
       <c r="D41" s="79" t="e">
         <f>AVERAGE(D11:D40)</f>
         <v>#DIV/0!</v>
@@ -6117,27 +4710,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G41" s="197" t="e">
+      <c r="G41" s="208" t="e">
         <f>AVERAGE(G11:H40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="198"/>
-      <c r="I41" s="209" t="e">
+      <c r="H41" s="209"/>
+      <c r="I41" s="202" t="e">
         <f>AVERAGE(I11:J40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="210"/>
+      <c r="J41" s="203"/>
       <c r="K41" s="37" t="e">
         <f>AVERAGE(K11:K40)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="185" t="s">
+      <c r="A42" s="221" t="s">
         <v>31</v>
       </c>
-      <c r="B42" s="186"/>
-      <c r="C42" s="186"/>
+      <c r="B42" s="222"/>
+      <c r="C42" s="222"/>
       <c r="D42" s="80">
         <f>MIN(D11:D40)</f>
         <v>0</v>
@@ -6150,27 +4743,27 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G42" s="218">
+      <c r="G42" s="191">
         <f>MIN(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="219"/>
-      <c r="I42" s="203">
+      <c r="H42" s="192"/>
+      <c r="I42" s="196">
         <f>MIN(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="204"/>
+      <c r="J42" s="197"/>
       <c r="K42" s="40">
         <f>MIN(K11:K40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="179" t="s">
+      <c r="A43" s="216" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="180"/>
-      <c r="C43" s="180"/>
+      <c r="B43" s="217"/>
+      <c r="C43" s="217"/>
       <c r="D43" s="81">
         <f>MAX(D11:D40)</f>
         <v>0</v>
@@ -6183,16 +4776,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G43" s="216">
+      <c r="G43" s="189">
         <f>MAX(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="217"/>
-      <c r="I43" s="214">
+      <c r="H43" s="190"/>
+      <c r="I43" s="187">
         <f>MAX(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="215"/>
+      <c r="J43" s="188"/>
       <c r="K43" s="83">
         <f>MAX(K11:K40)</f>
         <v>0</v>
@@ -6202,8 +4795,8 @@
       <c r="A44" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="171"/>
-      <c r="C44" s="171"/>
+      <c r="B44" s="135"/>
+      <c r="C44" s="135"/>
       <c r="D44" s="44" t="s">
         <v>22</v>
       </c>
@@ -6220,8 +4813,8 @@
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="50"/>
-      <c r="B45" s="172"/>
-      <c r="C45" s="172"/>
+      <c r="B45" s="136"/>
+      <c r="C45" s="136"/>
       <c r="D45" s="44"/>
       <c r="F45" s="46"/>
       <c r="G45" s="47"/>
@@ -6230,11 +4823,11 @@
       <c r="J45" s="51"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="170" t="s">
+      <c r="A46" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="170"/>
-      <c r="C46" s="170"/>
+      <c r="B46" s="134"/>
+      <c r="C46" s="134"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="47" t="s">
@@ -6247,11 +4840,11 @@
       <c r="H46" s="44"/>
     </row>
     <row r="47" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="170" t="s">
+      <c r="A47" s="134" t="s">
         <v>134</v>
       </c>
-      <c r="B47" s="170"/>
-      <c r="C47" s="170"/>
+      <c r="B47" s="134"/>
+      <c r="C47" s="134"/>
       <c r="D47" s="44"/>
       <c r="E47" s="44"/>
       <c r="F47" s="44"/>
@@ -6306,6 +4899,84 @@
     </row>
   </sheetData>
   <mergeCells count="94">
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A7:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H10"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K7:K10"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="J5:K5"/>
@@ -6322,118 +4993,40 @@
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="G39:H39"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K7:K10"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H10"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A7:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="D11:D43">
-    <cfRule type="cellIs" dxfId="36" priority="8" operator="notBetween">
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="notBetween">
       <formula>700</formula>
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11:E43">
-    <cfRule type="cellIs" dxfId="35" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:F43">
-    <cfRule type="cellIs" dxfId="34" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="lessThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:H19 G20:G39 G40:H43">
-    <cfRule type="cellIs" dxfId="33" priority="4" operator="notBetween">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="notBetween">
       <formula>45</formula>
       <formula>55</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I11:J43">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="notBetween">
+      <formula>290</formula>
+      <formula>293</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K11:K43">
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="notBetween">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="notBetween">
       <formula>410</formula>
       <formula>450</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I11:J43">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="notBetween">
-      <formula>290</formula>
-      <formula>293</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.11811023622047245" bottom="0.11811023622047245" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6455,35 +5048,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
+      <c r="B1" s="158"/>
+      <c r="C1" s="158"/>
+      <c r="D1" s="158"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="158"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="158" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -6504,18 +5097,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="144" t="s">
+      <c r="A4" s="159" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="145">
+      <c r="B4" s="160">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="220">
+      <c r="C4" s="185">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="182"/>
+      <c r="D4" s="186"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -6533,25 +5126,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="221">
+      <c r="J4" s="173">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="222"/>
+      <c r="K4" s="174"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="148" t="s">
+      <c r="A5" s="163" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="149">
+      <c r="B5" s="164">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="150">
+      <c r="C5" s="165">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="151"/>
+      <c r="D5" s="166"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -6569,81 +5162,81 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="223">
+      <c r="J5" s="175">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="224"/>
+      <c r="K5" s="176"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="156" t="s">
+      <c r="A6" s="170" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="157"/>
-      <c r="C6" s="235"/>
-      <c r="D6" s="236"/>
-      <c r="E6" s="135"/>
-      <c r="F6" s="135"/>
-      <c r="G6" s="155"/>
+      <c r="B6" s="171"/>
+      <c r="C6" s="227"/>
+      <c r="D6" s="228"/>
+      <c r="E6" s="151"/>
+      <c r="F6" s="151"/>
+      <c r="G6" s="169"/>
       <c r="H6" s="119"/>
-      <c r="I6" s="176"/>
-      <c r="J6" s="177"/>
-      <c r="K6" s="211"/>
+      <c r="I6" s="215"/>
+      <c r="J6" s="204"/>
+      <c r="K6" s="193"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="176" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="177"/>
-      <c r="C7" s="211"/>
-      <c r="D7" s="181" t="s">
+      <c r="A7" s="215" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="204"/>
+      <c r="C7" s="193"/>
+      <c r="D7" s="218" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="237"/>
-      <c r="F7" s="237"/>
-      <c r="G7" s="182"/>
-      <c r="H7" s="227" t="s">
+      <c r="E7" s="229"/>
+      <c r="F7" s="229"/>
+      <c r="G7" s="186"/>
+      <c r="H7" s="233" t="s">
         <v>130</v>
       </c>
-      <c r="I7" s="187"/>
-      <c r="J7" s="188"/>
-      <c r="K7" s="212"/>
+      <c r="I7" s="223"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="194"/>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="187"/>
-      <c r="B8" s="188"/>
-      <c r="C8" s="212"/>
-      <c r="D8" s="233" t="s">
+      <c r="A8" s="223"/>
+      <c r="B8" s="205"/>
+      <c r="C8" s="194"/>
+      <c r="D8" s="239" t="s">
         <v>127</v>
       </c>
-      <c r="E8" s="190" t="s">
+      <c r="E8" s="225" t="s">
         <v>128</v>
       </c>
-      <c r="F8" s="190" t="s">
+      <c r="F8" s="225" t="s">
         <v>131</v>
       </c>
-      <c r="G8" s="190" t="s">
+      <c r="G8" s="225" t="s">
         <v>129</v>
       </c>
-      <c r="H8" s="228" t="s">
+      <c r="H8" s="234" t="s">
         <v>130</v>
       </c>
-      <c r="I8" s="187"/>
-      <c r="J8" s="188"/>
-      <c r="K8" s="212"/>
+      <c r="I8" s="223"/>
+      <c r="J8" s="205"/>
+      <c r="K8" s="194"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="189"/>
-      <c r="B9" s="196"/>
-      <c r="C9" s="213"/>
-      <c r="D9" s="234"/>
-      <c r="E9" s="153"/>
-      <c r="F9" s="153"/>
-      <c r="G9" s="153"/>
-      <c r="H9" s="229"/>
-      <c r="I9" s="187"/>
-      <c r="J9" s="188"/>
-      <c r="K9" s="212"/>
+      <c r="A9" s="224"/>
+      <c r="B9" s="207"/>
+      <c r="C9" s="195"/>
+      <c r="D9" s="240"/>
+      <c r="E9" s="168"/>
+      <c r="F9" s="168"/>
+      <c r="G9" s="168"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="223"/>
+      <c r="J9" s="205"/>
+      <c r="K9" s="194"/>
     </row>
     <row r="10" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="62">
@@ -6663,9 +5256,9 @@
       <c r="F10" s="23"/>
       <c r="G10" s="121"/>
       <c r="H10" s="122"/>
-      <c r="I10" s="187"/>
-      <c r="J10" s="188"/>
-      <c r="K10" s="212"/>
+      <c r="I10" s="223"/>
+      <c r="J10" s="205"/>
+      <c r="K10" s="194"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="67">
@@ -6685,9 +5278,9 @@
       <c r="F11" s="26"/>
       <c r="G11" s="124"/>
       <c r="H11" s="125"/>
-      <c r="I11" s="187"/>
-      <c r="J11" s="188"/>
-      <c r="K11" s="212"/>
+      <c r="I11" s="223"/>
+      <c r="J11" s="205"/>
+      <c r="K11" s="194"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="67">
@@ -6707,9 +5300,9 @@
       <c r="F12" s="26"/>
       <c r="G12" s="124"/>
       <c r="H12" s="125"/>
-      <c r="I12" s="187"/>
-      <c r="J12" s="188"/>
-      <c r="K12" s="212"/>
+      <c r="I12" s="223"/>
+      <c r="J12" s="205"/>
+      <c r="K12" s="194"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="67">
@@ -6729,9 +5322,9 @@
       <c r="F13" s="23"/>
       <c r="G13" s="121"/>
       <c r="H13" s="125"/>
-      <c r="I13" s="187"/>
-      <c r="J13" s="188"/>
-      <c r="K13" s="212"/>
+      <c r="I13" s="223"/>
+      <c r="J13" s="205"/>
+      <c r="K13" s="194"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="67">
@@ -6751,9 +5344,9 @@
       <c r="F14" s="26"/>
       <c r="G14" s="124"/>
       <c r="H14" s="125"/>
-      <c r="I14" s="187"/>
-      <c r="J14" s="188"/>
-      <c r="K14" s="212"/>
+      <c r="I14" s="223"/>
+      <c r="J14" s="205"/>
+      <c r="K14" s="194"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="67">
@@ -6773,9 +5366,9 @@
       <c r="F15" s="26"/>
       <c r="G15" s="124"/>
       <c r="H15" s="125"/>
-      <c r="I15" s="187"/>
-      <c r="J15" s="188"/>
-      <c r="K15" s="212"/>
+      <c r="I15" s="223"/>
+      <c r="J15" s="205"/>
+      <c r="K15" s="194"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="67">
@@ -6795,9 +5388,9 @@
       <c r="F16" s="26"/>
       <c r="G16" s="124"/>
       <c r="H16" s="125"/>
-      <c r="I16" s="187"/>
-      <c r="J16" s="188"/>
-      <c r="K16" s="212"/>
+      <c r="I16" s="223"/>
+      <c r="J16" s="205"/>
+      <c r="K16" s="194"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="67">
@@ -6817,9 +5410,9 @@
       <c r="F17" s="26"/>
       <c r="G17" s="124"/>
       <c r="H17" s="125"/>
-      <c r="I17" s="187"/>
-      <c r="J17" s="188"/>
-      <c r="K17" s="212"/>
+      <c r="I17" s="223"/>
+      <c r="J17" s="205"/>
+      <c r="K17" s="194"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="67">
@@ -6839,9 +5432,9 @@
       <c r="F18" s="26"/>
       <c r="G18" s="124"/>
       <c r="H18" s="125"/>
-      <c r="I18" s="187"/>
-      <c r="J18" s="188"/>
-      <c r="K18" s="212"/>
+      <c r="I18" s="223"/>
+      <c r="J18" s="205"/>
+      <c r="K18" s="194"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="67">
@@ -6861,9 +5454,9 @@
       <c r="F19" s="26"/>
       <c r="G19" s="124"/>
       <c r="H19" s="125"/>
-      <c r="I19" s="187"/>
-      <c r="J19" s="188"/>
-      <c r="K19" s="212"/>
+      <c r="I19" s="223"/>
+      <c r="J19" s="205"/>
+      <c r="K19" s="194"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="75">
@@ -6883,9 +5476,9 @@
       <c r="F20" s="26"/>
       <c r="G20" s="124"/>
       <c r="H20" s="125"/>
-      <c r="I20" s="187"/>
-      <c r="J20" s="188"/>
-      <c r="K20" s="212"/>
+      <c r="I20" s="223"/>
+      <c r="J20" s="205"/>
+      <c r="K20" s="194"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="67">
@@ -6905,9 +5498,9 @@
       <c r="F21" s="26"/>
       <c r="G21" s="124"/>
       <c r="H21" s="125"/>
-      <c r="I21" s="187"/>
-      <c r="J21" s="188"/>
-      <c r="K21" s="212"/>
+      <c r="I21" s="223"/>
+      <c r="J21" s="205"/>
+      <c r="K21" s="194"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="67">
@@ -6927,9 +5520,9 @@
       <c r="F22" s="26"/>
       <c r="G22" s="124"/>
       <c r="H22" s="125"/>
-      <c r="I22" s="187"/>
-      <c r="J22" s="188"/>
-      <c r="K22" s="212"/>
+      <c r="I22" s="223"/>
+      <c r="J22" s="205"/>
+      <c r="K22" s="194"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="67">
@@ -6949,9 +5542,9 @@
       <c r="F23" s="26"/>
       <c r="G23" s="124"/>
       <c r="H23" s="125"/>
-      <c r="I23" s="187"/>
-      <c r="J23" s="188"/>
-      <c r="K23" s="212"/>
+      <c r="I23" s="223"/>
+      <c r="J23" s="205"/>
+      <c r="K23" s="194"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="67">
@@ -6971,9 +5564,9 @@
       <c r="F24" s="26"/>
       <c r="G24" s="124"/>
       <c r="H24" s="125"/>
-      <c r="I24" s="187"/>
-      <c r="J24" s="188"/>
-      <c r="K24" s="212"/>
+      <c r="I24" s="223"/>
+      <c r="J24" s="205"/>
+      <c r="K24" s="194"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="67">
@@ -6993,9 +5586,9 @@
       <c r="F25" s="26"/>
       <c r="G25" s="124"/>
       <c r="H25" s="125"/>
-      <c r="I25" s="187"/>
-      <c r="J25" s="188"/>
-      <c r="K25" s="212"/>
+      <c r="I25" s="223"/>
+      <c r="J25" s="205"/>
+      <c r="K25" s="194"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="67">
@@ -7015,9 +5608,9 @@
       <c r="F26" s="26"/>
       <c r="G26" s="124"/>
       <c r="H26" s="125"/>
-      <c r="I26" s="187"/>
-      <c r="J26" s="188"/>
-      <c r="K26" s="212"/>
+      <c r="I26" s="223"/>
+      <c r="J26" s="205"/>
+      <c r="K26" s="194"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="67">
@@ -7037,9 +5630,9 @@
       <c r="F27" s="26"/>
       <c r="G27" s="124"/>
       <c r="H27" s="125"/>
-      <c r="I27" s="187"/>
-      <c r="J27" s="188"/>
-      <c r="K27" s="212"/>
+      <c r="I27" s="223"/>
+      <c r="J27" s="205"/>
+      <c r="K27" s="194"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="67">
@@ -7059,9 +5652,9 @@
       <c r="F28" s="26"/>
       <c r="G28" s="124"/>
       <c r="H28" s="125"/>
-      <c r="I28" s="187"/>
-      <c r="J28" s="188"/>
-      <c r="K28" s="212"/>
+      <c r="I28" s="223"/>
+      <c r="J28" s="205"/>
+      <c r="K28" s="194"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="67">
@@ -7081,9 +5674,9 @@
       <c r="F29" s="26"/>
       <c r="G29" s="124"/>
       <c r="H29" s="125"/>
-      <c r="I29" s="187"/>
-      <c r="J29" s="188"/>
-      <c r="K29" s="212"/>
+      <c r="I29" s="223"/>
+      <c r="J29" s="205"/>
+      <c r="K29" s="194"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="75">
@@ -7103,9 +5696,9 @@
       <c r="F30" s="26"/>
       <c r="G30" s="124"/>
       <c r="H30" s="125"/>
-      <c r="I30" s="187"/>
-      <c r="J30" s="188"/>
-      <c r="K30" s="212"/>
+      <c r="I30" s="223"/>
+      <c r="J30" s="205"/>
+      <c r="K30" s="194"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="67">
@@ -7125,9 +5718,9 @@
       <c r="F31" s="26"/>
       <c r="G31" s="124"/>
       <c r="H31" s="125"/>
-      <c r="I31" s="187"/>
-      <c r="J31" s="188"/>
-      <c r="K31" s="212"/>
+      <c r="I31" s="223"/>
+      <c r="J31" s="205"/>
+      <c r="K31" s="194"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="67">
@@ -7147,9 +5740,9 @@
       <c r="F32" s="26"/>
       <c r="G32" s="124"/>
       <c r="H32" s="125"/>
-      <c r="I32" s="187"/>
-      <c r="J32" s="188"/>
-      <c r="K32" s="212"/>
+      <c r="I32" s="223"/>
+      <c r="J32" s="205"/>
+      <c r="K32" s="194"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="67">
@@ -7169,9 +5762,9 @@
       <c r="F33" s="26"/>
       <c r="G33" s="124"/>
       <c r="H33" s="125"/>
-      <c r="I33" s="187"/>
-      <c r="J33" s="188"/>
-      <c r="K33" s="212"/>
+      <c r="I33" s="223"/>
+      <c r="J33" s="205"/>
+      <c r="K33" s="194"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="67">
@@ -7191,9 +5784,9 @@
       <c r="F34" s="26"/>
       <c r="G34" s="124"/>
       <c r="H34" s="125"/>
-      <c r="I34" s="187"/>
-      <c r="J34" s="188"/>
-      <c r="K34" s="212"/>
+      <c r="I34" s="223"/>
+      <c r="J34" s="205"/>
+      <c r="K34" s="194"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="67">
@@ -7213,9 +5806,9 @@
       <c r="F35" s="26"/>
       <c r="G35" s="124"/>
       <c r="H35" s="125"/>
-      <c r="I35" s="187"/>
-      <c r="J35" s="188"/>
-      <c r="K35" s="212"/>
+      <c r="I35" s="223"/>
+      <c r="J35" s="205"/>
+      <c r="K35" s="194"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="67">
@@ -7235,9 +5828,9 @@
       <c r="F36" s="26"/>
       <c r="G36" s="124"/>
       <c r="H36" s="125"/>
-      <c r="I36" s="187"/>
-      <c r="J36" s="188"/>
-      <c r="K36" s="212"/>
+      <c r="I36" s="223"/>
+      <c r="J36" s="205"/>
+      <c r="K36" s="194"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="67">
@@ -7257,9 +5850,9 @@
       <c r="F37" s="26"/>
       <c r="G37" s="124"/>
       <c r="H37" s="125"/>
-      <c r="I37" s="187"/>
-      <c r="J37" s="188"/>
-      <c r="K37" s="212"/>
+      <c r="I37" s="223"/>
+      <c r="J37" s="205"/>
+      <c r="K37" s="194"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="67">
@@ -7279,9 +5872,9 @@
       <c r="F38" s="26"/>
       <c r="G38" s="124"/>
       <c r="H38" s="125"/>
-      <c r="I38" s="187"/>
-      <c r="J38" s="188"/>
-      <c r="K38" s="212"/>
+      <c r="I38" s="223"/>
+      <c r="J38" s="205"/>
+      <c r="K38" s="194"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="76">
@@ -7301,16 +5894,16 @@
       <c r="F39" s="26"/>
       <c r="G39" s="124"/>
       <c r="H39" s="125"/>
-      <c r="I39" s="187"/>
-      <c r="J39" s="188"/>
-      <c r="K39" s="212"/>
+      <c r="I39" s="223"/>
+      <c r="J39" s="205"/>
+      <c r="K39" s="194"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="238" t="s">
+      <c r="A40" s="230" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="239"/>
-      <c r="C40" s="240"/>
+      <c r="B40" s="231"/>
+      <c r="C40" s="232"/>
       <c r="D40" s="126" t="e">
         <f>AVERAGE(D10:D39)</f>
         <v>#DIV/0!</v>
@@ -7331,16 +5924,16 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I40" s="187"/>
-      <c r="J40" s="188"/>
-      <c r="K40" s="212"/>
+      <c r="I40" s="223"/>
+      <c r="J40" s="205"/>
+      <c r="K40" s="194"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="164" t="s">
+      <c r="A41" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="165"/>
-      <c r="C41" s="166"/>
+      <c r="B41" s="145"/>
+      <c r="C41" s="146"/>
       <c r="D41" s="128">
         <f>MIN(D10:D39)</f>
         <v>0</v>
@@ -7361,16 +5954,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I41" s="187"/>
-      <c r="J41" s="188"/>
-      <c r="K41" s="212"/>
+      <c r="I41" s="223"/>
+      <c r="J41" s="205"/>
+      <c r="K41" s="194"/>
     </row>
     <row r="42" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="230" t="s">
+      <c r="A42" s="236" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="231"/>
-      <c r="C42" s="232"/>
+      <c r="B42" s="237"/>
+      <c r="C42" s="238"/>
       <c r="D42" s="130">
         <f>MAX(D10:D39)</f>
         <v>0</v>
@@ -7391,16 +5984,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I42" s="189"/>
-      <c r="J42" s="196"/>
-      <c r="K42" s="213"/>
+      <c r="I42" s="224"/>
+      <c r="J42" s="207"/>
+      <c r="K42" s="195"/>
     </row>
     <row r="43" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="171"/>
-      <c r="C43" s="171"/>
+      <c r="B43" s="135"/>
+      <c r="C43" s="135"/>
       <c r="D43" s="44" t="s">
         <v>22</v>
       </c>
@@ -7417,8 +6010,8 @@
     </row>
     <row r="44" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="50"/>
-      <c r="B44" s="172"/>
-      <c r="C44" s="172"/>
+      <c r="B44" s="136"/>
+      <c r="C44" s="136"/>
       <c r="D44" s="44"/>
       <c r="F44" s="46"/>
       <c r="G44" s="47"/>
@@ -7427,11 +6020,11 @@
       <c r="J44" s="51"/>
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="170" t="s">
+      <c r="A45" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="170"/>
-      <c r="C45" s="170"/>
+      <c r="B45" s="134"/>
+      <c r="C45" s="134"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="47" t="s">
@@ -7444,11 +6037,11 @@
       <c r="H45" s="44"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="170" t="s">
+      <c r="A46" s="134" t="s">
         <v>134</v>
       </c>
-      <c r="B46" s="170"/>
-      <c r="C46" s="170"/>
+      <c r="B46" s="134"/>
+      <c r="C46" s="134"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="44"/>
@@ -7473,6 +6066,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A7:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="J4:K4"/>
@@ -7489,36 +6091,27 @@
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="A40:C40"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A7:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
   </mergeCells>
   <conditionalFormatting sqref="D10:D42">
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="notBetween">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="notBetween">
       <formula>53</formula>
       <formula>65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10:E42">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="notBetween">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="notBetween">
       <formula>31</formula>
       <formula>41</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F42">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="notBetween">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="notBetween">
       <formula>-28</formula>
       <formula>-20</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:H42">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="notBetween">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="notBetween">
       <formula>0</formula>
       <formula>4</formula>
     </cfRule>
@@ -7544,15 +6137,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="241" t="s">
+      <c r="A1" s="304" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="242"/>
-      <c r="C1" s="242"/>
-      <c r="D1" s="242"/>
-      <c r="E1" s="242"/>
-      <c r="F1" s="242"/>
-      <c r="G1" s="243"/>
+      <c r="B1" s="305"/>
+      <c r="C1" s="305"/>
+      <c r="D1" s="305"/>
+      <c r="E1" s="305"/>
+      <c r="F1" s="305"/>
+      <c r="G1" s="306"/>
     </row>
     <row r="2" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="87"/>
@@ -7566,37 +6159,37 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="292" t="s">
+      <c r="A3" s="242" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="293"/>
-      <c r="C3" s="293"/>
-      <c r="D3" s="293"/>
-      <c r="E3" s="293"/>
-      <c r="F3" s="293"/>
-      <c r="G3" s="294"/>
+      <c r="B3" s="243"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="244"/>
     </row>
     <row r="4" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="187" t="s">
+      <c r="A4" s="223" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="188"/>
-      <c r="C4" s="188"/>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="212"/>
+      <c r="B4" s="205"/>
+      <c r="C4" s="205"/>
+      <c r="D4" s="205"/>
+      <c r="E4" s="205"/>
+      <c r="F4" s="205"/>
+      <c r="G4" s="194"/>
     </row>
     <row r="5" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="244" t="s">
+      <c r="A5" s="307" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="245"/>
-      <c r="C5" s="245"/>
-      <c r="D5" s="245"/>
-      <c r="E5" s="245"/>
-      <c r="F5" s="245"/>
-      <c r="G5" s="246"/>
+      <c r="B5" s="308"/>
+      <c r="C5" s="308"/>
+      <c r="D5" s="308"/>
+      <c r="E5" s="308"/>
+      <c r="F5" s="308"/>
+      <c r="G5" s="309"/>
     </row>
     <row r="6" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="90" t="s">
@@ -7608,14 +6201,15 @@
       <c r="C6" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="247" t="s">
-        <v>141</v>
-      </c>
-      <c r="E6" s="248"/>
-      <c r="F6" s="249" t="s">
+      <c r="D6" s="263">
+        <f>Page1!H4</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="265"/>
+      <c r="F6" s="284" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="250">
+      <c r="G6" s="288">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
@@ -7628,13 +6222,13 @@
       <c r="C7" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="247">
+      <c r="D7" s="263">
         <f>Page1!F5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="248"/>
-      <c r="F7" s="249"/>
-      <c r="G7" s="251"/>
+      <c r="E7" s="265"/>
+      <c r="F7" s="284"/>
+      <c r="G7" s="310"/>
     </row>
     <row r="8" spans="1:7" s="86" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="90" t="s">
@@ -7647,15 +6241,15 @@
       <c r="C8" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="249">
+      <c r="D8" s="284">
         <f>Page1!H5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="249"/>
-      <c r="F8" s="261" t="s">
+      <c r="E8" s="284"/>
+      <c r="F8" s="285" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="250">
+      <c r="G8" s="288">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
@@ -7668,15 +6262,15 @@
         <f>Page1!G44</f>
         <v>461347000</v>
       </c>
-      <c r="C9" s="261" t="s">
+      <c r="C9" s="285" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="266" t="s">
+      <c r="D9" s="291" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="267"/>
-      <c r="F9" s="262"/>
-      <c r="G9" s="264"/>
+      <c r="E9" s="292"/>
+      <c r="F9" s="286"/>
+      <c r="G9" s="289"/>
     </row>
     <row r="10" spans="1:7" s="86" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="97" t="s">
@@ -7686,34 +6280,34 @@
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="C10" s="263"/>
-      <c r="D10" s="268"/>
-      <c r="E10" s="269"/>
-      <c r="F10" s="263"/>
-      <c r="G10" s="265"/>
+      <c r="C10" s="287"/>
+      <c r="D10" s="293"/>
+      <c r="E10" s="294"/>
+      <c r="F10" s="287"/>
+      <c r="G10" s="290"/>
     </row>
     <row r="11" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="252" t="s">
+      <c r="A11" s="295" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="254" t="s">
+      <c r="B11" s="297" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="256" t="s">
+      <c r="C11" s="299" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="257"/>
-      <c r="E11" s="258"/>
-      <c r="F11" s="254" t="s">
+      <c r="D11" s="300"/>
+      <c r="E11" s="301"/>
+      <c r="F11" s="297" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="259" t="s">
+      <c r="G11" s="302" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="253"/>
-      <c r="B12" s="255"/>
+      <c r="A12" s="296"/>
+      <c r="B12" s="298"/>
       <c r="C12" s="99" t="s">
         <v>63</v>
       </c>
@@ -7723,8 +6317,8 @@
       <c r="E12" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="255"/>
-      <c r="G12" s="260"/>
+      <c r="F12" s="298"/>
+      <c r="G12" s="303"/>
     </row>
     <row r="13" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="100" t="s">
@@ -7794,7 +6388,7 @@
         <f>Page1!K39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="270" t="s">
+      <c r="G15" s="280" t="s">
         <v>74</v>
       </c>
     </row>
@@ -7818,7 +6412,7 @@
         <f>Page2!F41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="228"/>
+      <c r="G16" s="234"/>
     </row>
     <row r="17" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="104" t="s">
@@ -7840,7 +6434,7 @@
         <f>Page1!I39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="228"/>
+      <c r="G17" s="234"/>
     </row>
     <row r="18" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="104" t="s">
@@ -7862,7 +6456,7 @@
         <f>Page2!D41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="228"/>
+      <c r="G18" s="234"/>
     </row>
     <row r="19" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="104" t="s">
@@ -7884,7 +6478,7 @@
         <f>Page1!J39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="228"/>
+      <c r="G19" s="234"/>
     </row>
     <row r="20" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="104" t="s">
@@ -7906,7 +6500,7 @@
         <f>Page2!E41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="228"/>
+      <c r="G20" s="234"/>
     </row>
     <row r="21" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="104" t="s">
@@ -7928,7 +6522,7 @@
         <f>Page1!G39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="228"/>
+      <c r="G21" s="234"/>
     </row>
     <row r="22" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="104" t="s">
@@ -7950,7 +6544,7 @@
         <f>Page1!H39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="138"/>
+      <c r="G22" s="153"/>
     </row>
     <row r="23" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="104" t="s">
@@ -8050,26 +6644,26 @@
       </c>
     </row>
     <row r="27" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="271" t="s">
+      <c r="A27" s="277" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="272"/>
-      <c r="C27" s="272"/>
-      <c r="D27" s="272"/>
-      <c r="E27" s="272"/>
-      <c r="F27" s="272"/>
-      <c r="G27" s="273"/>
+      <c r="B27" s="278"/>
+      <c r="C27" s="278"/>
+      <c r="D27" s="278"/>
+      <c r="E27" s="278"/>
+      <c r="F27" s="278"/>
+      <c r="G27" s="279"/>
     </row>
     <row r="28" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="274" t="s">
+      <c r="A28" s="261" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="275"/>
-      <c r="C28" s="276" t="s">
+      <c r="B28" s="262"/>
+      <c r="C28" s="281" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="277"/>
-      <c r="E28" s="278"/>
+      <c r="D28" s="282"/>
+      <c r="E28" s="283"/>
       <c r="F28" s="113" t="s">
         <v>95</v>
       </c>
@@ -8078,15 +6672,15 @@
       </c>
     </row>
     <row r="29" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="279" t="s">
+      <c r="A29" s="266" t="s">
         <v>97</v>
       </c>
-      <c r="B29" s="248"/>
-      <c r="C29" s="280" t="s">
+      <c r="B29" s="265"/>
+      <c r="C29" s="271" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="281"/>
-      <c r="E29" s="282"/>
+      <c r="D29" s="272"/>
+      <c r="E29" s="273"/>
       <c r="F29" s="80" t="s">
         <v>95</v>
       </c>
@@ -8095,15 +6689,15 @@
       </c>
     </row>
     <row r="30" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="279" t="s">
+      <c r="A30" s="266" t="s">
         <v>100</v>
       </c>
-      <c r="B30" s="248"/>
-      <c r="C30" s="280" t="s">
+      <c r="B30" s="265"/>
+      <c r="C30" s="271" t="s">
         <v>101</v>
       </c>
-      <c r="D30" s="281"/>
-      <c r="E30" s="282"/>
+      <c r="D30" s="272"/>
+      <c r="E30" s="273"/>
       <c r="F30" s="80" t="s">
         <v>95</v>
       </c>
@@ -8112,15 +6706,15 @@
       </c>
     </row>
     <row r="31" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="279" t="s">
+      <c r="A31" s="266" t="s">
         <v>102</v>
       </c>
-      <c r="B31" s="248"/>
-      <c r="C31" s="280" t="s">
+      <c r="B31" s="265"/>
+      <c r="C31" s="271" t="s">
         <v>103</v>
       </c>
-      <c r="D31" s="281"/>
-      <c r="E31" s="282"/>
+      <c r="D31" s="272"/>
+      <c r="E31" s="273"/>
       <c r="F31" s="80" t="s">
         <v>95</v>
       </c>
@@ -8129,15 +6723,15 @@
       </c>
     </row>
     <row r="32" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="279" t="s">
+      <c r="A32" s="266" t="s">
         <v>105</v>
       </c>
-      <c r="B32" s="248"/>
-      <c r="C32" s="280" t="s">
+      <c r="B32" s="265"/>
+      <c r="C32" s="271" t="s">
         <v>106</v>
       </c>
-      <c r="D32" s="281"/>
-      <c r="E32" s="282"/>
+      <c r="D32" s="272"/>
+      <c r="E32" s="273"/>
       <c r="F32" s="80" t="s">
         <v>95</v>
       </c>
@@ -8146,15 +6740,15 @@
       </c>
     </row>
     <row r="33" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="279" t="s">
+      <c r="A33" s="266" t="s">
         <v>107</v>
       </c>
-      <c r="B33" s="248"/>
-      <c r="C33" s="280" t="s">
+      <c r="B33" s="265"/>
+      <c r="C33" s="271" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="281"/>
-      <c r="E33" s="282"/>
+      <c r="D33" s="272"/>
+      <c r="E33" s="273"/>
       <c r="F33" s="80" t="s">
         <v>95</v>
       </c>
@@ -8163,15 +6757,15 @@
       </c>
     </row>
     <row r="34" spans="1:7" s="86" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="163" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="149"/>
-      <c r="C34" s="283" t="s">
+      <c r="B34" s="164"/>
+      <c r="C34" s="274" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="284"/>
-      <c r="E34" s="285"/>
+      <c r="D34" s="275"/>
+      <c r="E34" s="276"/>
       <c r="F34" s="114" t="s">
         <v>95</v>
       </c>
@@ -8180,26 +6774,26 @@
       </c>
     </row>
     <row r="35" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="271" t="s">
+      <c r="A35" s="277" t="s">
         <v>112</v>
       </c>
-      <c r="B35" s="272"/>
-      <c r="C35" s="272"/>
-      <c r="D35" s="272"/>
-      <c r="E35" s="272"/>
-      <c r="F35" s="272"/>
-      <c r="G35" s="273"/>
+      <c r="B35" s="278"/>
+      <c r="C35" s="278"/>
+      <c r="D35" s="278"/>
+      <c r="E35" s="278"/>
+      <c r="F35" s="278"/>
+      <c r="G35" s="279"/>
     </row>
     <row r="36" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="144" t="s">
+      <c r="A36" s="159" t="s">
         <v>113</v>
       </c>
-      <c r="B36" s="145"/>
-      <c r="C36" s="289" t="s">
+      <c r="B36" s="160"/>
+      <c r="C36" s="269" t="s">
         <v>101</v>
       </c>
-      <c r="D36" s="290"/>
-      <c r="E36" s="145"/>
+      <c r="D36" s="270"/>
+      <c r="E36" s="160"/>
       <c r="F36" s="10" t="s">
         <v>95</v>
       </c>
@@ -8208,15 +6802,15 @@
       </c>
     </row>
     <row r="37" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="274" t="s">
+      <c r="A37" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="B37" s="275"/>
-      <c r="C37" s="247" t="s">
+      <c r="B37" s="262"/>
+      <c r="C37" s="263" t="s">
         <v>115</v>
       </c>
-      <c r="D37" s="286"/>
-      <c r="E37" s="248"/>
+      <c r="D37" s="264"/>
+      <c r="E37" s="265"/>
       <c r="F37" s="106" t="s">
         <v>95</v>
       </c>
@@ -8225,15 +6819,15 @@
       </c>
     </row>
     <row r="38" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="279" t="s">
+      <c r="A38" s="266" t="s">
         <v>116</v>
       </c>
-      <c r="B38" s="248"/>
-      <c r="C38" s="247" t="s">
+      <c r="B38" s="265"/>
+      <c r="C38" s="263" t="s">
         <v>117</v>
       </c>
-      <c r="D38" s="286"/>
-      <c r="E38" s="248"/>
+      <c r="D38" s="264"/>
+      <c r="E38" s="265"/>
       <c r="F38" s="106" t="s">
         <v>95</v>
       </c>
@@ -8242,15 +6836,15 @@
       </c>
     </row>
     <row r="39" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="148" t="s">
+      <c r="A39" s="163" t="s">
         <v>118</v>
       </c>
-      <c r="B39" s="149"/>
-      <c r="C39" s="287" t="s">
+      <c r="B39" s="164"/>
+      <c r="C39" s="267" t="s">
         <v>119</v>
       </c>
-      <c r="D39" s="288"/>
-      <c r="E39" s="149"/>
+      <c r="D39" s="268"/>
+      <c r="E39" s="164"/>
       <c r="F39" s="1" t="s">
         <v>95</v>
       </c>
@@ -8259,50 +6853,50 @@
       </c>
     </row>
     <row r="40" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="295" t="s">
+      <c r="A40" s="245" t="s">
         <v>120</v>
       </c>
-      <c r="B40" s="296"/>
-      <c r="C40" s="297" t="s">
+      <c r="B40" s="246"/>
+      <c r="C40" s="247" t="s">
         <v>137</v>
       </c>
-      <c r="D40" s="298"/>
-      <c r="E40" s="299"/>
-      <c r="F40" s="297" t="s">
+      <c r="D40" s="248"/>
+      <c r="E40" s="249"/>
+      <c r="F40" s="247" t="s">
         <v>138</v>
       </c>
-      <c r="G40" s="299"/>
+      <c r="G40" s="249"/>
     </row>
     <row r="41" spans="1:7" s="86" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="300"/>
-      <c r="B41" s="301"/>
-      <c r="C41" s="187"/>
-      <c r="D41" s="188"/>
-      <c r="E41" s="212"/>
-      <c r="F41" s="304"/>
-      <c r="G41" s="305"/>
+      <c r="A41" s="250"/>
+      <c r="B41" s="251"/>
+      <c r="C41" s="223"/>
+      <c r="D41" s="205"/>
+      <c r="E41" s="194"/>
+      <c r="F41" s="254"/>
+      <c r="G41" s="255"/>
     </row>
     <row r="42" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="302"/>
-      <c r="B42" s="303"/>
-      <c r="C42" s="306" t="s">
+      <c r="A42" s="252"/>
+      <c r="B42" s="253"/>
+      <c r="C42" s="256" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="307"/>
-      <c r="E42" s="308"/>
-      <c r="F42" s="306" t="s">
+      <c r="D42" s="257"/>
+      <c r="E42" s="258"/>
+      <c r="F42" s="256" t="s">
         <v>139</v>
       </c>
-      <c r="G42" s="308"/>
+      <c r="G42" s="258"/>
     </row>
     <row r="43" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="115"/>
       <c r="B43" s="115"/>
       <c r="C43" s="115"/>
       <c r="D43" s="115"/>
-      <c r="E43" s="309"/>
-      <c r="F43" s="309"/>
-      <c r="G43" s="309"/>
+      <c r="E43" s="259"/>
+      <c r="F43" s="259"/>
+      <c r="G43" s="259"/>
     </row>
     <row r="44" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="46" t="s">
@@ -8311,25 +6905,64 @@
       <c r="B44" s="116"/>
       <c r="C44" s="117"/>
       <c r="D44" s="115"/>
-      <c r="E44" s="310"/>
-      <c r="F44" s="310"/>
-      <c r="G44" s="310"/>
+      <c r="E44" s="260"/>
+      <c r="F44" s="260"/>
+      <c r="G44" s="260"/>
     </row>
     <row r="45" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="291" t="s">
+      <c r="A46" s="241" t="s">
         <v>122</v>
       </c>
-      <c r="B46" s="291"/>
+      <c r="B46" s="241"/>
     </row>
     <row r="47" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="291" t="s">
+      <c r="A47" s="241" t="s">
         <v>123</v>
       </c>
-      <c r="B47" s="291"/>
+      <c r="B47" s="241"/>
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="G15:G22"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:E36"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A3:G3"/>
@@ -8346,45 +6979,6 @@
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="G15:G22"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="D7:E7"/>
   </mergeCells>
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.78740157480314965" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="84" orientation="portrait" r:id="rId1"/>

--- a/backend/templates/UC-18gsm-290NP-ABQR.xlsx
+++ b/backend/templates/UC-18gsm-290NP-ABQR.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABCA98F-3912-46E8-BE56-CA0A23ACA099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC5F9C5-F525-461F-AB34-3B428DD21338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1426,7 +1426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="311">
+  <cellXfs count="312">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1852,6 +1852,120 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1861,166 +1975,133 @@
     <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2041,151 +2122,220 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2226,176 +2376,29 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2965,35 +2968,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="158" t="s">
+      <c r="A2" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3014,12 +3017,12 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="159" t="s">
+      <c r="A4" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="160"/>
-      <c r="C4" s="161"/>
-      <c r="D4" s="162"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="147"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -3031,19 +3034,19 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="154"/>
-      <c r="K4" s="155"/>
+      <c r="J4" s="139"/>
+      <c r="K4" s="140"/>
       <c r="M4" s="45" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="163" t="s">
+      <c r="A5" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="164"/>
-      <c r="C5" s="165"/>
-      <c r="D5" s="166"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="150"/>
+      <c r="D5" s="151"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -3055,64 +3058,64 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="156"/>
-      <c r="K5" s="157"/>
+      <c r="J5" s="141"/>
+      <c r="K5" s="142"/>
     </row>
     <row r="6" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="170" t="s">
+      <c r="A6" s="156" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="171"/>
-      <c r="C6" s="172"/>
+      <c r="B6" s="157"/>
+      <c r="C6" s="158"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="G6" s="150"/>
-      <c r="H6" s="169"/>
-      <c r="I6" s="150"/>
-      <c r="J6" s="151"/>
-      <c r="K6" s="152"/>
+      <c r="G6" s="134"/>
+      <c r="H6" s="155"/>
+      <c r="I6" s="134"/>
+      <c r="J6" s="135"/>
+      <c r="K6" s="136"/>
     </row>
     <row r="7" spans="1:13" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="137" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="138"/>
-      <c r="C7" s="138"/>
-      <c r="D7" s="138" t="s">
+      <c r="A7" s="159" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="137"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="138" t="s">
+      <c r="E7" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="138" t="s">
+      <c r="F7" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="167" t="s">
+      <c r="G7" s="152" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="167" t="s">
+      <c r="H7" s="152" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="138" t="s">
+      <c r="I7" s="137" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="138"/>
-      <c r="K7" s="153"/>
+      <c r="J7" s="137"/>
+      <c r="K7" s="138"/>
     </row>
     <row r="8" spans="1:13" s="5" customFormat="1" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="139"/>
-      <c r="B8" s="140"/>
-      <c r="C8" s="140"/>
-      <c r="D8" s="140"/>
-      <c r="E8" s="140" t="s">
+      <c r="A8" s="160"/>
+      <c r="B8" s="154"/>
+      <c r="C8" s="154"/>
+      <c r="D8" s="154"/>
+      <c r="E8" s="154" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="140"/>
-      <c r="G8" s="168"/>
-      <c r="H8" s="168"/>
+      <c r="F8" s="154"/>
+      <c r="G8" s="153"/>
+      <c r="H8" s="153"/>
       <c r="I8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3514,11 +3517,11 @@
       <c r="K38" s="28"/>
     </row>
     <row r="39" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="147" t="s">
+      <c r="A39" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="148"/>
-      <c r="C39" s="149"/>
+      <c r="B39" s="168"/>
+      <c r="C39" s="169"/>
       <c r="D39" s="35" t="e">
         <f>AVERAGE(D9:D38)</f>
         <v>#DIV/0!</v>
@@ -3553,11 +3556,11 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="144" t="s">
+      <c r="A40" s="164" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="145"/>
-      <c r="C40" s="146"/>
+      <c r="B40" s="165"/>
+      <c r="C40" s="166"/>
       <c r="D40" s="38">
         <f>MIN(D9:D38)</f>
         <v>0</v>
@@ -3592,11 +3595,11 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="141" t="s">
+      <c r="A41" s="161" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="142"/>
-      <c r="C41" s="143"/>
+      <c r="B41" s="162"/>
+      <c r="C41" s="163"/>
       <c r="D41" s="41">
         <f>MAX(D9:D38)</f>
         <v>0</v>
@@ -3637,8 +3640,8 @@
       <c r="A42" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="135"/>
-      <c r="C42" s="135"/>
+      <c r="B42" s="171"/>
+      <c r="C42" s="171"/>
       <c r="D42" s="44" t="s">
         <v>22</v>
       </c>
@@ -3655,8 +3658,8 @@
     </row>
     <row r="43" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="50"/>
-      <c r="B43" s="136"/>
-      <c r="C43" s="136"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="44"/>
       <c r="F43" s="46"/>
       <c r="G43" s="47"/>
@@ -3665,11 +3668,11 @@
       <c r="J43" s="51"/>
     </row>
     <row r="44" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="134" t="s">
+      <c r="A44" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="134"/>
-      <c r="C44" s="134"/>
+      <c r="B44" s="170"/>
+      <c r="C44" s="170"/>
       <c r="D44" s="44"/>
       <c r="E44" s="44"/>
       <c r="F44" s="47" t="s">
@@ -3681,11 +3684,11 @@
       <c r="H44" s="44"/>
     </row>
     <row r="45" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="134" t="s">
+      <c r="A45" s="170" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="134"/>
-      <c r="C45" s="134"/>
+      <c r="B45" s="170"/>
+      <c r="C45" s="170"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="44"/>
@@ -3696,9 +3699,9 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="134"/>
-      <c r="B46" s="134"/>
-      <c r="C46" s="134"/>
+      <c r="A46" s="170"/>
+      <c r="B46" s="170"/>
+      <c r="C46" s="170"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="44"/>
@@ -3727,6 +3730,16 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="26">
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A39:C39"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="J4:K4"/>
@@ -3743,16 +3756,6 @@
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A45:C45"/>
   </mergeCells>
   <conditionalFormatting sqref="D9:D41">
     <cfRule type="cellIs" dxfId="17" priority="13" operator="notBetween">
@@ -3819,35 +3822,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="158" t="s">
+      <c r="A2" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3868,18 +3871,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="159" t="s">
+      <c r="A4" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="160">
+      <c r="B4" s="145">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="185">
+      <c r="C4" s="220">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="186"/>
+      <c r="D4" s="182"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -3897,25 +3900,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="173">
+      <c r="J4" s="221">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="174"/>
+      <c r="K4" s="222"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="163" t="s">
+      <c r="A5" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="164">
+      <c r="B5" s="149">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="165">
+      <c r="C5" s="150">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="166"/>
+      <c r="D5" s="151"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -3933,104 +3936,104 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="175">
+      <c r="J5" s="223">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="176"/>
+      <c r="K5" s="224"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="212" t="s">
+      <c r="A6" s="173" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="213"/>
-      <c r="C6" s="214"/>
-      <c r="D6" s="215"/>
-      <c r="E6" s="204"/>
-      <c r="F6" s="199"/>
-      <c r="G6" s="198"/>
-      <c r="H6" s="199"/>
-      <c r="I6" s="200"/>
-      <c r="J6" s="201"/>
+      <c r="B6" s="174"/>
+      <c r="C6" s="175"/>
+      <c r="D6" s="176"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="178"/>
+      <c r="G6" s="193"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="207"/>
+      <c r="J6" s="208"/>
       <c r="K6" s="56"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="215" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="204"/>
-      <c r="C7" s="204"/>
-      <c r="D7" s="218" t="s">
+      <c r="A7" s="176" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="177"/>
+      <c r="C7" s="177"/>
+      <c r="D7" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="204"/>
-      <c r="F7" s="186"/>
-      <c r="G7" s="198" t="s">
+      <c r="E7" s="177"/>
+      <c r="F7" s="182"/>
+      <c r="G7" s="193" t="s">
         <v>126</v>
       </c>
-      <c r="H7" s="204"/>
-      <c r="I7" s="198" t="s">
+      <c r="H7" s="177"/>
+      <c r="I7" s="193" t="s">
         <v>135</v>
       </c>
-      <c r="J7" s="199"/>
-      <c r="K7" s="193" t="s">
+      <c r="J7" s="178"/>
+      <c r="K7" s="211" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="223"/>
-      <c r="B8" s="205"/>
-      <c r="C8" s="205"/>
-      <c r="D8" s="223" t="s">
+      <c r="A8" s="187"/>
+      <c r="B8" s="188"/>
+      <c r="C8" s="188"/>
+      <c r="D8" s="187" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="225" t="s">
+      <c r="E8" s="190" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="182" t="s">
+      <c r="F8" s="191" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="181"/>
-      <c r="H8" s="205"/>
-      <c r="I8" s="181" t="s">
+      <c r="G8" s="194"/>
+      <c r="H8" s="188"/>
+      <c r="I8" s="194" t="s">
         <v>136</v>
       </c>
-      <c r="J8" s="182"/>
-      <c r="K8" s="194"/>
+      <c r="J8" s="191"/>
+      <c r="K8" s="212"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="223"/>
-      <c r="B9" s="205"/>
-      <c r="C9" s="205"/>
-      <c r="D9" s="223"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="182"/>
-      <c r="G9" s="181"/>
-      <c r="H9" s="205"/>
+      <c r="A9" s="187"/>
+      <c r="B9" s="188"/>
+      <c r="C9" s="188"/>
+      <c r="D9" s="187"/>
+      <c r="E9" s="152"/>
+      <c r="F9" s="191"/>
+      <c r="G9" s="194"/>
+      <c r="H9" s="188"/>
       <c r="I9" s="58" t="s">
         <v>42</v>
       </c>
       <c r="J9" s="59">
         <v>290</v>
       </c>
-      <c r="K9" s="194"/>
+      <c r="K9" s="212"/>
     </row>
     <row r="10" spans="1:11" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="223"/>
-      <c r="B10" s="205"/>
-      <c r="C10" s="205"/>
-      <c r="D10" s="224"/>
-      <c r="E10" s="168"/>
-      <c r="F10" s="226"/>
-      <c r="G10" s="206"/>
-      <c r="H10" s="207"/>
+      <c r="A10" s="187"/>
+      <c r="B10" s="188"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="189"/>
+      <c r="E10" s="153"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="195"/>
+      <c r="H10" s="196"/>
       <c r="I10" s="60" t="s">
         <v>43</v>
       </c>
       <c r="J10" s="61">
         <v>293</v>
       </c>
-      <c r="K10" s="195"/>
+      <c r="K10" s="213"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="62">
@@ -4048,10 +4051,10 @@
       <c r="D11" s="65"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
-      <c r="G11" s="210"/>
-      <c r="H11" s="210"/>
-      <c r="I11" s="179"/>
-      <c r="J11" s="180"/>
+      <c r="G11" s="199"/>
+      <c r="H11" s="199"/>
+      <c r="I11" s="225"/>
+      <c r="J11" s="226"/>
       <c r="K11" s="66"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4070,10 +4073,10 @@
       <c r="D12" s="70"/>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
-      <c r="G12" s="211"/>
-      <c r="H12" s="211"/>
-      <c r="I12" s="177"/>
-      <c r="J12" s="178"/>
+      <c r="G12" s="200"/>
+      <c r="H12" s="200"/>
+      <c r="I12" s="205"/>
+      <c r="J12" s="206"/>
       <c r="K12" s="71"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4092,10 +4095,10 @@
       <c r="D13" s="70"/>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
-      <c r="G13" s="211"/>
-      <c r="H13" s="211"/>
-      <c r="I13" s="177"/>
-      <c r="J13" s="178"/>
+      <c r="G13" s="200"/>
+      <c r="H13" s="200"/>
+      <c r="I13" s="205"/>
+      <c r="J13" s="206"/>
       <c r="K13" s="71"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4114,10 +4117,10 @@
       <c r="D14" s="70"/>
       <c r="E14" s="25"/>
       <c r="F14" s="25"/>
-      <c r="G14" s="211"/>
-      <c r="H14" s="211"/>
-      <c r="I14" s="177"/>
-      <c r="J14" s="178"/>
+      <c r="G14" s="200"/>
+      <c r="H14" s="200"/>
+      <c r="I14" s="205"/>
+      <c r="J14" s="206"/>
       <c r="K14" s="71"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4136,10 +4139,10 @@
       <c r="D15" s="70"/>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
-      <c r="G15" s="211"/>
-      <c r="H15" s="211"/>
-      <c r="I15" s="177"/>
-      <c r="J15" s="178"/>
+      <c r="G15" s="200"/>
+      <c r="H15" s="200"/>
+      <c r="I15" s="205"/>
+      <c r="J15" s="206"/>
       <c r="K15" s="71"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4158,10 +4161,10 @@
       <c r="D16" s="65"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
-      <c r="G16" s="210"/>
-      <c r="H16" s="210"/>
-      <c r="I16" s="177"/>
-      <c r="J16" s="178"/>
+      <c r="G16" s="199"/>
+      <c r="H16" s="199"/>
+      <c r="I16" s="205"/>
+      <c r="J16" s="206"/>
       <c r="K16" s="66"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4180,10 +4183,10 @@
       <c r="D17" s="70"/>
       <c r="E17" s="25"/>
       <c r="F17" s="25"/>
-      <c r="G17" s="211"/>
-      <c r="H17" s="211"/>
-      <c r="I17" s="177"/>
-      <c r="J17" s="178"/>
+      <c r="G17" s="200"/>
+      <c r="H17" s="200"/>
+      <c r="I17" s="205"/>
+      <c r="J17" s="206"/>
       <c r="K17" s="71"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4202,10 +4205,10 @@
       <c r="D18" s="70"/>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
-      <c r="G18" s="211"/>
-      <c r="H18" s="211"/>
-      <c r="I18" s="177"/>
-      <c r="J18" s="178"/>
+      <c r="G18" s="200"/>
+      <c r="H18" s="200"/>
+      <c r="I18" s="205"/>
+      <c r="J18" s="206"/>
       <c r="K18" s="71"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4224,10 +4227,10 @@
       <c r="D19" s="70"/>
       <c r="E19" s="25"/>
       <c r="F19" s="25"/>
-      <c r="G19" s="211"/>
-      <c r="H19" s="211"/>
-      <c r="I19" s="177"/>
-      <c r="J19" s="178"/>
+      <c r="G19" s="200"/>
+      <c r="H19" s="200"/>
+      <c r="I19" s="205"/>
+      <c r="J19" s="206"/>
       <c r="K19" s="71"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4246,10 +4249,10 @@
       <c r="D20" s="70"/>
       <c r="E20" s="25"/>
       <c r="F20" s="25"/>
-      <c r="G20" s="183"/>
-      <c r="H20" s="184"/>
-      <c r="I20" s="177"/>
-      <c r="J20" s="178"/>
+      <c r="G20" s="201"/>
+      <c r="H20" s="202"/>
+      <c r="I20" s="205"/>
+      <c r="J20" s="206"/>
       <c r="K20" s="71"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4268,10 +4271,10 @@
       <c r="D21" s="70"/>
       <c r="E21" s="25"/>
       <c r="F21" s="25"/>
-      <c r="G21" s="183"/>
-      <c r="H21" s="184"/>
-      <c r="I21" s="177"/>
-      <c r="J21" s="178"/>
+      <c r="G21" s="201"/>
+      <c r="H21" s="202"/>
+      <c r="I21" s="205"/>
+      <c r="J21" s="206"/>
       <c r="K21" s="71"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4290,10 +4293,10 @@
       <c r="D22" s="70"/>
       <c r="E22" s="25"/>
       <c r="F22" s="25"/>
-      <c r="G22" s="183"/>
-      <c r="H22" s="184"/>
-      <c r="I22" s="177"/>
-      <c r="J22" s="178"/>
+      <c r="G22" s="201"/>
+      <c r="H22" s="202"/>
+      <c r="I22" s="205"/>
+      <c r="J22" s="206"/>
       <c r="K22" s="71"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4312,10 +4315,10 @@
       <c r="D23" s="70"/>
       <c r="E23" s="25"/>
       <c r="F23" s="25"/>
-      <c r="G23" s="183"/>
-      <c r="H23" s="184"/>
-      <c r="I23" s="177"/>
-      <c r="J23" s="178"/>
+      <c r="G23" s="201"/>
+      <c r="H23" s="202"/>
+      <c r="I23" s="205"/>
+      <c r="J23" s="206"/>
       <c r="K23" s="71"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4334,10 +4337,10 @@
       <c r="D24" s="70"/>
       <c r="E24" s="25"/>
       <c r="F24" s="25"/>
-      <c r="G24" s="183"/>
-      <c r="H24" s="184"/>
-      <c r="I24" s="177"/>
-      <c r="J24" s="178"/>
+      <c r="G24" s="201"/>
+      <c r="H24" s="202"/>
+      <c r="I24" s="205"/>
+      <c r="J24" s="206"/>
       <c r="K24" s="71"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4356,10 +4359,10 @@
       <c r="D25" s="70"/>
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
-      <c r="G25" s="183"/>
-      <c r="H25" s="184"/>
-      <c r="I25" s="177"/>
-      <c r="J25" s="178"/>
+      <c r="G25" s="201"/>
+      <c r="H25" s="202"/>
+      <c r="I25" s="205"/>
+      <c r="J25" s="206"/>
       <c r="K25" s="71"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4378,10 +4381,10 @@
       <c r="D26" s="70"/>
       <c r="E26" s="25"/>
       <c r="F26" s="25"/>
-      <c r="G26" s="183"/>
-      <c r="H26" s="184"/>
-      <c r="I26" s="177"/>
-      <c r="J26" s="178"/>
+      <c r="G26" s="201"/>
+      <c r="H26" s="202"/>
+      <c r="I26" s="205"/>
+      <c r="J26" s="206"/>
       <c r="K26" s="71"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4400,10 +4403,10 @@
       <c r="D27" s="70"/>
       <c r="E27" s="25"/>
       <c r="F27" s="25"/>
-      <c r="G27" s="183"/>
-      <c r="H27" s="184"/>
-      <c r="I27" s="177"/>
-      <c r="J27" s="178"/>
+      <c r="G27" s="201"/>
+      <c r="H27" s="202"/>
+      <c r="I27" s="205"/>
+      <c r="J27" s="206"/>
       <c r="K27" s="71"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4422,10 +4425,10 @@
       <c r="D28" s="70"/>
       <c r="E28" s="25"/>
       <c r="F28" s="25"/>
-      <c r="G28" s="183"/>
-      <c r="H28" s="184"/>
-      <c r="I28" s="177"/>
-      <c r="J28" s="178"/>
+      <c r="G28" s="201"/>
+      <c r="H28" s="202"/>
+      <c r="I28" s="205"/>
+      <c r="J28" s="206"/>
       <c r="K28" s="71"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4444,10 +4447,10 @@
       <c r="D29" s="70"/>
       <c r="E29" s="25"/>
       <c r="F29" s="25"/>
-      <c r="G29" s="183"/>
-      <c r="H29" s="184"/>
-      <c r="I29" s="177"/>
-      <c r="J29" s="178"/>
+      <c r="G29" s="201"/>
+      <c r="H29" s="202"/>
+      <c r="I29" s="205"/>
+      <c r="J29" s="206"/>
       <c r="K29" s="71"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4466,10 +4469,10 @@
       <c r="D30" s="70"/>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
-      <c r="G30" s="183"/>
-      <c r="H30" s="184"/>
-      <c r="I30" s="177"/>
-      <c r="J30" s="178"/>
+      <c r="G30" s="201"/>
+      <c r="H30" s="202"/>
+      <c r="I30" s="205"/>
+      <c r="J30" s="206"/>
       <c r="K30" s="71"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4488,10 +4491,10 @@
       <c r="D31" s="70"/>
       <c r="E31" s="25"/>
       <c r="F31" s="25"/>
-      <c r="G31" s="183"/>
-      <c r="H31" s="184"/>
-      <c r="I31" s="177"/>
-      <c r="J31" s="178"/>
+      <c r="G31" s="201"/>
+      <c r="H31" s="202"/>
+      <c r="I31" s="205"/>
+      <c r="J31" s="206"/>
       <c r="K31" s="71"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4510,10 +4513,10 @@
       <c r="D32" s="70"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
-      <c r="G32" s="183"/>
-      <c r="H32" s="184"/>
-      <c r="I32" s="177"/>
-      <c r="J32" s="178"/>
+      <c r="G32" s="201"/>
+      <c r="H32" s="202"/>
+      <c r="I32" s="205"/>
+      <c r="J32" s="206"/>
       <c r="K32" s="71"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4532,10 +4535,10 @@
       <c r="D33" s="70"/>
       <c r="E33" s="25"/>
       <c r="F33" s="25"/>
-      <c r="G33" s="183"/>
-      <c r="H33" s="184"/>
-      <c r="I33" s="177"/>
-      <c r="J33" s="178"/>
+      <c r="G33" s="201"/>
+      <c r="H33" s="202"/>
+      <c r="I33" s="205"/>
+      <c r="J33" s="206"/>
       <c r="K33" s="71"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4554,10 +4557,10 @@
       <c r="D34" s="70"/>
       <c r="E34" s="25"/>
       <c r="F34" s="25"/>
-      <c r="G34" s="183"/>
-      <c r="H34" s="184"/>
-      <c r="I34" s="177"/>
-      <c r="J34" s="178"/>
+      <c r="G34" s="201"/>
+      <c r="H34" s="202"/>
+      <c r="I34" s="205"/>
+      <c r="J34" s="206"/>
       <c r="K34" s="71"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4576,10 +4579,10 @@
       <c r="D35" s="70"/>
       <c r="E35" s="25"/>
       <c r="F35" s="25"/>
-      <c r="G35" s="183"/>
-      <c r="H35" s="184"/>
-      <c r="I35" s="177"/>
-      <c r="J35" s="178"/>
+      <c r="G35" s="201"/>
+      <c r="H35" s="202"/>
+      <c r="I35" s="205"/>
+      <c r="J35" s="206"/>
       <c r="K35" s="71"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4598,10 +4601,10 @@
       <c r="D36" s="70"/>
       <c r="E36" s="25"/>
       <c r="F36" s="25"/>
-      <c r="G36" s="183"/>
-      <c r="H36" s="184"/>
-      <c r="I36" s="177"/>
-      <c r="J36" s="178"/>
+      <c r="G36" s="201"/>
+      <c r="H36" s="202"/>
+      <c r="I36" s="205"/>
+      <c r="J36" s="206"/>
       <c r="K36" s="71"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4620,10 +4623,10 @@
       <c r="D37" s="70"/>
       <c r="E37" s="25"/>
       <c r="F37" s="25"/>
-      <c r="G37" s="183"/>
-      <c r="H37" s="184"/>
-      <c r="I37" s="177"/>
-      <c r="J37" s="178"/>
+      <c r="G37" s="201"/>
+      <c r="H37" s="202"/>
+      <c r="I37" s="205"/>
+      <c r="J37" s="206"/>
       <c r="K37" s="71"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4642,10 +4645,10 @@
       <c r="D38" s="70"/>
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
-      <c r="G38" s="183"/>
-      <c r="H38" s="184"/>
-      <c r="I38" s="177"/>
-      <c r="J38" s="178"/>
+      <c r="G38" s="201"/>
+      <c r="H38" s="202"/>
+      <c r="I38" s="205"/>
+      <c r="J38" s="206"/>
       <c r="K38" s="71"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4664,10 +4667,10 @@
       <c r="D39" s="70"/>
       <c r="E39" s="25"/>
       <c r="F39" s="25"/>
-      <c r="G39" s="183"/>
-      <c r="H39" s="184"/>
-      <c r="I39" s="177"/>
-      <c r="J39" s="178"/>
+      <c r="G39" s="201"/>
+      <c r="H39" s="202"/>
+      <c r="I39" s="205"/>
+      <c r="J39" s="206"/>
       <c r="K39" s="71"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4686,18 +4689,18 @@
       <c r="D40" s="70"/>
       <c r="E40" s="25"/>
       <c r="F40" s="25"/>
-      <c r="G40" s="211"/>
-      <c r="H40" s="211"/>
-      <c r="I40" s="177"/>
-      <c r="J40" s="178"/>
+      <c r="G40" s="200"/>
+      <c r="H40" s="200"/>
+      <c r="I40" s="205"/>
+      <c r="J40" s="206"/>
       <c r="K40" s="71"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="219" t="s">
+      <c r="A41" s="183" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="220"/>
-      <c r="C41" s="220"/>
+      <c r="B41" s="184"/>
+      <c r="C41" s="184"/>
       <c r="D41" s="79" t="e">
         <f>AVERAGE(D11:D40)</f>
         <v>#DIV/0!</v>
@@ -4710,27 +4713,27 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G41" s="208" t="e">
+      <c r="G41" s="197" t="e">
         <f>AVERAGE(G11:H40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="209"/>
-      <c r="I41" s="202" t="e">
+      <c r="H41" s="198"/>
+      <c r="I41" s="209" t="e">
         <f>AVERAGE(I11:J40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="203"/>
+      <c r="J41" s="210"/>
       <c r="K41" s="37" t="e">
         <f>AVERAGE(K11:K40)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="221" t="s">
+      <c r="A42" s="185" t="s">
         <v>31</v>
       </c>
-      <c r="B42" s="222"/>
-      <c r="C42" s="222"/>
+      <c r="B42" s="186"/>
+      <c r="C42" s="186"/>
       <c r="D42" s="80">
         <f>MIN(D11:D40)</f>
         <v>0</v>
@@ -4743,27 +4746,27 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G42" s="191">
+      <c r="G42" s="218">
         <f>MIN(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="192"/>
-      <c r="I42" s="196">
+      <c r="H42" s="219"/>
+      <c r="I42" s="203">
         <f>MIN(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="197"/>
+      <c r="J42" s="204"/>
       <c r="K42" s="40">
         <f>MIN(K11:K40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="216" t="s">
+      <c r="A43" s="179" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="217"/>
-      <c r="C43" s="217"/>
+      <c r="B43" s="180"/>
+      <c r="C43" s="180"/>
       <c r="D43" s="81">
         <f>MAX(D11:D40)</f>
         <v>0</v>
@@ -4776,16 +4779,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G43" s="189">
+      <c r="G43" s="216">
         <f>MAX(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="190"/>
-      <c r="I43" s="187">
+      <c r="H43" s="217"/>
+      <c r="I43" s="214">
         <f>MAX(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="188"/>
+      <c r="J43" s="215"/>
       <c r="K43" s="83">
         <f>MAX(K11:K40)</f>
         <v>0</v>
@@ -4795,8 +4798,8 @@
       <c r="A44" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="135"/>
-      <c r="C44" s="135"/>
+      <c r="B44" s="171"/>
+      <c r="C44" s="171"/>
       <c r="D44" s="44" t="s">
         <v>22</v>
       </c>
@@ -4813,8 +4816,8 @@
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="50"/>
-      <c r="B45" s="136"/>
-      <c r="C45" s="136"/>
+      <c r="B45" s="172"/>
+      <c r="C45" s="172"/>
       <c r="D45" s="44"/>
       <c r="F45" s="46"/>
       <c r="G45" s="47"/>
@@ -4823,11 +4826,11 @@
       <c r="J45" s="51"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="134" t="s">
+      <c r="A46" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="134"/>
-      <c r="C46" s="134"/>
+      <c r="B46" s="170"/>
+      <c r="C46" s="170"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="47" t="s">
@@ -4840,11 +4843,11 @@
       <c r="H46" s="44"/>
     </row>
     <row r="47" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="134" t="s">
+      <c r="A47" s="170" t="s">
         <v>134</v>
       </c>
-      <c r="B47" s="134"/>
-      <c r="C47" s="134"/>
+      <c r="B47" s="170"/>
+      <c r="C47" s="170"/>
       <c r="D47" s="44"/>
       <c r="E47" s="44"/>
       <c r="F47" s="44"/>
@@ -4899,19 +4902,71 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A7:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K7:K10"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I33:J33"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="G7:H10"/>
     <mergeCell ref="G41:H41"/>
@@ -4928,71 +4983,19 @@
     <mergeCell ref="G40:H40"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K7:K10"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A7:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="D11:D43">
@@ -5048,35 +5051,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="158"/>
-      <c r="J1" s="158"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="158" t="s">
+      <c r="A2" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -5097,18 +5100,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="159" t="s">
+      <c r="A4" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="160">
+      <c r="B4" s="145">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="185">
+      <c r="C4" s="220">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="186"/>
+      <c r="D4" s="182"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -5126,25 +5129,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="173">
+      <c r="J4" s="221">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="174"/>
+      <c r="K4" s="222"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="163" t="s">
+      <c r="A5" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="164">
+      <c r="B5" s="149">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="165">
+      <c r="C5" s="150">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="166"/>
+      <c r="D5" s="151"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -5162,81 +5165,81 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="175">
+      <c r="J5" s="223">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="176"/>
+      <c r="K5" s="224"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="170" t="s">
+      <c r="A6" s="156" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="171"/>
-      <c r="C6" s="227"/>
-      <c r="D6" s="228"/>
-      <c r="E6" s="151"/>
-      <c r="F6" s="151"/>
-      <c r="G6" s="169"/>
+      <c r="B6" s="157"/>
+      <c r="C6" s="235"/>
+      <c r="D6" s="236"/>
+      <c r="E6" s="135"/>
+      <c r="F6" s="135"/>
+      <c r="G6" s="155"/>
       <c r="H6" s="119"/>
-      <c r="I6" s="215"/>
-      <c r="J6" s="204"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="176"/>
+      <c r="J6" s="177"/>
+      <c r="K6" s="211"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="215" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="204"/>
-      <c r="C7" s="193"/>
-      <c r="D7" s="218" t="s">
+      <c r="A7" s="176" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="177"/>
+      <c r="C7" s="211"/>
+      <c r="D7" s="181" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="229"/>
-      <c r="F7" s="229"/>
-      <c r="G7" s="186"/>
-      <c r="H7" s="233" t="s">
+      <c r="E7" s="237"/>
+      <c r="F7" s="237"/>
+      <c r="G7" s="182"/>
+      <c r="H7" s="227" t="s">
         <v>130</v>
       </c>
-      <c r="I7" s="223"/>
-      <c r="J7" s="205"/>
-      <c r="K7" s="194"/>
+      <c r="I7" s="187"/>
+      <c r="J7" s="188"/>
+      <c r="K7" s="212"/>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="223"/>
-      <c r="B8" s="205"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="239" t="s">
+      <c r="A8" s="187"/>
+      <c r="B8" s="188"/>
+      <c r="C8" s="212"/>
+      <c r="D8" s="233" t="s">
         <v>127</v>
       </c>
-      <c r="E8" s="225" t="s">
+      <c r="E8" s="190" t="s">
         <v>128</v>
       </c>
-      <c r="F8" s="225" t="s">
+      <c r="F8" s="190" t="s">
         <v>131</v>
       </c>
-      <c r="G8" s="225" t="s">
+      <c r="G8" s="190" t="s">
         <v>129</v>
       </c>
-      <c r="H8" s="234" t="s">
+      <c r="H8" s="228" t="s">
         <v>130</v>
       </c>
-      <c r="I8" s="223"/>
-      <c r="J8" s="205"/>
-      <c r="K8" s="194"/>
+      <c r="I8" s="187"/>
+      <c r="J8" s="188"/>
+      <c r="K8" s="212"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="224"/>
-      <c r="B9" s="207"/>
-      <c r="C9" s="195"/>
-      <c r="D9" s="240"/>
-      <c r="E9" s="168"/>
-      <c r="F9" s="168"/>
-      <c r="G9" s="168"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="223"/>
-      <c r="J9" s="205"/>
-      <c r="K9" s="194"/>
+      <c r="A9" s="189"/>
+      <c r="B9" s="196"/>
+      <c r="C9" s="213"/>
+      <c r="D9" s="234"/>
+      <c r="E9" s="153"/>
+      <c r="F9" s="153"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="229"/>
+      <c r="I9" s="187"/>
+      <c r="J9" s="188"/>
+      <c r="K9" s="212"/>
     </row>
     <row r="10" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="62">
@@ -5256,9 +5259,9 @@
       <c r="F10" s="23"/>
       <c r="G10" s="121"/>
       <c r="H10" s="122"/>
-      <c r="I10" s="223"/>
-      <c r="J10" s="205"/>
-      <c r="K10" s="194"/>
+      <c r="I10" s="187"/>
+      <c r="J10" s="188"/>
+      <c r="K10" s="212"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="67">
@@ -5278,9 +5281,9 @@
       <c r="F11" s="26"/>
       <c r="G11" s="124"/>
       <c r="H11" s="125"/>
-      <c r="I11" s="223"/>
-      <c r="J11" s="205"/>
-      <c r="K11" s="194"/>
+      <c r="I11" s="187"/>
+      <c r="J11" s="188"/>
+      <c r="K11" s="212"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="67">
@@ -5300,9 +5303,9 @@
       <c r="F12" s="26"/>
       <c r="G12" s="124"/>
       <c r="H12" s="125"/>
-      <c r="I12" s="223"/>
-      <c r="J12" s="205"/>
-      <c r="K12" s="194"/>
+      <c r="I12" s="187"/>
+      <c r="J12" s="188"/>
+      <c r="K12" s="212"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="67">
@@ -5322,9 +5325,9 @@
       <c r="F13" s="23"/>
       <c r="G13" s="121"/>
       <c r="H13" s="125"/>
-      <c r="I13" s="223"/>
-      <c r="J13" s="205"/>
-      <c r="K13" s="194"/>
+      <c r="I13" s="187"/>
+      <c r="J13" s="188"/>
+      <c r="K13" s="212"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="67">
@@ -5344,9 +5347,9 @@
       <c r="F14" s="26"/>
       <c r="G14" s="124"/>
       <c r="H14" s="125"/>
-      <c r="I14" s="223"/>
-      <c r="J14" s="205"/>
-      <c r="K14" s="194"/>
+      <c r="I14" s="187"/>
+      <c r="J14" s="188"/>
+      <c r="K14" s="212"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="67">
@@ -5366,9 +5369,9 @@
       <c r="F15" s="26"/>
       <c r="G15" s="124"/>
       <c r="H15" s="125"/>
-      <c r="I15" s="223"/>
-      <c r="J15" s="205"/>
-      <c r="K15" s="194"/>
+      <c r="I15" s="187"/>
+      <c r="J15" s="188"/>
+      <c r="K15" s="212"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="67">
@@ -5388,9 +5391,9 @@
       <c r="F16" s="26"/>
       <c r="G16" s="124"/>
       <c r="H16" s="125"/>
-      <c r="I16" s="223"/>
-      <c r="J16" s="205"/>
-      <c r="K16" s="194"/>
+      <c r="I16" s="187"/>
+      <c r="J16" s="188"/>
+      <c r="K16" s="212"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="67">
@@ -5410,9 +5413,9 @@
       <c r="F17" s="26"/>
       <c r="G17" s="124"/>
       <c r="H17" s="125"/>
-      <c r="I17" s="223"/>
-      <c r="J17" s="205"/>
-      <c r="K17" s="194"/>
+      <c r="I17" s="187"/>
+      <c r="J17" s="188"/>
+      <c r="K17" s="212"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="67">
@@ -5432,9 +5435,9 @@
       <c r="F18" s="26"/>
       <c r="G18" s="124"/>
       <c r="H18" s="125"/>
-      <c r="I18" s="223"/>
-      <c r="J18" s="205"/>
-      <c r="K18" s="194"/>
+      <c r="I18" s="187"/>
+      <c r="J18" s="188"/>
+      <c r="K18" s="212"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="67">
@@ -5454,9 +5457,9 @@
       <c r="F19" s="26"/>
       <c r="G19" s="124"/>
       <c r="H19" s="125"/>
-      <c r="I19" s="223"/>
-      <c r="J19" s="205"/>
-      <c r="K19" s="194"/>
+      <c r="I19" s="187"/>
+      <c r="J19" s="188"/>
+      <c r="K19" s="212"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="75">
@@ -5476,9 +5479,9 @@
       <c r="F20" s="26"/>
       <c r="G20" s="124"/>
       <c r="H20" s="125"/>
-      <c r="I20" s="223"/>
-      <c r="J20" s="205"/>
-      <c r="K20" s="194"/>
+      <c r="I20" s="187"/>
+      <c r="J20" s="188"/>
+      <c r="K20" s="212"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="67">
@@ -5498,9 +5501,9 @@
       <c r="F21" s="26"/>
       <c r="G21" s="124"/>
       <c r="H21" s="125"/>
-      <c r="I21" s="223"/>
-      <c r="J21" s="205"/>
-      <c r="K21" s="194"/>
+      <c r="I21" s="187"/>
+      <c r="J21" s="188"/>
+      <c r="K21" s="212"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="67">
@@ -5520,9 +5523,9 @@
       <c r="F22" s="26"/>
       <c r="G22" s="124"/>
       <c r="H22" s="125"/>
-      <c r="I22" s="223"/>
-      <c r="J22" s="205"/>
-      <c r="K22" s="194"/>
+      <c r="I22" s="187"/>
+      <c r="J22" s="188"/>
+      <c r="K22" s="212"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="67">
@@ -5542,9 +5545,9 @@
       <c r="F23" s="26"/>
       <c r="G23" s="124"/>
       <c r="H23" s="125"/>
-      <c r="I23" s="223"/>
-      <c r="J23" s="205"/>
-      <c r="K23" s="194"/>
+      <c r="I23" s="187"/>
+      <c r="J23" s="188"/>
+      <c r="K23" s="212"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="67">
@@ -5564,9 +5567,9 @@
       <c r="F24" s="26"/>
       <c r="G24" s="124"/>
       <c r="H24" s="125"/>
-      <c r="I24" s="223"/>
-      <c r="J24" s="205"/>
-      <c r="K24" s="194"/>
+      <c r="I24" s="187"/>
+      <c r="J24" s="188"/>
+      <c r="K24" s="212"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="67">
@@ -5586,9 +5589,9 @@
       <c r="F25" s="26"/>
       <c r="G25" s="124"/>
       <c r="H25" s="125"/>
-      <c r="I25" s="223"/>
-      <c r="J25" s="205"/>
-      <c r="K25" s="194"/>
+      <c r="I25" s="187"/>
+      <c r="J25" s="188"/>
+      <c r="K25" s="212"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="67">
@@ -5608,9 +5611,9 @@
       <c r="F26" s="26"/>
       <c r="G26" s="124"/>
       <c r="H26" s="125"/>
-      <c r="I26" s="223"/>
-      <c r="J26" s="205"/>
-      <c r="K26" s="194"/>
+      <c r="I26" s="187"/>
+      <c r="J26" s="188"/>
+      <c r="K26" s="212"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="67">
@@ -5630,9 +5633,9 @@
       <c r="F27" s="26"/>
       <c r="G27" s="124"/>
       <c r="H27" s="125"/>
-      <c r="I27" s="223"/>
-      <c r="J27" s="205"/>
-      <c r="K27" s="194"/>
+      <c r="I27" s="187"/>
+      <c r="J27" s="188"/>
+      <c r="K27" s="212"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="67">
@@ -5652,9 +5655,9 @@
       <c r="F28" s="26"/>
       <c r="G28" s="124"/>
       <c r="H28" s="125"/>
-      <c r="I28" s="223"/>
-      <c r="J28" s="205"/>
-      <c r="K28" s="194"/>
+      <c r="I28" s="187"/>
+      <c r="J28" s="188"/>
+      <c r="K28" s="212"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="67">
@@ -5674,9 +5677,9 @@
       <c r="F29" s="26"/>
       <c r="G29" s="124"/>
       <c r="H29" s="125"/>
-      <c r="I29" s="223"/>
-      <c r="J29" s="205"/>
-      <c r="K29" s="194"/>
+      <c r="I29" s="187"/>
+      <c r="J29" s="188"/>
+      <c r="K29" s="212"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="75">
@@ -5696,9 +5699,9 @@
       <c r="F30" s="26"/>
       <c r="G30" s="124"/>
       <c r="H30" s="125"/>
-      <c r="I30" s="223"/>
-      <c r="J30" s="205"/>
-      <c r="K30" s="194"/>
+      <c r="I30" s="187"/>
+      <c r="J30" s="188"/>
+      <c r="K30" s="212"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="67">
@@ -5718,9 +5721,9 @@
       <c r="F31" s="26"/>
       <c r="G31" s="124"/>
       <c r="H31" s="125"/>
-      <c r="I31" s="223"/>
-      <c r="J31" s="205"/>
-      <c r="K31" s="194"/>
+      <c r="I31" s="187"/>
+      <c r="J31" s="188"/>
+      <c r="K31" s="212"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="67">
@@ -5740,9 +5743,9 @@
       <c r="F32" s="26"/>
       <c r="G32" s="124"/>
       <c r="H32" s="125"/>
-      <c r="I32" s="223"/>
-      <c r="J32" s="205"/>
-      <c r="K32" s="194"/>
+      <c r="I32" s="187"/>
+      <c r="J32" s="188"/>
+      <c r="K32" s="212"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="67">
@@ -5762,9 +5765,9 @@
       <c r="F33" s="26"/>
       <c r="G33" s="124"/>
       <c r="H33" s="125"/>
-      <c r="I33" s="223"/>
-      <c r="J33" s="205"/>
-      <c r="K33" s="194"/>
+      <c r="I33" s="187"/>
+      <c r="J33" s="188"/>
+      <c r="K33" s="212"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="67">
@@ -5784,9 +5787,9 @@
       <c r="F34" s="26"/>
       <c r="G34" s="124"/>
       <c r="H34" s="125"/>
-      <c r="I34" s="223"/>
-      <c r="J34" s="205"/>
-      <c r="K34" s="194"/>
+      <c r="I34" s="187"/>
+      <c r="J34" s="188"/>
+      <c r="K34" s="212"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="67">
@@ -5806,9 +5809,9 @@
       <c r="F35" s="26"/>
       <c r="G35" s="124"/>
       <c r="H35" s="125"/>
-      <c r="I35" s="223"/>
-      <c r="J35" s="205"/>
-      <c r="K35" s="194"/>
+      <c r="I35" s="187"/>
+      <c r="J35" s="188"/>
+      <c r="K35" s="212"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="67">
@@ -5828,9 +5831,9 @@
       <c r="F36" s="26"/>
       <c r="G36" s="124"/>
       <c r="H36" s="125"/>
-      <c r="I36" s="223"/>
-      <c r="J36" s="205"/>
-      <c r="K36" s="194"/>
+      <c r="I36" s="187"/>
+      <c r="J36" s="188"/>
+      <c r="K36" s="212"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="67">
@@ -5850,9 +5853,9 @@
       <c r="F37" s="26"/>
       <c r="G37" s="124"/>
       <c r="H37" s="125"/>
-      <c r="I37" s="223"/>
-      <c r="J37" s="205"/>
-      <c r="K37" s="194"/>
+      <c r="I37" s="187"/>
+      <c r="J37" s="188"/>
+      <c r="K37" s="212"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="67">
@@ -5872,9 +5875,9 @@
       <c r="F38" s="26"/>
       <c r="G38" s="124"/>
       <c r="H38" s="125"/>
-      <c r="I38" s="223"/>
-      <c r="J38" s="205"/>
-      <c r="K38" s="194"/>
+      <c r="I38" s="187"/>
+      <c r="J38" s="188"/>
+      <c r="K38" s="212"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="76">
@@ -5894,16 +5897,16 @@
       <c r="F39" s="26"/>
       <c r="G39" s="124"/>
       <c r="H39" s="125"/>
-      <c r="I39" s="223"/>
-      <c r="J39" s="205"/>
-      <c r="K39" s="194"/>
+      <c r="I39" s="187"/>
+      <c r="J39" s="188"/>
+      <c r="K39" s="212"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="230" t="s">
+      <c r="A40" s="238" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="231"/>
-      <c r="C40" s="232"/>
+      <c r="B40" s="239"/>
+      <c r="C40" s="240"/>
       <c r="D40" s="126" t="e">
         <f>AVERAGE(D10:D39)</f>
         <v>#DIV/0!</v>
@@ -5924,16 +5927,16 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I40" s="223"/>
-      <c r="J40" s="205"/>
-      <c r="K40" s="194"/>
+      <c r="I40" s="187"/>
+      <c r="J40" s="188"/>
+      <c r="K40" s="212"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="144" t="s">
+      <c r="A41" s="164" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="145"/>
-      <c r="C41" s="146"/>
+      <c r="B41" s="165"/>
+      <c r="C41" s="166"/>
       <c r="D41" s="128">
         <f>MIN(D10:D39)</f>
         <v>0</v>
@@ -5954,16 +5957,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I41" s="223"/>
-      <c r="J41" s="205"/>
-      <c r="K41" s="194"/>
+      <c r="I41" s="187"/>
+      <c r="J41" s="188"/>
+      <c r="K41" s="212"/>
     </row>
     <row r="42" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="236" t="s">
+      <c r="A42" s="230" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="237"/>
-      <c r="C42" s="238"/>
+      <c r="B42" s="231"/>
+      <c r="C42" s="232"/>
       <c r="D42" s="130">
         <f>MAX(D10:D39)</f>
         <v>0</v>
@@ -5984,16 +5987,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I42" s="224"/>
-      <c r="J42" s="207"/>
-      <c r="K42" s="195"/>
+      <c r="I42" s="189"/>
+      <c r="J42" s="196"/>
+      <c r="K42" s="213"/>
     </row>
     <row r="43" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="135"/>
-      <c r="C43" s="135"/>
+      <c r="B43" s="171"/>
+      <c r="C43" s="171"/>
       <c r="D43" s="44" t="s">
         <v>22</v>
       </c>
@@ -6010,8 +6013,8 @@
     </row>
     <row r="44" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="50"/>
-      <c r="B44" s="136"/>
-      <c r="C44" s="136"/>
+      <c r="B44" s="172"/>
+      <c r="C44" s="172"/>
       <c r="D44" s="44"/>
       <c r="F44" s="46"/>
       <c r="G44" s="47"/>
@@ -6020,11 +6023,11 @@
       <c r="J44" s="51"/>
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="134" t="s">
+      <c r="A45" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="134"/>
-      <c r="C45" s="134"/>
+      <c r="B45" s="170"/>
+      <c r="C45" s="170"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="47" t="s">
@@ -6037,11 +6040,11 @@
       <c r="H45" s="44"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="134" t="s">
+      <c r="A46" s="170" t="s">
         <v>134</v>
       </c>
-      <c r="B46" s="134"/>
-      <c r="C46" s="134"/>
+      <c r="B46" s="170"/>
+      <c r="C46" s="170"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="44"/>
@@ -6066,15 +6069,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A7:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="J4:K4"/>
@@ -6091,6 +6085,15 @@
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="A40:C40"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A7:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
   </mergeCells>
   <conditionalFormatting sqref="D10:D42">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="notBetween">
@@ -6137,15 +6140,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="304" t="s">
+      <c r="A1" s="241" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="305"/>
-      <c r="C1" s="305"/>
-      <c r="D1" s="305"/>
-      <c r="E1" s="305"/>
-      <c r="F1" s="305"/>
-      <c r="G1" s="306"/>
+      <c r="B1" s="242"/>
+      <c r="C1" s="242"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="242"/>
+      <c r="F1" s="242"/>
+      <c r="G1" s="243"/>
     </row>
     <row r="2" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="87"/>
@@ -6159,37 +6162,37 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="242" t="s">
+      <c r="A3" s="292" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="243"/>
-      <c r="C3" s="243"/>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="244"/>
+      <c r="B3" s="293"/>
+      <c r="C3" s="293"/>
+      <c r="D3" s="293"/>
+      <c r="E3" s="293"/>
+      <c r="F3" s="293"/>
+      <c r="G3" s="294"/>
     </row>
     <row r="4" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="223" t="s">
+      <c r="A4" s="187" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="205"/>
-      <c r="C4" s="205"/>
-      <c r="D4" s="205"/>
-      <c r="E4" s="205"/>
-      <c r="F4" s="205"/>
-      <c r="G4" s="194"/>
+      <c r="B4" s="188"/>
+      <c r="C4" s="188"/>
+      <c r="D4" s="188"/>
+      <c r="E4" s="188"/>
+      <c r="F4" s="188"/>
+      <c r="G4" s="212"/>
     </row>
     <row r="5" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="307" t="s">
+      <c r="A5" s="244" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="308"/>
-      <c r="C5" s="308"/>
-      <c r="D5" s="308"/>
-      <c r="E5" s="308"/>
-      <c r="F5" s="308"/>
-      <c r="G5" s="309"/>
+      <c r="B5" s="245"/>
+      <c r="C5" s="245"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="246"/>
     </row>
     <row r="6" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="90" t="s">
@@ -6201,15 +6204,15 @@
       <c r="C6" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="263">
+      <c r="D6" s="247">
         <f>Page1!H4</f>
         <v>0</v>
       </c>
-      <c r="E6" s="265"/>
-      <c r="F6" s="284" t="s">
+      <c r="E6" s="248"/>
+      <c r="F6" s="249" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="288">
+      <c r="G6" s="250">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
@@ -6222,13 +6225,13 @@
       <c r="C7" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="263">
+      <c r="D7" s="247">
         <f>Page1!F5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="265"/>
-      <c r="F7" s="284"/>
-      <c r="G7" s="310"/>
+      <c r="E7" s="248"/>
+      <c r="F7" s="249"/>
+      <c r="G7" s="251"/>
     </row>
     <row r="8" spans="1:7" s="86" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="90" t="s">
@@ -6241,15 +6244,15 @@
       <c r="C8" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="284">
+      <c r="D8" s="249">
         <f>Page1!H5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="284"/>
-      <c r="F8" s="285" t="s">
+      <c r="E8" s="249"/>
+      <c r="F8" s="261" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="288">
+      <c r="G8" s="250">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
@@ -6262,15 +6265,15 @@
         <f>Page1!G44</f>
         <v>461347000</v>
       </c>
-      <c r="C9" s="285" t="s">
+      <c r="C9" s="261" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="291" t="s">
+      <c r="D9" s="266" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="292"/>
-      <c r="F9" s="286"/>
-      <c r="G9" s="289"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="262"/>
+      <c r="G9" s="264"/>
     </row>
     <row r="10" spans="1:7" s="86" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="97" t="s">
@@ -6280,34 +6283,34 @@
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="C10" s="287"/>
-      <c r="D10" s="293"/>
-      <c r="E10" s="294"/>
-      <c r="F10" s="287"/>
-      <c r="G10" s="290"/>
+      <c r="C10" s="263"/>
+      <c r="D10" s="268"/>
+      <c r="E10" s="269"/>
+      <c r="F10" s="263"/>
+      <c r="G10" s="265"/>
     </row>
     <row r="11" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="295" t="s">
+      <c r="A11" s="252" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="297" t="s">
+      <c r="B11" s="254" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="299" t="s">
+      <c r="C11" s="256" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="300"/>
-      <c r="E11" s="301"/>
-      <c r="F11" s="297" t="s">
+      <c r="D11" s="257"/>
+      <c r="E11" s="258"/>
+      <c r="F11" s="254" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="302" t="s">
+      <c r="G11" s="259" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="296"/>
-      <c r="B12" s="298"/>
+      <c r="A12" s="253"/>
+      <c r="B12" s="255"/>
       <c r="C12" s="99" t="s">
         <v>63</v>
       </c>
@@ -6317,8 +6320,8 @@
       <c r="E12" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="298"/>
-      <c r="G12" s="303"/>
+      <c r="F12" s="255"/>
+      <c r="G12" s="260"/>
     </row>
     <row r="13" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="100" t="s">
@@ -6388,7 +6391,7 @@
         <f>Page1!K39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="280" t="s">
+      <c r="G15" s="270" t="s">
         <v>74</v>
       </c>
     </row>
@@ -6412,7 +6415,7 @@
         <f>Page2!F41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="234"/>
+      <c r="G16" s="228"/>
     </row>
     <row r="17" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="104" t="s">
@@ -6434,7 +6437,7 @@
         <f>Page1!I39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="234"/>
+      <c r="G17" s="228"/>
     </row>
     <row r="18" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="104" t="s">
@@ -6456,7 +6459,7 @@
         <f>Page2!D41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="234"/>
+      <c r="G18" s="228"/>
     </row>
     <row r="19" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="104" t="s">
@@ -6478,7 +6481,7 @@
         <f>Page1!J39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="234"/>
+      <c r="G19" s="228"/>
     </row>
     <row r="20" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="104" t="s">
@@ -6500,7 +6503,7 @@
         <f>Page2!E41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="234"/>
+      <c r="G20" s="228"/>
     </row>
     <row r="21" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="104" t="s">
@@ -6522,7 +6525,7 @@
         <f>Page1!G39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="234"/>
+      <c r="G21" s="228"/>
     </row>
     <row r="22" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="104" t="s">
@@ -6544,7 +6547,7 @@
         <f>Page1!H39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="153"/>
+      <c r="G22" s="138"/>
     </row>
     <row r="23" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="104" t="s">
@@ -6644,26 +6647,26 @@
       </c>
     </row>
     <row r="27" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="277" t="s">
+      <c r="A27" s="271" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="278"/>
-      <c r="C27" s="278"/>
-      <c r="D27" s="278"/>
-      <c r="E27" s="278"/>
-      <c r="F27" s="278"/>
-      <c r="G27" s="279"/>
+      <c r="B27" s="272"/>
+      <c r="C27" s="272"/>
+      <c r="D27" s="272"/>
+      <c r="E27" s="272"/>
+      <c r="F27" s="272"/>
+      <c r="G27" s="273"/>
     </row>
     <row r="28" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="261" t="s">
+      <c r="A28" s="274" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="262"/>
-      <c r="C28" s="281" t="s">
+      <c r="B28" s="275"/>
+      <c r="C28" s="276" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="282"/>
-      <c r="E28" s="283"/>
+      <c r="D28" s="277"/>
+      <c r="E28" s="278"/>
       <c r="F28" s="113" t="s">
         <v>95</v>
       </c>
@@ -6672,15 +6675,15 @@
       </c>
     </row>
     <row r="29" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="266" t="s">
+      <c r="A29" s="279" t="s">
         <v>97</v>
       </c>
-      <c r="B29" s="265"/>
-      <c r="C29" s="271" t="s">
+      <c r="B29" s="248"/>
+      <c r="C29" s="280" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="272"/>
-      <c r="E29" s="273"/>
+      <c r="D29" s="281"/>
+      <c r="E29" s="282"/>
       <c r="F29" s="80" t="s">
         <v>95</v>
       </c>
@@ -6689,15 +6692,15 @@
       </c>
     </row>
     <row r="30" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="266" t="s">
+      <c r="A30" s="279" t="s">
         <v>100</v>
       </c>
-      <c r="B30" s="265"/>
-      <c r="C30" s="271" t="s">
+      <c r="B30" s="248"/>
+      <c r="C30" s="280" t="s">
         <v>101</v>
       </c>
-      <c r="D30" s="272"/>
-      <c r="E30" s="273"/>
+      <c r="D30" s="281"/>
+      <c r="E30" s="282"/>
       <c r="F30" s="80" t="s">
         <v>95</v>
       </c>
@@ -6706,15 +6709,15 @@
       </c>
     </row>
     <row r="31" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="266" t="s">
+      <c r="A31" s="279" t="s">
         <v>102</v>
       </c>
-      <c r="B31" s="265"/>
-      <c r="C31" s="271" t="s">
+      <c r="B31" s="248"/>
+      <c r="C31" s="280" t="s">
         <v>103</v>
       </c>
-      <c r="D31" s="272"/>
-      <c r="E31" s="273"/>
+      <c r="D31" s="281"/>
+      <c r="E31" s="282"/>
       <c r="F31" s="80" t="s">
         <v>95</v>
       </c>
@@ -6723,15 +6726,15 @@
       </c>
     </row>
     <row r="32" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="266" t="s">
+      <c r="A32" s="279" t="s">
         <v>105</v>
       </c>
-      <c r="B32" s="265"/>
-      <c r="C32" s="271" t="s">
+      <c r="B32" s="248"/>
+      <c r="C32" s="280" t="s">
         <v>106</v>
       </c>
-      <c r="D32" s="272"/>
-      <c r="E32" s="273"/>
+      <c r="D32" s="281"/>
+      <c r="E32" s="282"/>
       <c r="F32" s="80" t="s">
         <v>95</v>
       </c>
@@ -6740,15 +6743,15 @@
       </c>
     </row>
     <row r="33" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="266" t="s">
+      <c r="A33" s="279" t="s">
         <v>107</v>
       </c>
-      <c r="B33" s="265"/>
-      <c r="C33" s="271" t="s">
+      <c r="B33" s="248"/>
+      <c r="C33" s="280" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="272"/>
-      <c r="E33" s="273"/>
+      <c r="D33" s="281"/>
+      <c r="E33" s="282"/>
       <c r="F33" s="80" t="s">
         <v>95</v>
       </c>
@@ -6757,15 +6760,15 @@
       </c>
     </row>
     <row r="34" spans="1:7" s="86" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="163" t="s">
+      <c r="A34" s="148" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="164"/>
-      <c r="C34" s="274" t="s">
+      <c r="B34" s="149"/>
+      <c r="C34" s="283" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="275"/>
-      <c r="E34" s="276"/>
+      <c r="D34" s="284"/>
+      <c r="E34" s="285"/>
       <c r="F34" s="114" t="s">
         <v>95</v>
       </c>
@@ -6774,26 +6777,26 @@
       </c>
     </row>
     <row r="35" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="277" t="s">
+      <c r="A35" s="271" t="s">
         <v>112</v>
       </c>
-      <c r="B35" s="278"/>
-      <c r="C35" s="278"/>
-      <c r="D35" s="278"/>
-      <c r="E35" s="278"/>
-      <c r="F35" s="278"/>
-      <c r="G35" s="279"/>
+      <c r="B35" s="272"/>
+      <c r="C35" s="272"/>
+      <c r="D35" s="272"/>
+      <c r="E35" s="272"/>
+      <c r="F35" s="272"/>
+      <c r="G35" s="273"/>
     </row>
     <row r="36" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="159" t="s">
+      <c r="A36" s="144" t="s">
         <v>113</v>
       </c>
-      <c r="B36" s="160"/>
-      <c r="C36" s="269" t="s">
+      <c r="B36" s="145"/>
+      <c r="C36" s="289" t="s">
         <v>101</v>
       </c>
-      <c r="D36" s="270"/>
-      <c r="E36" s="160"/>
+      <c r="D36" s="290"/>
+      <c r="E36" s="145"/>
       <c r="F36" s="10" t="s">
         <v>95</v>
       </c>
@@ -6802,15 +6805,15 @@
       </c>
     </row>
     <row r="37" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="261" t="s">
+      <c r="A37" s="274" t="s">
         <v>114</v>
       </c>
-      <c r="B37" s="262"/>
-      <c r="C37" s="263" t="s">
+      <c r="B37" s="275"/>
+      <c r="C37" s="247" t="s">
         <v>115</v>
       </c>
-      <c r="D37" s="264"/>
-      <c r="E37" s="265"/>
+      <c r="D37" s="286"/>
+      <c r="E37" s="248"/>
       <c r="F37" s="106" t="s">
         <v>95</v>
       </c>
@@ -6819,15 +6822,15 @@
       </c>
     </row>
     <row r="38" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="266" t="s">
+      <c r="A38" s="279" t="s">
         <v>116</v>
       </c>
-      <c r="B38" s="265"/>
-      <c r="C38" s="263" t="s">
+      <c r="B38" s="248"/>
+      <c r="C38" s="247" t="s">
         <v>117</v>
       </c>
-      <c r="D38" s="264"/>
-      <c r="E38" s="265"/>
+      <c r="D38" s="286"/>
+      <c r="E38" s="248"/>
       <c r="F38" s="106" t="s">
         <v>95</v>
       </c>
@@ -6836,15 +6839,15 @@
       </c>
     </row>
     <row r="39" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="163" t="s">
+      <c r="A39" s="148" t="s">
         <v>118</v>
       </c>
-      <c r="B39" s="164"/>
-      <c r="C39" s="267" t="s">
+      <c r="B39" s="149"/>
+      <c r="C39" s="287" t="s">
         <v>119</v>
       </c>
-      <c r="D39" s="268"/>
-      <c r="E39" s="164"/>
+      <c r="D39" s="288"/>
+      <c r="E39" s="149"/>
       <c r="F39" s="1" t="s">
         <v>95</v>
       </c>
@@ -6853,50 +6856,50 @@
       </c>
     </row>
     <row r="40" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="245" t="s">
+      <c r="A40" s="295" t="s">
         <v>120</v>
       </c>
-      <c r="B40" s="246"/>
-      <c r="C40" s="247" t="s">
+      <c r="B40" s="296"/>
+      <c r="C40" s="297" t="s">
         <v>137</v>
       </c>
-      <c r="D40" s="248"/>
-      <c r="E40" s="249"/>
-      <c r="F40" s="247" t="s">
+      <c r="D40" s="298"/>
+      <c r="E40" s="299"/>
+      <c r="F40" s="297" t="s">
         <v>138</v>
       </c>
-      <c r="G40" s="249"/>
-    </row>
-    <row r="41" spans="1:7" s="86" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="250"/>
-      <c r="B41" s="251"/>
-      <c r="C41" s="223"/>
-      <c r="D41" s="205"/>
-      <c r="E41" s="194"/>
-      <c r="F41" s="254"/>
-      <c r="G41" s="255"/>
-    </row>
-    <row r="42" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="252"/>
-      <c r="B42" s="253"/>
-      <c r="C42" s="256" t="s">
+      <c r="G40" s="299"/>
+    </row>
+    <row r="41" spans="1:7" s="86" customFormat="1" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="300"/>
+      <c r="B41" s="301"/>
+      <c r="C41" s="306"/>
+      <c r="D41" s="307"/>
+      <c r="E41" s="308"/>
+      <c r="F41" s="306"/>
+      <c r="G41" s="308"/>
+    </row>
+    <row r="42" spans="1:7" s="86" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="302"/>
+      <c r="B42" s="303"/>
+      <c r="C42" s="309" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="257"/>
-      <c r="E42" s="258"/>
-      <c r="F42" s="256" t="s">
+      <c r="D42" s="310"/>
+      <c r="E42" s="311"/>
+      <c r="F42" s="309" t="s">
         <v>139</v>
       </c>
-      <c r="G42" s="258"/>
+      <c r="G42" s="311"/>
     </row>
     <row r="43" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="115"/>
       <c r="B43" s="115"/>
       <c r="C43" s="115"/>
       <c r="D43" s="115"/>
-      <c r="E43" s="259"/>
-      <c r="F43" s="259"/>
-      <c r="G43" s="259"/>
+      <c r="E43" s="304"/>
+      <c r="F43" s="304"/>
+      <c r="G43" s="304"/>
     </row>
     <row r="44" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="46" t="s">
@@ -6905,64 +6908,25 @@
       <c r="B44" s="116"/>
       <c r="C44" s="117"/>
       <c r="D44" s="115"/>
-      <c r="E44" s="260"/>
-      <c r="F44" s="260"/>
-      <c r="G44" s="260"/>
+      <c r="E44" s="305"/>
+      <c r="F44" s="305"/>
+      <c r="G44" s="305"/>
     </row>
     <row r="45" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="241" t="s">
+      <c r="A46" s="291" t="s">
         <v>122</v>
       </c>
-      <c r="B46" s="241"/>
+      <c r="B46" s="291"/>
     </row>
     <row r="47" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="241" t="s">
+      <c r="A47" s="291" t="s">
         <v>123</v>
       </c>
-      <c r="B47" s="241"/>
+      <c r="B47" s="291"/>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="G15:G22"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:E36"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A3:G3"/>
@@ -6979,6 +6943,45 @@
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="G15:G22"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="D7:E7"/>
   </mergeCells>
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.78740157480314965" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="84" orientation="portrait" r:id="rId1"/>
